--- a/jogos_2025-07-16.xlsx
+++ b/jogos_2025-07-16.xlsx
@@ -169,27 +169,27 @@
     <t>Norway Eliteserien</t>
   </si>
   <si>
+    <t>USA MLS</t>
+  </si>
+  <si>
+    <t>USA USL Championship</t>
+  </si>
+  <si>
     <t>USA MLS Next Pro</t>
   </si>
   <si>
-    <t>USA MLS</t>
-  </si>
-  <si>
-    <t>USA USL Championship</t>
-  </si>
-  <si>
     <t>2025</t>
   </si>
   <si>
     <t>Grêmio</t>
   </si>
   <si>
+    <t>Bahia</t>
+  </si>
+  <si>
     <t>Atlético Mineiro</t>
   </si>
   <si>
-    <t>Bahia</t>
-  </si>
-  <si>
     <t>Juventude</t>
   </si>
   <si>
@@ -205,60 +205,60 @@
     <t>Santos</t>
   </si>
   <si>
+    <t>New York RB</t>
+  </si>
+  <si>
+    <t>Charlotte</t>
+  </si>
+  <si>
+    <t>Philadelphia Union</t>
+  </si>
+  <si>
+    <t>Atlanta United FC</t>
+  </si>
+  <si>
+    <t>FC Cincinnati</t>
+  </si>
+  <si>
+    <t>Hartford Athletic</t>
+  </si>
+  <si>
+    <t>Orlando City</t>
+  </si>
+  <si>
     <t>New York City II</t>
   </si>
   <si>
-    <t>Orlando City</t>
-  </si>
-  <si>
-    <t>FC Cincinnati</t>
-  </si>
-  <si>
-    <t>Hartford Athletic</t>
-  </si>
-  <si>
-    <t>Philadelphia Union</t>
-  </si>
-  <si>
-    <t>Atlanta United FC</t>
-  </si>
-  <si>
-    <t>Charlotte</t>
-  </si>
-  <si>
-    <t>New York RB</t>
-  </si>
-  <si>
     <t>St. Louis City II</t>
   </si>
   <si>
+    <t>Botafogo</t>
+  </si>
+  <si>
+    <t>Tulsa Roughnecks</t>
+  </si>
+  <si>
+    <t>Nashville SC</t>
+  </si>
+  <si>
     <t>Minnesota United</t>
   </si>
   <si>
-    <t>Tulsa Roughnecks</t>
-  </si>
-  <si>
-    <t>Nashville SC</t>
+    <t>Houston Dynamo</t>
   </si>
   <si>
     <t>Bragantino</t>
   </si>
   <si>
-    <t>Houston Dynamo</t>
-  </si>
-  <si>
-    <t>Botafogo</t>
-  </si>
-  <si>
     <t>Seattle Sounders</t>
   </si>
   <si>
+    <t>Portland Timbers</t>
+  </si>
+  <si>
     <t>SJ Earthquakes</t>
   </si>
   <si>
-    <t>Portland Timbers</t>
-  </si>
-  <si>
     <t>San Diego</t>
   </si>
   <si>
@@ -268,12 +268,12 @@
     <t>Fortaleza</t>
   </si>
   <si>
+    <t>Internacional</t>
+  </si>
+  <si>
     <t>Sport Recife</t>
   </si>
   <si>
-    <t>Internacional</t>
-  </si>
-  <si>
     <t>Vasco da Gama</t>
   </si>
   <si>
@@ -289,58 +289,58 @@
     <t>Flamengo</t>
   </si>
   <si>
+    <t>New England Revolution</t>
+  </si>
+  <si>
+    <t>DC United</t>
+  </si>
+  <si>
+    <t>Montreal Impact</t>
+  </si>
+  <si>
+    <t>Chicago Fire</t>
+  </si>
+  <si>
+    <t>Inter Miami</t>
+  </si>
+  <si>
+    <t>Tampa Bay Rowdies</t>
+  </si>
+  <si>
+    <t>New York City</t>
+  </si>
+  <si>
     <t>Toronto II</t>
   </si>
   <si>
-    <t>New York City</t>
-  </si>
-  <si>
-    <t>Inter Miami</t>
-  </si>
-  <si>
-    <t>Tampa Bay Rowdies</t>
-  </si>
-  <si>
-    <t>Montreal Impact</t>
-  </si>
-  <si>
-    <t>Chicago Fire</t>
-  </si>
-  <si>
-    <t>DC United</t>
-  </si>
-  <si>
-    <t>New England Revolution</t>
-  </si>
-  <si>
     <t>LA Galaxy II</t>
   </si>
   <si>
+    <t>Vitória</t>
+  </si>
+  <si>
+    <t>Monterey Bay</t>
+  </si>
+  <si>
+    <t>Columbus Crew</t>
+  </si>
+  <si>
     <t>Los Angeles FC</t>
   </si>
   <si>
-    <t>Monterey Bay</t>
-  </si>
-  <si>
-    <t>Columbus Crew</t>
+    <t>Vancouver Whitecaps</t>
   </si>
   <si>
     <t>São Paulo</t>
   </si>
   <si>
-    <t>Vancouver Whitecaps</t>
-  </si>
-  <si>
-    <t>Vitória</t>
-  </si>
-  <si>
     <t>Colorado Rapids</t>
   </si>
   <si>
+    <t>Real Salt Lake</t>
+  </si>
+  <si>
     <t>FC Dallas</t>
-  </si>
-  <si>
-    <t>Real Salt Lake</t>
   </si>
   <si>
     <t>Toronto</t>
@@ -986,43 +986,43 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="L3">
-        <v>1.48</v>
+        <v>2.51</v>
       </c>
       <c r="M3">
-        <v>4.4</v>
+        <v>3.16</v>
       </c>
       <c r="N3">
-        <v>6.4</v>
+        <v>2.9</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="P3">
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X3">
         <v>0</v>
@@ -1037,10 +1037,10 @@
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>1.91</v>
+        <v>2.3</v>
       </c>
       <c r="AC3">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -1049,10 +1049,10 @@
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -1102,43 +1102,43 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L4">
-        <v>2.44</v>
+        <v>1.48</v>
       </c>
       <c r="M4">
-        <v>3.09</v>
+        <v>4.4</v>
       </c>
       <c r="N4">
-        <v>2.89</v>
+        <v>5.93</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P4">
         <v>0</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X4">
         <v>0</v>
@@ -1153,10 +1153,10 @@
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>2.3</v>
+        <v>1.91</v>
       </c>
       <c r="AC4">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AD4">
         <v>0</v>
@@ -1165,10 +1165,10 @@
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH4">
         <v>0</v>
@@ -1221,13 +1221,13 @@
         <v>112</v>
       </c>
       <c r="L5">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="M5">
         <v>3.25</v>
       </c>
       <c r="N5">
-        <v>2.79</v>
+        <v>2.95</v>
       </c>
       <c r="O5">
         <v>0</v>
@@ -1453,10 +1453,10 @@
         <v>111</v>
       </c>
       <c r="L7">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="M7">
-        <v>4.4</v>
+        <v>4.34</v>
       </c>
       <c r="N7">
         <v>8.5</v>
@@ -1474,13 +1474,13 @@
         <v>1.4</v>
       </c>
       <c r="S7">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="T7">
         <v>3.17</v>
       </c>
       <c r="U7">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V7">
         <v>8</v>
@@ -1489,31 +1489,31 @@
         <v>1.06</v>
       </c>
       <c r="X7">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y7">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Z7">
         <v>1.31</v>
       </c>
       <c r="AA7">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="AB7">
         <v>2.05</v>
       </c>
       <c r="AC7">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AD7">
-        <v>3.72</v>
+        <v>3.6</v>
       </c>
       <c r="AE7">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AF7">
-        <v>2.25</v>
+        <v>2.34</v>
       </c>
       <c r="AG7">
         <v>1.6</v>
@@ -1569,13 +1569,13 @@
         <v>111</v>
       </c>
       <c r="L8">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="M8">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="N8">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="O8">
         <v>1.91</v>
@@ -1590,7 +1590,7 @@
         <v>1.46</v>
       </c>
       <c r="S8">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="T8">
         <v>3.14</v>
@@ -1605,28 +1605,28 @@
         <v>1.02</v>
       </c>
       <c r="X8">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="Y8">
-        <v>6.85</v>
+        <v>7</v>
       </c>
       <c r="Z8">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AA8">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="AB8">
         <v>2.38</v>
       </c>
       <c r="AC8">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="AD8">
         <v>4</v>
       </c>
       <c r="AE8">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AF8">
         <v>1.95</v>
@@ -1635,7 +1635,7 @@
         <v>1.75</v>
       </c>
       <c r="AH8">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="AI8">
         <v>1.02</v>
@@ -1688,10 +1688,10 @@
         <v>4</v>
       </c>
       <c r="M9">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="N9">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="O9">
         <v>2.63</v>
@@ -1703,55 +1703,55 @@
         <v>1.57</v>
       </c>
       <c r="R9">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="S9">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="T9">
         <v>3</v>
       </c>
       <c r="U9">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="V9">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="W9">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X9">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y9">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="Z9">
         <v>1.36</v>
       </c>
       <c r="AA9">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="AB9">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="AC9">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AD9">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="AE9">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AF9">
         <v>1.99</v>
       </c>
       <c r="AG9">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AH9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI9">
         <v>1.02</v>
@@ -1801,76 +1801,76 @@
         <v>111</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH10">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AI10">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AJ10" t="s">
         <v>113</v>
@@ -1890,7 +1890,7 @@
         <v>44</v>
       </c>
       <c r="C11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D11" t="s">
         <v>54</v>
@@ -1917,22 +1917,22 @@
         <v>111</v>
       </c>
       <c r="L11">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="M11">
-        <v>3.55</v>
+        <v>3.81</v>
       </c>
       <c r="N11">
-        <v>3.83</v>
+        <v>4.2</v>
       </c>
       <c r="O11">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="P11">
         <v>13</v>
       </c>
       <c r="Q11">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="R11">
         <v>1.27</v>
@@ -1941,16 +1941,16 @@
         <v>3.4</v>
       </c>
       <c r="T11">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="U11">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="V11">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="W11">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X11">
         <v>1.04</v>
@@ -1959,34 +1959,34 @@
         <v>10</v>
       </c>
       <c r="Z11">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AA11">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="AB11">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AC11">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AD11">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="AE11">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AF11">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AG11">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AH11">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AI11">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AJ11" t="s">
         <v>113</v>
@@ -2006,7 +2006,7 @@
         <v>44</v>
       </c>
       <c r="C12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D12" t="s">
         <v>54</v>
@@ -2033,40 +2033,40 @@
         <v>111</v>
       </c>
       <c r="L12">
-        <v>2.06</v>
+        <v>1.38</v>
       </c>
       <c r="M12">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="N12">
-        <v>2.82</v>
+        <v>6</v>
       </c>
       <c r="O12">
-        <v>1.82</v>
+        <v>1.44</v>
       </c>
       <c r="P12">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Q12">
-        <v>2.05</v>
+        <v>2.95</v>
       </c>
       <c r="R12">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S12">
         <v>3.4</v>
       </c>
       <c r="T12">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="U12">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="V12">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="W12">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X12">
         <v>1.04</v>
@@ -2075,34 +2075,34 @@
         <v>10</v>
       </c>
       <c r="Z12">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AA12">
-        <v>4.75</v>
+        <v>4.33</v>
       </c>
       <c r="AB12">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AC12">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AD12">
-        <v>2.1</v>
+        <v>2.55</v>
       </c>
       <c r="AE12">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AF12">
-        <v>1.47</v>
+        <v>1.7</v>
       </c>
       <c r="AG12">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="AH12">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AI12">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AJ12" t="s">
         <v>113</v>
@@ -2122,7 +2122,7 @@
         <v>44</v>
       </c>
       <c r="C13" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D13" t="s">
         <v>54</v>
@@ -2149,76 +2149,76 @@
         <v>111</v>
       </c>
       <c r="L13">
-        <v>2.55</v>
+        <v>2</v>
       </c>
       <c r="M13">
-        <v>3.3</v>
+        <v>3.63</v>
       </c>
       <c r="N13">
-        <v>2.49</v>
+        <v>2.91</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AB13">
-        <v>1.83</v>
+        <v>1.59</v>
       </c>
       <c r="AC13">
-        <v>1.91</v>
+        <v>2.36</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH13">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AI13">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AJ13" t="s">
         <v>113</v>
@@ -2238,7 +2238,7 @@
         <v>44</v>
       </c>
       <c r="C14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D14" t="s">
         <v>54</v>
@@ -2265,40 +2265,40 @@
         <v>111</v>
       </c>
       <c r="L14">
-        <v>1.38</v>
+        <v>2.06</v>
       </c>
       <c r="M14">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="N14">
-        <v>6</v>
+        <v>2.82</v>
       </c>
       <c r="O14">
-        <v>1.44</v>
+        <v>1.82</v>
       </c>
       <c r="P14">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Q14">
-        <v>2.95</v>
+        <v>2.05</v>
       </c>
       <c r="R14">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S14">
         <v>3.4</v>
       </c>
       <c r="T14">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="U14">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="V14">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="W14">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X14">
         <v>1.04</v>
@@ -2307,34 +2307,34 @@
         <v>10</v>
       </c>
       <c r="Z14">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AA14">
-        <v>4.33</v>
+        <v>4.75</v>
       </c>
       <c r="AB14">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AC14">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="AD14">
-        <v>2.55</v>
+        <v>2.1</v>
       </c>
       <c r="AE14">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AF14">
-        <v>1.7</v>
+        <v>1.47</v>
       </c>
       <c r="AG14">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="AH14">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="AI14">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AJ14" t="s">
         <v>113</v>
@@ -2381,76 +2381,76 @@
         <v>111</v>
       </c>
       <c r="L15">
-        <v>2</v>
+        <v>2.55</v>
       </c>
       <c r="M15">
-        <v>3.63</v>
+        <v>3.32</v>
       </c>
       <c r="N15">
-        <v>2.91</v>
+        <v>2.5</v>
       </c>
       <c r="O15">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="P15">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Q15">
-        <v>2.15</v>
+        <v>1.92</v>
       </c>
       <c r="R15">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="S15">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="T15">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="U15">
-        <v>1.58</v>
+        <v>1.4</v>
       </c>
       <c r="V15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W15">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X15">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y15">
         <v>10</v>
       </c>
       <c r="Z15">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AA15">
-        <v>4.75</v>
+        <v>3.6</v>
       </c>
       <c r="AB15">
-        <v>1.59</v>
+        <v>1.85</v>
       </c>
       <c r="AC15">
-        <v>2.36</v>
+        <v>1.93</v>
       </c>
       <c r="AD15">
-        <v>2.25</v>
+        <v>3.1</v>
       </c>
       <c r="AE15">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="AF15">
-        <v>1.49</v>
+        <v>1.67</v>
       </c>
       <c r="AG15">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="AH15">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="AI15">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AJ15" t="s">
         <v>113</v>
@@ -2470,7 +2470,7 @@
         <v>44</v>
       </c>
       <c r="C16" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D16" t="s">
         <v>54</v>
@@ -2497,22 +2497,22 @@
         <v>111</v>
       </c>
       <c r="L16">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="M16">
-        <v>3.81</v>
+        <v>3.55</v>
       </c>
       <c r="N16">
-        <v>4.2</v>
+        <v>3.83</v>
       </c>
       <c r="O16">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="P16">
         <v>13</v>
       </c>
       <c r="Q16">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="R16">
         <v>1.27</v>
@@ -2521,16 +2521,16 @@
         <v>3.4</v>
       </c>
       <c r="T16">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="U16">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="V16">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="W16">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X16">
         <v>1.04</v>
@@ -2539,34 +2539,34 @@
         <v>10</v>
       </c>
       <c r="Z16">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AA16">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="AB16">
+        <v>1.65</v>
+      </c>
+      <c r="AC16">
+        <v>2.1</v>
+      </c>
+      <c r="AD16">
+        <v>2.4</v>
+      </c>
+      <c r="AE16">
         <v>1.57</v>
       </c>
-      <c r="AC16">
+      <c r="AF16">
+        <v>1.57</v>
+      </c>
+      <c r="AG16">
         <v>2.25</v>
       </c>
-      <c r="AD16">
-        <v>2.55</v>
-      </c>
-      <c r="AE16">
-        <v>1.5</v>
-      </c>
-      <c r="AF16">
-        <v>1.61</v>
-      </c>
-      <c r="AG16">
-        <v>2.15</v>
-      </c>
       <c r="AH16">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="AI16">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AJ16" t="s">
         <v>113</v>
@@ -2586,7 +2586,7 @@
         <v>44</v>
       </c>
       <c r="C17" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D17" t="s">
         <v>54</v>
@@ -2613,76 +2613,76 @@
         <v>111</v>
       </c>
       <c r="L17">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M17">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N17">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="O17">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="P17">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="Q17">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="R17">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S17">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T17">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U17">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="V17">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W17">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X17">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y17">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="Z17">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AA17">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AB17">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC17">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD17">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AE17">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AF17">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH17">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AI17">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="s">
         <v>113</v>
@@ -2702,7 +2702,7 @@
         <v>45</v>
       </c>
       <c r="C18" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D18" t="s">
         <v>54</v>
@@ -2818,7 +2818,7 @@
         <v>46</v>
       </c>
       <c r="C19" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D19" t="s">
         <v>54</v>
@@ -2845,76 +2845,76 @@
         <v>111</v>
       </c>
       <c r="L19">
-        <v>2.53</v>
+        <v>1.53</v>
       </c>
       <c r="M19">
-        <v>3.3</v>
+        <v>4.12</v>
       </c>
       <c r="N19">
-        <v>2.37</v>
+        <v>6.72</v>
       </c>
       <c r="O19">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="P19">
-        <v>10</v>
+        <v>8.25</v>
       </c>
       <c r="Q19">
-        <v>1.93</v>
+        <v>3.5</v>
       </c>
       <c r="R19">
+        <v>1.4</v>
+      </c>
+      <c r="S19">
+        <v>2.88</v>
+      </c>
+      <c r="T19">
+        <v>2.91</v>
+      </c>
+      <c r="U19">
         <v>1.33</v>
       </c>
-      <c r="S19">
+      <c r="V19">
+        <v>7</v>
+      </c>
+      <c r="W19">
+        <v>1.08</v>
+      </c>
+      <c r="X19">
+        <v>1.02</v>
+      </c>
+      <c r="Y19">
+        <v>8.5</v>
+      </c>
+      <c r="Z19">
+        <v>1.36</v>
+      </c>
+      <c r="AA19">
         <v>3</v>
       </c>
-      <c r="T19">
-        <v>2.5</v>
-      </c>
-      <c r="U19">
-        <v>1.46</v>
-      </c>
-      <c r="V19">
-        <v>6</v>
-      </c>
-      <c r="W19">
-        <v>1.11</v>
-      </c>
-      <c r="X19">
-        <v>1.05</v>
-      </c>
-      <c r="Y19">
-        <v>9.5</v>
-      </c>
-      <c r="Z19">
-        <v>1.25</v>
-      </c>
-      <c r="AA19">
-        <v>3.75</v>
-      </c>
       <c r="AB19">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="AC19">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AD19">
-        <v>3</v>
+        <v>3.55</v>
       </c>
       <c r="AE19">
-        <v>1.38</v>
+        <v>1.23</v>
       </c>
       <c r="AF19">
-        <v>1.63</v>
+        <v>2.19</v>
       </c>
       <c r="AG19">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="AH19">
-        <v>5.5</v>
+        <v>6.75</v>
       </c>
       <c r="AI19">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AJ19" t="s">
         <v>113</v>
@@ -2934,7 +2934,7 @@
         <v>46</v>
       </c>
       <c r="C20" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D20" t="s">
         <v>54</v>
@@ -2961,76 +2961,76 @@
         <v>111</v>
       </c>
       <c r="L20">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="M20">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="N20">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>11.75</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AB20">
+        <v>1.89</v>
+      </c>
+      <c r="AC20">
+        <v>1.87</v>
+      </c>
+      <c r="AD20">
+        <v>3.14</v>
+      </c>
+      <c r="AE20">
+        <v>1.3</v>
+      </c>
+      <c r="AF20">
         <v>1.91</v>
       </c>
-      <c r="AC20">
-        <v>1.88</v>
-      </c>
-      <c r="AD20">
-        <v>0</v>
-      </c>
-      <c r="AE20">
-        <v>0</v>
-      </c>
-      <c r="AF20">
-        <v>0</v>
-      </c>
       <c r="AG20">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH20">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AI20">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AJ20" t="s">
         <v>113</v>
@@ -3050,7 +3050,7 @@
         <v>46</v>
       </c>
       <c r="C21" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D21" t="s">
         <v>54</v>
@@ -3166,7 +3166,7 @@
         <v>46</v>
       </c>
       <c r="C22" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D22" t="s">
         <v>54</v>
@@ -3193,76 +3193,76 @@
         <v>111</v>
       </c>
       <c r="L22">
-        <v>2.18</v>
+        <v>2.53</v>
       </c>
       <c r="M22">
+        <v>3.3</v>
+      </c>
+      <c r="N22">
+        <v>2.37</v>
+      </c>
+      <c r="O22">
+        <v>2</v>
+      </c>
+      <c r="P22">
+        <v>10</v>
+      </c>
+      <c r="Q22">
+        <v>1.93</v>
+      </c>
+      <c r="R22">
+        <v>1.33</v>
+      </c>
+      <c r="S22">
         <v>3</v>
       </c>
-      <c r="N22">
-        <v>3.22</v>
-      </c>
-      <c r="O22">
-        <v>1.73</v>
-      </c>
-      <c r="P22">
-        <v>7</v>
-      </c>
-      <c r="Q22">
+      <c r="T22">
         <v>2.5</v>
       </c>
-      <c r="R22">
-        <v>1.5</v>
-      </c>
-      <c r="S22">
-        <v>2.4</v>
-      </c>
-      <c r="T22">
-        <v>3.28</v>
-      </c>
       <c r="U22">
-        <v>1.29</v>
+        <v>1.46</v>
       </c>
       <c r="V22">
-        <v>9.1</v>
+        <v>6</v>
       </c>
       <c r="W22">
+        <v>1.11</v>
+      </c>
+      <c r="X22">
         <v>1.05</v>
       </c>
-      <c r="X22">
-        <v>1.08</v>
-      </c>
       <c r="Y22">
-        <v>7.7</v>
+        <v>9.5</v>
       </c>
       <c r="Z22">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AA22">
-        <v>2.63</v>
+        <v>3.75</v>
       </c>
       <c r="AB22">
-        <v>2.3</v>
+        <v>1.75</v>
       </c>
       <c r="AC22">
-        <v>1.58</v>
+        <v>1.95</v>
       </c>
       <c r="AD22">
-        <v>4.45</v>
+        <v>3</v>
       </c>
       <c r="AE22">
-        <v>1.16</v>
+        <v>1.38</v>
       </c>
       <c r="AF22">
-        <v>2</v>
+        <v>1.63</v>
       </c>
       <c r="AG22">
-        <v>1.74</v>
+        <v>2.1</v>
       </c>
       <c r="AH22">
-        <v>9.5</v>
+        <v>5.5</v>
       </c>
       <c r="AI22">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AJ22" t="s">
         <v>113</v>
@@ -3282,7 +3282,7 @@
         <v>46</v>
       </c>
       <c r="C23" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D23" t="s">
         <v>54</v>
@@ -3425,76 +3425,76 @@
         <v>111</v>
       </c>
       <c r="L24">
-        <v>1.53</v>
+        <v>2.29</v>
       </c>
       <c r="M24">
-        <v>4.1</v>
+        <v>3.24</v>
       </c>
       <c r="N24">
-        <v>6.72</v>
+        <v>3.3</v>
       </c>
       <c r="O24">
+        <v>1.73</v>
+      </c>
+      <c r="P24">
+        <v>7</v>
+      </c>
+      <c r="Q24">
+        <v>2.5</v>
+      </c>
+      <c r="R24">
+        <v>1.45</v>
+      </c>
+      <c r="S24">
+        <v>2.48</v>
+      </c>
+      <c r="T24">
+        <v>3.3</v>
+      </c>
+      <c r="U24">
+        <v>1.29</v>
+      </c>
+      <c r="V24">
+        <v>8</v>
+      </c>
+      <c r="W24">
+        <v>1.05</v>
+      </c>
+      <c r="X24">
+        <v>1.03</v>
+      </c>
+      <c r="Y24">
+        <v>7.7</v>
+      </c>
+      <c r="Z24">
         <v>1.4</v>
       </c>
-      <c r="P24">
-        <v>8.25</v>
-      </c>
-      <c r="Q24">
-        <v>3.5</v>
-      </c>
-      <c r="R24">
-        <v>1.4</v>
-      </c>
-      <c r="S24">
-        <v>2.83</v>
-      </c>
-      <c r="T24">
-        <v>2.95</v>
-      </c>
-      <c r="U24">
-        <v>1.36</v>
-      </c>
-      <c r="V24">
-        <v>7</v>
-      </c>
-      <c r="W24">
-        <v>1.06</v>
-      </c>
-      <c r="X24">
-        <v>1.02</v>
-      </c>
-      <c r="Y24">
-        <v>7.8</v>
-      </c>
-      <c r="Z24">
-        <v>1.36</v>
-      </c>
       <c r="AA24">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="AB24">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AC24">
-        <v>1.72</v>
+        <v>1.58</v>
       </c>
       <c r="AD24">
-        <v>4.2</v>
+        <v>4.45</v>
       </c>
       <c r="AE24">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AF24">
-        <v>2.19</v>
+        <v>1.98</v>
       </c>
       <c r="AG24">
-        <v>1.6</v>
+        <v>1.74</v>
       </c>
       <c r="AH24">
-        <v>6.8</v>
+        <v>9.5</v>
       </c>
       <c r="AI24">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AJ24" t="s">
         <v>113</v>
@@ -3514,7 +3514,7 @@
         <v>47</v>
       </c>
       <c r="C25" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D25" t="s">
         <v>54</v>
@@ -3630,7 +3630,7 @@
         <v>48</v>
       </c>
       <c r="C26" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D26" t="s">
         <v>54</v>
@@ -3657,76 +3657,76 @@
         <v>111</v>
       </c>
       <c r="L26">
-        <v>1.59</v>
+        <v>1.99</v>
       </c>
       <c r="M26">
-        <v>3.95</v>
+        <v>3.25</v>
       </c>
       <c r="N26">
+        <v>3.25</v>
+      </c>
+      <c r="O26">
+        <v>1.67</v>
+      </c>
+      <c r="P26">
+        <v>10.5</v>
+      </c>
+      <c r="Q26">
+        <v>2.3</v>
+      </c>
+      <c r="R26">
+        <v>1.3</v>
+      </c>
+      <c r="S26">
+        <v>3.4</v>
+      </c>
+      <c r="T26">
+        <v>2.5</v>
+      </c>
+      <c r="U26">
+        <v>1.5</v>
+      </c>
+      <c r="V26">
+        <v>6</v>
+      </c>
+      <c r="W26">
+        <v>1.13</v>
+      </c>
+      <c r="X26">
+        <v>1.05</v>
+      </c>
+      <c r="Y26">
+        <v>9.5</v>
+      </c>
+      <c r="Z26">
+        <v>1.22</v>
+      </c>
+      <c r="AA26">
         <v>4.2</v>
       </c>
-      <c r="O26">
-        <v>1.51</v>
-      </c>
-      <c r="P26">
-        <v>17.5</v>
-      </c>
-      <c r="Q26">
-        <v>2.55</v>
-      </c>
-      <c r="R26">
-        <v>1.2</v>
-      </c>
-      <c r="S26">
-        <v>4.1</v>
-      </c>
-      <c r="T26">
-        <v>1.93</v>
-      </c>
-      <c r="U26">
-        <v>1.77</v>
-      </c>
-      <c r="V26">
-        <v>4</v>
-      </c>
-      <c r="W26">
-        <v>1.21</v>
-      </c>
-      <c r="X26">
-        <v>1.01</v>
-      </c>
-      <c r="Y26">
-        <v>23</v>
-      </c>
-      <c r="Z26">
-        <v>1.11</v>
-      </c>
-      <c r="AA26">
-        <v>6.25</v>
-      </c>
       <c r="AB26">
-        <v>1.38</v>
+        <v>1.65</v>
       </c>
       <c r="AC26">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="AD26">
-        <v>1.9</v>
+        <v>2.62</v>
       </c>
       <c r="AE26">
-        <v>1.8</v>
+        <v>1.48</v>
       </c>
       <c r="AF26">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AG26">
-        <v>2.55</v>
+        <v>2.25</v>
       </c>
       <c r="AH26">
-        <v>3.1</v>
+        <v>4.75</v>
       </c>
       <c r="AI26">
-        <v>1.35</v>
+        <v>1.18</v>
       </c>
       <c r="AJ26" t="s">
         <v>113</v>
@@ -3746,7 +3746,7 @@
         <v>48</v>
       </c>
       <c r="C27" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D27" t="s">
         <v>54</v>
@@ -3773,76 +3773,76 @@
         <v>111</v>
       </c>
       <c r="L27">
-        <v>2</v>
+        <v>1.59</v>
       </c>
       <c r="M27">
-        <v>3.28</v>
+        <v>3.95</v>
       </c>
       <c r="N27">
-        <v>3.28</v>
+        <v>4.2</v>
       </c>
       <c r="O27">
-        <v>1.67</v>
+        <v>1.51</v>
       </c>
       <c r="P27">
-        <v>10.5</v>
+        <v>17.5</v>
       </c>
       <c r="Q27">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="R27">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="S27">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="T27">
-        <v>2.5</v>
+        <v>1.93</v>
       </c>
       <c r="U27">
-        <v>1.5</v>
+        <v>1.77</v>
       </c>
       <c r="V27">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="W27">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="X27">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y27">
-        <v>9.5</v>
+        <v>23</v>
       </c>
       <c r="Z27">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="AA27">
-        <v>4.2</v>
+        <v>6.25</v>
       </c>
       <c r="AB27">
-        <v>1.7</v>
+        <v>1.36</v>
       </c>
       <c r="AC27">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="AD27">
-        <v>2.62</v>
+        <v>1.9</v>
       </c>
       <c r="AE27">
-        <v>1.48</v>
+        <v>1.8</v>
       </c>
       <c r="AF27">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AG27">
-        <v>2.25</v>
+        <v>2.55</v>
       </c>
       <c r="AH27">
-        <v>4.75</v>
+        <v>3.1</v>
       </c>
       <c r="AI27">
-        <v>1.18</v>
+        <v>1.35</v>
       </c>
       <c r="AJ27" t="s">
         <v>113</v>
@@ -3862,7 +3862,7 @@
         <v>48</v>
       </c>
       <c r="C28" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D28" t="s">
         <v>54</v>
@@ -3978,7 +3978,7 @@
         <v>48</v>
       </c>
       <c r="C29" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D29" t="s">
         <v>54</v>

--- a/jogos_2025-07-16.xlsx
+++ b/jogos_2025-07-16.xlsx
@@ -184,12 +184,12 @@
     <t>Grêmio</t>
   </si>
   <si>
+    <t>Atlético Mineiro</t>
+  </si>
+  <si>
     <t>Bahia</t>
   </si>
   <si>
-    <t>Atlético Mineiro</t>
-  </si>
-  <si>
     <t>Juventude</t>
   </si>
   <si>
@@ -205,51 +205,51 @@
     <t>Santos</t>
   </si>
   <si>
+    <t>Philadelphia Union</t>
+  </si>
+  <si>
+    <t>Hartford Athletic</t>
+  </si>
+  <si>
+    <t>Orlando City</t>
+  </si>
+  <si>
+    <t>FC Cincinnati</t>
+  </si>
+  <si>
+    <t>New York City II</t>
+  </si>
+  <si>
+    <t>Charlotte</t>
+  </si>
+  <si>
     <t>New York RB</t>
   </si>
   <si>
-    <t>Charlotte</t>
-  </si>
-  <si>
-    <t>Philadelphia Union</t>
-  </si>
-  <si>
     <t>Atlanta United FC</t>
   </si>
   <si>
-    <t>FC Cincinnati</t>
-  </si>
-  <si>
-    <t>Hartford Athletic</t>
-  </si>
-  <si>
-    <t>Orlando City</t>
-  </si>
-  <si>
-    <t>New York City II</t>
-  </si>
-  <si>
     <t>St. Louis City II</t>
   </si>
   <si>
+    <t>Tulsa Roughnecks</t>
+  </si>
+  <si>
+    <t>Bragantino</t>
+  </si>
+  <si>
+    <t>Houston Dynamo</t>
+  </si>
+  <si>
+    <t>Minnesota United</t>
+  </si>
+  <si>
     <t>Botafogo</t>
   </si>
   <si>
-    <t>Tulsa Roughnecks</t>
-  </si>
-  <si>
     <t>Nashville SC</t>
   </si>
   <si>
-    <t>Minnesota United</t>
-  </si>
-  <si>
-    <t>Houston Dynamo</t>
-  </si>
-  <si>
-    <t>Bragantino</t>
-  </si>
-  <si>
     <t>Seattle Sounders</t>
   </si>
   <si>
@@ -268,12 +268,12 @@
     <t>Fortaleza</t>
   </si>
   <si>
+    <t>Sport Recife</t>
+  </si>
+  <si>
     <t>Internacional</t>
   </si>
   <si>
-    <t>Sport Recife</t>
-  </si>
-  <si>
     <t>Vasco da Gama</t>
   </si>
   <si>
@@ -289,49 +289,49 @@
     <t>Flamengo</t>
   </si>
   <si>
+    <t>Montreal Impact</t>
+  </si>
+  <si>
+    <t>Tampa Bay Rowdies</t>
+  </si>
+  <si>
+    <t>New York City</t>
+  </si>
+  <si>
+    <t>Inter Miami</t>
+  </si>
+  <si>
+    <t>Toronto II</t>
+  </si>
+  <si>
+    <t>DC United</t>
+  </si>
+  <si>
     <t>New England Revolution</t>
   </si>
   <si>
-    <t>DC United</t>
-  </si>
-  <si>
-    <t>Montreal Impact</t>
-  </si>
-  <si>
     <t>Chicago Fire</t>
   </si>
   <si>
-    <t>Inter Miami</t>
-  </si>
-  <si>
-    <t>Tampa Bay Rowdies</t>
-  </si>
-  <si>
-    <t>New York City</t>
-  </si>
-  <si>
-    <t>Toronto II</t>
-  </si>
-  <si>
     <t>LA Galaxy II</t>
   </si>
   <si>
+    <t>Monterey Bay</t>
+  </si>
+  <si>
+    <t>São Paulo</t>
+  </si>
+  <si>
+    <t>Vancouver Whitecaps</t>
+  </si>
+  <si>
+    <t>Los Angeles FC</t>
+  </si>
+  <si>
     <t>Vitória</t>
   </si>
   <si>
-    <t>Monterey Bay</t>
-  </si>
-  <si>
     <t>Columbus Crew</t>
-  </si>
-  <si>
-    <t>Los Angeles FC</t>
-  </si>
-  <si>
-    <t>Vancouver Whitecaps</t>
-  </si>
-  <si>
-    <t>São Paulo</t>
   </si>
   <si>
     <t>Colorado Rapids</t>
@@ -986,43 +986,43 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L3">
-        <v>2.51</v>
+        <v>1.48</v>
       </c>
       <c r="M3">
-        <v>3.16</v>
+        <v>4.4</v>
       </c>
       <c r="N3">
-        <v>2.9</v>
+        <v>5.93</v>
       </c>
       <c r="O3">
-        <v>1.83</v>
+        <v>1.33</v>
       </c>
       <c r="P3">
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>2.3</v>
+        <v>3.6</v>
       </c>
       <c r="R3">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="S3">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="T3">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="U3">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="V3">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="W3">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X3">
         <v>0</v>
@@ -1037,10 +1037,10 @@
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>2.3</v>
+        <v>1.91</v>
       </c>
       <c r="AC3">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -1049,10 +1049,10 @@
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AG3">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -1102,43 +1102,43 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="L4">
-        <v>1.48</v>
+        <v>2.51</v>
       </c>
       <c r="M4">
-        <v>4.4</v>
+        <v>3.16</v>
       </c>
       <c r="N4">
-        <v>5.93</v>
+        <v>2.9</v>
       </c>
       <c r="O4">
-        <v>1.33</v>
+        <v>1.83</v>
       </c>
       <c r="P4">
         <v>0</v>
       </c>
       <c r="Q4">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="R4">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="S4">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="T4">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="U4">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="V4">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="W4">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X4">
         <v>0</v>
@@ -1153,10 +1153,10 @@
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>1.91</v>
+        <v>2.3</v>
       </c>
       <c r="AC4">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AD4">
         <v>0</v>
@@ -1165,10 +1165,10 @@
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AG4">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AH4">
         <v>0</v>
@@ -1801,64 +1801,64 @@
         <v>111</v>
       </c>
       <c r="L10">
-        <v>1.74</v>
+        <v>1.38</v>
       </c>
       <c r="M10">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="N10">
-        <v>3.87</v>
+        <v>6</v>
       </c>
       <c r="O10">
+        <v>1.44</v>
+      </c>
+      <c r="P10">
+        <v>12.5</v>
+      </c>
+      <c r="Q10">
+        <v>2.95</v>
+      </c>
+      <c r="R10">
+        <v>1.28</v>
+      </c>
+      <c r="S10">
+        <v>3.4</v>
+      </c>
+      <c r="T10">
+        <v>2.25</v>
+      </c>
+      <c r="U10">
+        <v>1.57</v>
+      </c>
+      <c r="V10">
+        <v>5</v>
+      </c>
+      <c r="W10">
+        <v>1.14</v>
+      </c>
+      <c r="X10">
+        <v>1.04</v>
+      </c>
+      <c r="Y10">
+        <v>10</v>
+      </c>
+      <c r="Z10">
+        <v>1.2</v>
+      </c>
+      <c r="AA10">
+        <v>4.33</v>
+      </c>
+      <c r="AB10">
         <v>1.6</v>
       </c>
-      <c r="P10">
-        <v>10.5</v>
-      </c>
-      <c r="Q10">
+      <c r="AC10">
+        <v>2.2</v>
+      </c>
+      <c r="AD10">
         <v>2.55</v>
       </c>
-      <c r="R10">
-        <v>1.33</v>
-      </c>
-      <c r="S10">
-        <v>3</v>
-      </c>
-      <c r="T10">
-        <v>2.5</v>
-      </c>
-      <c r="U10">
-        <v>1.46</v>
-      </c>
-      <c r="V10">
-        <v>6</v>
-      </c>
-      <c r="W10">
-        <v>1.11</v>
-      </c>
-      <c r="X10">
-        <v>1.05</v>
-      </c>
-      <c r="Y10">
-        <v>9.5</v>
-      </c>
-      <c r="Z10">
-        <v>1.25</v>
-      </c>
-      <c r="AA10">
-        <v>3.8</v>
-      </c>
-      <c r="AB10">
-        <v>1.75</v>
-      </c>
-      <c r="AC10">
-        <v>1.95</v>
-      </c>
-      <c r="AD10">
-        <v>2.95</v>
-      </c>
       <c r="AE10">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AF10">
         <v>1.7</v>
@@ -1867,10 +1867,10 @@
         <v>2</v>
       </c>
       <c r="AH10">
-        <v>5.5</v>
+        <v>4.33</v>
       </c>
       <c r="AI10">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AJ10" t="s">
         <v>113</v>
@@ -1890,7 +1890,7 @@
         <v>44</v>
       </c>
       <c r="C11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D11" t="s">
         <v>54</v>
@@ -1917,76 +1917,76 @@
         <v>111</v>
       </c>
       <c r="L11">
-        <v>1.61</v>
+        <v>2.55</v>
       </c>
       <c r="M11">
-        <v>3.81</v>
+        <v>3.32</v>
       </c>
       <c r="N11">
-        <v>4.2</v>
+        <v>2.5</v>
       </c>
       <c r="O11">
-        <v>1.53</v>
+        <v>1.95</v>
       </c>
       <c r="P11">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Q11">
-        <v>2.6</v>
+        <v>1.92</v>
       </c>
       <c r="R11">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="S11">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="T11">
-        <v>2.25</v>
+        <v>2.7</v>
       </c>
       <c r="U11">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="V11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W11">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="X11">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y11">
         <v>10</v>
       </c>
       <c r="Z11">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AA11">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="AB11">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="AC11">
-        <v>2.25</v>
+        <v>1.93</v>
       </c>
       <c r="AD11">
-        <v>2.55</v>
+        <v>3.1</v>
       </c>
       <c r="AE11">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AF11">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AG11">
         <v>2.15</v>
       </c>
       <c r="AH11">
-        <v>4.33</v>
+        <v>6</v>
       </c>
       <c r="AI11">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AJ11" t="s">
         <v>113</v>
@@ -2033,40 +2033,40 @@
         <v>111</v>
       </c>
       <c r="L12">
-        <v>1.38</v>
+        <v>1.73</v>
       </c>
       <c r="M12">
-        <v>4.3</v>
+        <v>3.55</v>
       </c>
       <c r="N12">
-        <v>6</v>
+        <v>3.83</v>
       </c>
       <c r="O12">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="P12">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Q12">
-        <v>2.95</v>
+        <v>2.65</v>
       </c>
       <c r="R12">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S12">
         <v>3.4</v>
       </c>
       <c r="T12">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="U12">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="V12">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="W12">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X12">
         <v>1.04</v>
@@ -2075,34 +2075,34 @@
         <v>10</v>
       </c>
       <c r="Z12">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AA12">
-        <v>4.33</v>
+        <v>4.75</v>
       </c>
       <c r="AB12">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AC12">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AD12">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="AE12">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AF12">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AG12">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AH12">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="AI12">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AJ12" t="s">
         <v>113</v>
@@ -2149,22 +2149,22 @@
         <v>111</v>
       </c>
       <c r="L13">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="M13">
-        <v>3.63</v>
+        <v>3.6</v>
       </c>
       <c r="N13">
-        <v>2.91</v>
+        <v>2.82</v>
       </c>
       <c r="O13">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="P13">
         <v>13</v>
       </c>
       <c r="Q13">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="R13">
         <v>1.27</v>
@@ -2176,10 +2176,10 @@
         <v>2.2</v>
       </c>
       <c r="U13">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="V13">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="W13">
         <v>1.15</v>
@@ -2197,22 +2197,22 @@
         <v>4.75</v>
       </c>
       <c r="AB13">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="AC13">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="AD13">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AE13">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AF13">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="AG13">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AH13">
         <v>4.2</v>
@@ -2238,7 +2238,7 @@
         <v>44</v>
       </c>
       <c r="C14" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D14" t="s">
         <v>54</v>
@@ -2265,76 +2265,76 @@
         <v>111</v>
       </c>
       <c r="L14">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="M14">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N14">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="O14">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="P14">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Q14">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="R14">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="S14">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T14">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U14">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="V14">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="W14">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X14">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y14">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z14">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AA14">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AB14">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC14">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD14">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE14">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF14">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AG14">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AH14">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AI14">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="s">
         <v>113</v>
@@ -2354,7 +2354,7 @@
         <v>44</v>
       </c>
       <c r="C15" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D15" t="s">
         <v>54</v>
@@ -2381,76 +2381,76 @@
         <v>111</v>
       </c>
       <c r="L15">
-        <v>2.55</v>
+        <v>1.61</v>
       </c>
       <c r="M15">
-        <v>3.32</v>
+        <v>3.81</v>
       </c>
       <c r="N15">
-        <v>2.5</v>
+        <v>4.2</v>
       </c>
       <c r="O15">
-        <v>1.95</v>
+        <v>1.53</v>
       </c>
       <c r="P15">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Q15">
-        <v>1.92</v>
+        <v>2.6</v>
       </c>
       <c r="R15">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="S15">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="T15">
-        <v>2.7</v>
+        <v>2.25</v>
       </c>
       <c r="U15">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="V15">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W15">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="X15">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y15">
         <v>10</v>
       </c>
       <c r="Z15">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AA15">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="AB15">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AC15">
-        <v>1.93</v>
+        <v>2.25</v>
       </c>
       <c r="AD15">
-        <v>3.1</v>
+        <v>2.55</v>
       </c>
       <c r="AE15">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AF15">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AG15">
         <v>2.15</v>
       </c>
       <c r="AH15">
-        <v>6</v>
+        <v>4.33</v>
       </c>
       <c r="AI15">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AJ15" t="s">
         <v>113</v>
@@ -2497,76 +2497,76 @@
         <v>111</v>
       </c>
       <c r="L16">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="M16">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="N16">
-        <v>3.83</v>
+        <v>3.87</v>
       </c>
       <c r="O16">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="P16">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="Q16">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="R16">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="S16">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="T16">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="U16">
-        <v>1.6</v>
+        <v>1.46</v>
       </c>
       <c r="V16">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="W16">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X16">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y16">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="Z16">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AA16">
-        <v>4.75</v>
+        <v>3.8</v>
       </c>
       <c r="AB16">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AC16">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AD16">
-        <v>2.4</v>
+        <v>2.95</v>
       </c>
       <c r="AE16">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AF16">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AG16">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AH16">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="AI16">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AJ16" t="s">
         <v>113</v>
@@ -2586,7 +2586,7 @@
         <v>44</v>
       </c>
       <c r="C17" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D17" t="s">
         <v>54</v>
@@ -2613,76 +2613,76 @@
         <v>111</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M17">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH17">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AI17">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AJ17" t="s">
         <v>113</v>
@@ -2818,7 +2818,7 @@
         <v>46</v>
       </c>
       <c r="C19" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D19" t="s">
         <v>54</v>
@@ -2845,76 +2845,76 @@
         <v>111</v>
       </c>
       <c r="L19">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="M19">
-        <v>4.12</v>
+        <v>3.75</v>
       </c>
       <c r="N19">
-        <v>6.72</v>
+        <v>5.3</v>
       </c>
       <c r="O19">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P19">
-        <v>8.25</v>
+        <v>11.75</v>
       </c>
       <c r="Q19">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="R19">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="S19">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="T19">
-        <v>2.91</v>
+        <v>2.63</v>
       </c>
       <c r="U19">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="V19">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="W19">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X19">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y19">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="Z19">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AA19">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="AB19">
-        <v>2.05</v>
+        <v>1.89</v>
       </c>
       <c r="AC19">
-        <v>1.7</v>
+        <v>1.87</v>
       </c>
       <c r="AD19">
-        <v>3.55</v>
+        <v>3.14</v>
       </c>
       <c r="AE19">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AF19">
-        <v>2.19</v>
+        <v>1.91</v>
       </c>
       <c r="AG19">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AH19">
-        <v>6.75</v>
+        <v>6</v>
       </c>
       <c r="AI19">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AJ19" t="s">
         <v>113</v>
@@ -2934,7 +2934,7 @@
         <v>46</v>
       </c>
       <c r="C20" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D20" t="s">
         <v>54</v>
@@ -2961,76 +2961,76 @@
         <v>111</v>
       </c>
       <c r="L20">
-        <v>1.5</v>
+        <v>2.29</v>
       </c>
       <c r="M20">
-        <v>3.75</v>
+        <v>3.24</v>
       </c>
       <c r="N20">
-        <v>5.3</v>
+        <v>3.3</v>
       </c>
       <c r="O20">
-        <v>1.41</v>
+        <v>1.73</v>
       </c>
       <c r="P20">
-        <v>11.75</v>
+        <v>7</v>
       </c>
       <c r="Q20">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="R20">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="S20">
-        <v>3.1</v>
+        <v>2.48</v>
       </c>
       <c r="T20">
+        <v>3.3</v>
+      </c>
+      <c r="U20">
+        <v>1.29</v>
+      </c>
+      <c r="V20">
+        <v>8</v>
+      </c>
+      <c r="W20">
+        <v>1.05</v>
+      </c>
+      <c r="X20">
+        <v>1.03</v>
+      </c>
+      <c r="Y20">
+        <v>7.7</v>
+      </c>
+      <c r="Z20">
+        <v>1.4</v>
+      </c>
+      <c r="AA20">
         <v>2.63</v>
       </c>
-      <c r="U20">
-        <v>1.44</v>
-      </c>
-      <c r="V20">
-        <v>6.5</v>
-      </c>
-      <c r="W20">
-        <v>1.1</v>
-      </c>
-      <c r="X20">
-        <v>1.05</v>
-      </c>
-      <c r="Y20">
-        <v>10</v>
-      </c>
-      <c r="Z20">
-        <v>1.29</v>
-      </c>
-      <c r="AA20">
-        <v>3.3</v>
-      </c>
       <c r="AB20">
-        <v>1.89</v>
+        <v>2.3</v>
       </c>
       <c r="AC20">
-        <v>1.87</v>
+        <v>1.58</v>
       </c>
       <c r="AD20">
-        <v>3.14</v>
+        <v>4.45</v>
       </c>
       <c r="AE20">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="AF20">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="AG20">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="AH20">
-        <v>6</v>
+        <v>9.5</v>
       </c>
       <c r="AI20">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AJ20" t="s">
         <v>113</v>
@@ -3077,76 +3077,76 @@
         <v>111</v>
       </c>
       <c r="L21">
-        <v>1.98</v>
+        <v>2.16</v>
       </c>
       <c r="M21">
-        <v>3.39</v>
+        <v>3.21</v>
       </c>
       <c r="N21">
-        <v>3.12</v>
+        <v>2.9</v>
       </c>
       <c r="O21">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="P21">
-        <v>11.5</v>
+        <v>9.5</v>
       </c>
       <c r="Q21">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="R21">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="S21">
-        <v>3.2</v>
+        <v>2.87</v>
       </c>
       <c r="T21">
-        <v>2.35</v>
+        <v>2.6</v>
       </c>
       <c r="U21">
-        <v>1.52</v>
+        <v>1.43</v>
       </c>
       <c r="V21">
+        <v>6.5</v>
+      </c>
+      <c r="W21">
+        <v>1.1</v>
+      </c>
+      <c r="X21">
+        <v>1.05</v>
+      </c>
+      <c r="Y21">
+        <v>9.5</v>
+      </c>
+      <c r="Z21">
+        <v>1.27</v>
+      </c>
+      <c r="AA21">
+        <v>3.4</v>
+      </c>
+      <c r="AB21">
+        <v>1.82</v>
+      </c>
+      <c r="AC21">
+        <v>1.88</v>
+      </c>
+      <c r="AD21">
+        <v>1.02</v>
+      </c>
+      <c r="AE21">
+        <v>1.02</v>
+      </c>
+      <c r="AF21">
+        <v>1.68</v>
+      </c>
+      <c r="AG21">
+        <v>2.05</v>
+      </c>
+      <c r="AH21">
         <v>5.5</v>
       </c>
-      <c r="W21">
-        <v>1.13</v>
-      </c>
-      <c r="X21">
-        <v>1.03</v>
-      </c>
-      <c r="Y21">
-        <v>11.5</v>
-      </c>
-      <c r="Z21">
-        <v>1.2</v>
-      </c>
-      <c r="AA21">
-        <v>4.1</v>
-      </c>
-      <c r="AB21">
-        <v>1.61</v>
-      </c>
-      <c r="AC21">
-        <v>2.15</v>
-      </c>
-      <c r="AD21">
-        <v>2.55</v>
-      </c>
-      <c r="AE21">
-        <v>1.46</v>
-      </c>
-      <c r="AF21">
-        <v>1.57</v>
-      </c>
-      <c r="AG21">
-        <v>2.2</v>
-      </c>
-      <c r="AH21">
-        <v>4.5</v>
-      </c>
       <c r="AI21">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AJ21" t="s">
         <v>113</v>
@@ -3282,7 +3282,7 @@
         <v>46</v>
       </c>
       <c r="C23" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D23" t="s">
         <v>54</v>
@@ -3309,76 +3309,76 @@
         <v>111</v>
       </c>
       <c r="L23">
-        <v>2.16</v>
+        <v>1.53</v>
       </c>
       <c r="M23">
-        <v>3.21</v>
+        <v>4.12</v>
       </c>
       <c r="N23">
-        <v>2.9</v>
+        <v>6.72</v>
       </c>
       <c r="O23">
-        <v>1.82</v>
+        <v>1.4</v>
       </c>
       <c r="P23">
-        <v>9.5</v>
+        <v>8.25</v>
       </c>
       <c r="Q23">
-        <v>2.15</v>
+        <v>3.5</v>
       </c>
       <c r="R23">
+        <v>1.4</v>
+      </c>
+      <c r="S23">
+        <v>2.88</v>
+      </c>
+      <c r="T23">
+        <v>2.91</v>
+      </c>
+      <c r="U23">
+        <v>1.33</v>
+      </c>
+      <c r="V23">
+        <v>7</v>
+      </c>
+      <c r="W23">
+        <v>1.08</v>
+      </c>
+      <c r="X23">
+        <v>1.02</v>
+      </c>
+      <c r="Y23">
+        <v>8.5</v>
+      </c>
+      <c r="Z23">
         <v>1.36</v>
       </c>
-      <c r="S23">
-        <v>2.87</v>
-      </c>
-      <c r="T23">
-        <v>2.6</v>
-      </c>
-      <c r="U23">
-        <v>1.43</v>
-      </c>
-      <c r="V23">
-        <v>6.5</v>
-      </c>
-      <c r="W23">
-        <v>1.1</v>
-      </c>
-      <c r="X23">
-        <v>1.05</v>
-      </c>
-      <c r="Y23">
-        <v>9.5</v>
-      </c>
-      <c r="Z23">
-        <v>1.27</v>
-      </c>
       <c r="AA23">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="AB23">
-        <v>1.82</v>
+        <v>2.05</v>
       </c>
       <c r="AC23">
-        <v>1.88</v>
+        <v>1.7</v>
       </c>
       <c r="AD23">
-        <v>1.02</v>
+        <v>3.55</v>
       </c>
       <c r="AE23">
-        <v>1.02</v>
+        <v>1.23</v>
       </c>
       <c r="AF23">
-        <v>1.68</v>
+        <v>2.19</v>
       </c>
       <c r="AG23">
-        <v>2.05</v>
+        <v>1.6</v>
       </c>
       <c r="AH23">
-        <v>5.5</v>
+        <v>6.75</v>
       </c>
       <c r="AI23">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AJ23" t="s">
         <v>113</v>
@@ -3398,7 +3398,7 @@
         <v>46</v>
       </c>
       <c r="C24" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D24" t="s">
         <v>54</v>
@@ -3425,76 +3425,76 @@
         <v>111</v>
       </c>
       <c r="L24">
-        <v>2.29</v>
+        <v>1.98</v>
       </c>
       <c r="M24">
-        <v>3.24</v>
+        <v>3.39</v>
       </c>
       <c r="N24">
-        <v>3.3</v>
+        <v>3.12</v>
       </c>
       <c r="O24">
         <v>1.73</v>
       </c>
       <c r="P24">
-        <v>7</v>
+        <v>11.5</v>
       </c>
       <c r="Q24">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="R24">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="S24">
-        <v>2.48</v>
+        <v>3.2</v>
       </c>
       <c r="T24">
-        <v>3.3</v>
+        <v>2.35</v>
       </c>
       <c r="U24">
-        <v>1.29</v>
+        <v>1.52</v>
       </c>
       <c r="V24">
-        <v>8</v>
+        <v>5.5</v>
       </c>
       <c r="W24">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="X24">
         <v>1.03</v>
       </c>
       <c r="Y24">
-        <v>7.7</v>
+        <v>11.5</v>
       </c>
       <c r="Z24">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="AA24">
-        <v>2.63</v>
+        <v>4.1</v>
       </c>
       <c r="AB24">
-        <v>2.3</v>
+        <v>1.61</v>
       </c>
       <c r="AC24">
-        <v>1.58</v>
+        <v>2.15</v>
       </c>
       <c r="AD24">
-        <v>4.45</v>
+        <v>2.55</v>
       </c>
       <c r="AE24">
-        <v>1.16</v>
+        <v>1.46</v>
       </c>
       <c r="AF24">
-        <v>1.98</v>
+        <v>1.57</v>
       </c>
       <c r="AG24">
-        <v>1.74</v>
+        <v>2.2</v>
       </c>
       <c r="AH24">
-        <v>9.5</v>
+        <v>4.5</v>
       </c>
       <c r="AI24">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AJ24" t="s">
         <v>113</v>

--- a/jogos_2025-07-16.xlsx
+++ b/jogos_2025-07-16.xlsx
@@ -205,63 +205,63 @@
     <t>Santos</t>
   </si>
   <si>
+    <t>Orlando City</t>
+  </si>
+  <si>
+    <t>Atlanta United FC</t>
+  </si>
+  <si>
+    <t>New York RB</t>
+  </si>
+  <si>
     <t>Philadelphia Union</t>
   </si>
   <si>
+    <t>FC Cincinnati</t>
+  </si>
+  <si>
+    <t>Charlotte</t>
+  </si>
+  <si>
     <t>Hartford Athletic</t>
   </si>
   <si>
-    <t>Orlando City</t>
-  </si>
-  <si>
-    <t>FC Cincinnati</t>
-  </si>
-  <si>
     <t>New York City II</t>
   </si>
   <si>
-    <t>Charlotte</t>
-  </si>
-  <si>
-    <t>New York RB</t>
-  </si>
-  <si>
-    <t>Atlanta United FC</t>
-  </si>
-  <si>
     <t>St. Louis City II</t>
   </si>
   <si>
+    <t>Minnesota United</t>
+  </si>
+  <si>
+    <t>Houston Dynamo</t>
+  </si>
+  <si>
+    <t>Bragantino</t>
+  </si>
+  <si>
+    <t>Nashville SC</t>
+  </si>
+  <si>
     <t>Tulsa Roughnecks</t>
   </si>
   <si>
-    <t>Bragantino</t>
-  </si>
-  <si>
-    <t>Houston Dynamo</t>
-  </si>
-  <si>
-    <t>Minnesota United</t>
-  </si>
-  <si>
     <t>Botafogo</t>
   </si>
   <si>
-    <t>Nashville SC</t>
-  </si>
-  <si>
     <t>Seattle Sounders</t>
   </si>
   <si>
+    <t>San Diego</t>
+  </si>
+  <si>
+    <t>SJ Earthquakes</t>
+  </si>
+  <si>
     <t>Portland Timbers</t>
   </si>
   <si>
-    <t>SJ Earthquakes</t>
-  </si>
-  <si>
-    <t>San Diego</t>
-  </si>
-  <si>
     <t>LA Galaxy</t>
   </si>
   <si>
@@ -289,61 +289,61 @@
     <t>Flamengo</t>
   </si>
   <si>
+    <t>New York City</t>
+  </si>
+  <si>
+    <t>Chicago Fire</t>
+  </si>
+  <si>
+    <t>New England Revolution</t>
+  </si>
+  <si>
     <t>Montreal Impact</t>
   </si>
   <si>
+    <t>Inter Miami</t>
+  </si>
+  <si>
+    <t>DC United</t>
+  </si>
+  <si>
     <t>Tampa Bay Rowdies</t>
   </si>
   <si>
-    <t>New York City</t>
-  </si>
-  <si>
-    <t>Inter Miami</t>
-  </si>
-  <si>
     <t>Toronto II</t>
   </si>
   <si>
-    <t>DC United</t>
-  </si>
-  <si>
-    <t>New England Revolution</t>
-  </si>
-  <si>
-    <t>Chicago Fire</t>
-  </si>
-  <si>
     <t>LA Galaxy II</t>
   </si>
   <si>
+    <t>Los Angeles FC</t>
+  </si>
+  <si>
+    <t>Vancouver Whitecaps</t>
+  </si>
+  <si>
+    <t>São Paulo</t>
+  </si>
+  <si>
+    <t>Columbus Crew</t>
+  </si>
+  <si>
     <t>Monterey Bay</t>
   </si>
   <si>
-    <t>São Paulo</t>
-  </si>
-  <si>
-    <t>Vancouver Whitecaps</t>
-  </si>
-  <si>
-    <t>Los Angeles FC</t>
-  </si>
-  <si>
     <t>Vitória</t>
   </si>
   <si>
-    <t>Columbus Crew</t>
-  </si>
-  <si>
     <t>Colorado Rapids</t>
   </si>
   <si>
+    <t>Toronto</t>
+  </si>
+  <si>
+    <t>FC Dallas</t>
+  </si>
+  <si>
     <t>Real Salt Lake</t>
-  </si>
-  <si>
-    <t>FC Dallas</t>
-  </si>
-  <si>
-    <t>Toronto</t>
   </si>
   <si>
     <t>Austin</t>
@@ -986,16 +986,16 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="L3">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="M3">
         <v>4.4</v>
       </c>
       <c r="N3">
-        <v>5.93</v>
+        <v>6.25</v>
       </c>
       <c r="O3">
         <v>1.33</v>
@@ -1037,10 +1037,10 @@
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AC3">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -1105,13 +1105,13 @@
         <v>111</v>
       </c>
       <c r="L4">
-        <v>2.51</v>
+        <v>2.55</v>
       </c>
       <c r="M4">
-        <v>3.16</v>
+        <v>3.2</v>
       </c>
       <c r="N4">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="O4">
         <v>1.83</v>
@@ -1153,7 +1153,7 @@
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AC4">
         <v>1.57</v>
@@ -1221,10 +1221,10 @@
         <v>112</v>
       </c>
       <c r="L5">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="M5">
-        <v>3.25</v>
+        <v>3.11</v>
       </c>
       <c r="N5">
         <v>2.95</v>
@@ -1456,10 +1456,10 @@
         <v>1.44</v>
       </c>
       <c r="M7">
-        <v>4.34</v>
+        <v>4.33</v>
       </c>
       <c r="N7">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="O7">
         <v>1.29</v>
@@ -1471,49 +1471,49 @@
         <v>4.33</v>
       </c>
       <c r="R7">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="S7">
         <v>2.7</v>
       </c>
       <c r="T7">
-        <v>3.17</v>
+        <v>2.9</v>
       </c>
       <c r="U7">
         <v>1.36</v>
       </c>
       <c r="V7">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="W7">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X7">
         <v>1.04</v>
       </c>
       <c r="Y7">
-        <v>9.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="Z7">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AA7">
         <v>3</v>
       </c>
       <c r="AB7">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AC7">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AD7">
-        <v>3.6</v>
+        <v>3.81</v>
       </c>
       <c r="AE7">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AF7">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="AG7">
         <v>1.6</v>
@@ -1569,13 +1569,13 @@
         <v>111</v>
       </c>
       <c r="L8">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="M8">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="N8">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="O8">
         <v>1.91</v>
@@ -1587,58 +1587,58 @@
         <v>2.2</v>
       </c>
       <c r="R8">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="S8">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="T8">
-        <v>3.14</v>
+        <v>3.4</v>
       </c>
       <c r="U8">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="V8">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="W8">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X8">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Y8">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="Z8">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AA8">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="AB8">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="AC8">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="AD8">
-        <v>4</v>
+        <v>5.11</v>
       </c>
       <c r="AE8">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="AF8">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AG8">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AH8">
-        <v>7.8</v>
+        <v>9.75</v>
       </c>
       <c r="AI8">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AJ8" t="s">
         <v>113</v>
@@ -1685,13 +1685,13 @@
         <v>111</v>
       </c>
       <c r="L9">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="M9">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="N9">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="O9">
         <v>2.63</v>
@@ -1703,58 +1703,58 @@
         <v>1.57</v>
       </c>
       <c r="R9">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="S9">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="T9">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="U9">
+        <v>1.3</v>
+      </c>
+      <c r="V9">
+        <v>7</v>
+      </c>
+      <c r="W9">
+        <v>1.02</v>
+      </c>
+      <c r="X9">
+        <v>1.08</v>
+      </c>
+      <c r="Y9">
+        <v>8</v>
+      </c>
+      <c r="Z9">
         <v>1.38</v>
-      </c>
-      <c r="V9">
-        <v>8.1</v>
-      </c>
-      <c r="W9">
-        <v>1.06</v>
-      </c>
-      <c r="X9">
-        <v>1.06</v>
-      </c>
-      <c r="Y9">
-        <v>7.6</v>
-      </c>
-      <c r="Z9">
-        <v>1.36</v>
       </c>
       <c r="AA9">
         <v>2.8</v>
       </c>
       <c r="AB9">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="AC9">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AD9">
-        <v>4.05</v>
+        <v>3.8</v>
       </c>
       <c r="AE9">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF9">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="AG9">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AH9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI9">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AJ9" t="s">
         <v>113</v>
@@ -1801,40 +1801,40 @@
         <v>111</v>
       </c>
       <c r="L10">
-        <v>1.38</v>
+        <v>1.73</v>
       </c>
       <c r="M10">
-        <v>4.3</v>
+        <v>3.55</v>
       </c>
       <c r="N10">
-        <v>6</v>
+        <v>3.83</v>
       </c>
       <c r="O10">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="P10">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Q10">
-        <v>2.95</v>
+        <v>2.65</v>
       </c>
       <c r="R10">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S10">
         <v>3.4</v>
       </c>
       <c r="T10">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="U10">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="V10">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="W10">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X10">
         <v>1.04</v>
@@ -1843,34 +1843,34 @@
         <v>10</v>
       </c>
       <c r="Z10">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AA10">
-        <v>4.33</v>
+        <v>4.75</v>
       </c>
       <c r="AB10">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AC10">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AD10">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="AE10">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AF10">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AG10">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AH10">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="AI10">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AJ10" t="s">
         <v>113</v>
@@ -1890,7 +1890,7 @@
         <v>44</v>
       </c>
       <c r="C11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D11" t="s">
         <v>54</v>
@@ -1917,76 +1917,76 @@
         <v>111</v>
       </c>
       <c r="L11">
-        <v>2.55</v>
+        <v>2</v>
       </c>
       <c r="M11">
-        <v>3.32</v>
+        <v>3.63</v>
       </c>
       <c r="N11">
-        <v>2.5</v>
+        <v>2.91</v>
       </c>
       <c r="O11">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="P11">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Q11">
-        <v>1.92</v>
+        <v>2.15</v>
       </c>
       <c r="R11">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="S11">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="T11">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="U11">
-        <v>1.4</v>
+        <v>1.58</v>
       </c>
       <c r="V11">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W11">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="X11">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y11">
         <v>10</v>
       </c>
       <c r="Z11">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AA11">
-        <v>3.6</v>
+        <v>4.75</v>
       </c>
       <c r="AB11">
-        <v>1.85</v>
+        <v>1.59</v>
       </c>
       <c r="AC11">
-        <v>1.93</v>
+        <v>2.36</v>
       </c>
       <c r="AD11">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="AE11">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AF11">
-        <v>1.67</v>
+        <v>1.49</v>
       </c>
       <c r="AG11">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="AH11">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="AI11">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AJ11" t="s">
         <v>113</v>
@@ -2033,76 +2033,76 @@
         <v>111</v>
       </c>
       <c r="L12">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="M12">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="N12">
-        <v>3.83</v>
+        <v>3.87</v>
       </c>
       <c r="O12">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="P12">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="Q12">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="R12">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="S12">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="T12">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="U12">
-        <v>1.6</v>
+        <v>1.46</v>
       </c>
       <c r="V12">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="W12">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X12">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y12">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="Z12">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AA12">
-        <v>4.75</v>
+        <v>3.8</v>
       </c>
       <c r="AB12">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AC12">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AD12">
-        <v>2.4</v>
+        <v>2.95</v>
       </c>
       <c r="AE12">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AF12">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AG12">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AH12">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="AI12">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AJ12" t="s">
         <v>113</v>
@@ -2149,40 +2149,40 @@
         <v>111</v>
       </c>
       <c r="L13">
-        <v>2.06</v>
+        <v>1.38</v>
       </c>
       <c r="M13">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="N13">
-        <v>2.82</v>
+        <v>6</v>
       </c>
       <c r="O13">
-        <v>1.82</v>
+        <v>1.44</v>
       </c>
       <c r="P13">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Q13">
-        <v>2.05</v>
+        <v>2.95</v>
       </c>
       <c r="R13">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S13">
         <v>3.4</v>
       </c>
       <c r="T13">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="U13">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="V13">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="W13">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X13">
         <v>1.04</v>
@@ -2191,34 +2191,34 @@
         <v>10</v>
       </c>
       <c r="Z13">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AA13">
-        <v>4.75</v>
+        <v>4.33</v>
       </c>
       <c r="AB13">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AC13">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AD13">
-        <v>2.1</v>
+        <v>2.55</v>
       </c>
       <c r="AE13">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AF13">
-        <v>1.47</v>
+        <v>1.7</v>
       </c>
       <c r="AG13">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="AH13">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AI13">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AJ13" t="s">
         <v>113</v>
@@ -2238,7 +2238,7 @@
         <v>44</v>
       </c>
       <c r="C14" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D14" t="s">
         <v>54</v>
@@ -2265,76 +2265,76 @@
         <v>111</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="M14">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH14">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AI14">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AJ14" t="s">
         <v>113</v>
@@ -2435,10 +2435,10 @@
         <v>2.25</v>
       </c>
       <c r="AD15">
-        <v>2.55</v>
+        <v>2.48</v>
       </c>
       <c r="AE15">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AF15">
         <v>1.61</v>
@@ -2470,7 +2470,7 @@
         <v>44</v>
       </c>
       <c r="C16" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D16" t="s">
         <v>54</v>
@@ -2497,22 +2497,22 @@
         <v>111</v>
       </c>
       <c r="L16">
-        <v>1.74</v>
+        <v>2.55</v>
       </c>
       <c r="M16">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="N16">
-        <v>3.87</v>
+        <v>2.49</v>
       </c>
       <c r="O16">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="P16">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="Q16">
-        <v>2.55</v>
+        <v>1.92</v>
       </c>
       <c r="R16">
         <v>1.33</v>
@@ -2521,52 +2521,52 @@
         <v>3</v>
       </c>
       <c r="T16">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="U16">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="V16">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="W16">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X16">
         <v>1.05</v>
       </c>
       <c r="Y16">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="Z16">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AA16">
-        <v>3.8</v>
+        <v>3.58</v>
       </c>
       <c r="AB16">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AC16">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AD16">
         <v>2.95</v>
       </c>
       <c r="AE16">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="AF16">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG16">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AH16">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="AI16">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="AJ16" t="s">
         <v>113</v>
@@ -2586,7 +2586,7 @@
         <v>44</v>
       </c>
       <c r="C17" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D17" t="s">
         <v>54</v>
@@ -2613,76 +2613,76 @@
         <v>111</v>
       </c>
       <c r="L17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M17">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="N17">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="O17">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="P17">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Q17">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="R17">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="S17">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T17">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U17">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="V17">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W17">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X17">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y17">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z17">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AA17">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AB17">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AC17">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AD17">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE17">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF17">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AG17">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AH17">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AI17">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="s">
         <v>113</v>
@@ -2818,7 +2818,7 @@
         <v>46</v>
       </c>
       <c r="C19" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D19" t="s">
         <v>54</v>
@@ -2845,76 +2845,76 @@
         <v>111</v>
       </c>
       <c r="L19">
-        <v>1.5</v>
+        <v>2.53</v>
       </c>
       <c r="M19">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="N19">
-        <v>5.3</v>
+        <v>2.37</v>
       </c>
       <c r="O19">
-        <v>1.41</v>
+        <v>2</v>
       </c>
       <c r="P19">
-        <v>11.75</v>
+        <v>10</v>
       </c>
       <c r="Q19">
-        <v>3.1</v>
+        <v>1.93</v>
       </c>
       <c r="R19">
         <v>1.33</v>
       </c>
       <c r="S19">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="T19">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="U19">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="V19">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="W19">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X19">
         <v>1.05</v>
       </c>
       <c r="Y19">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="Z19">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AA19">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="AB19">
-        <v>1.89</v>
+        <v>1.75</v>
       </c>
       <c r="AC19">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AD19">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="AE19">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AF19">
-        <v>1.91</v>
+        <v>1.63</v>
       </c>
       <c r="AG19">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AH19">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="AI19">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AJ19" t="s">
         <v>113</v>
@@ -2934,7 +2934,7 @@
         <v>46</v>
       </c>
       <c r="C20" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D20" t="s">
         <v>54</v>
@@ -2961,76 +2961,76 @@
         <v>111</v>
       </c>
       <c r="L20">
-        <v>2.29</v>
+        <v>2.16</v>
       </c>
       <c r="M20">
-        <v>3.24</v>
+        <v>3.21</v>
       </c>
       <c r="N20">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="O20">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="P20">
-        <v>7</v>
+        <v>9.5</v>
       </c>
       <c r="Q20">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="R20">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="S20">
-        <v>2.48</v>
+        <v>2.87</v>
       </c>
       <c r="T20">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="U20">
-        <v>1.29</v>
+        <v>1.43</v>
       </c>
       <c r="V20">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="W20">
+        <v>1.1</v>
+      </c>
+      <c r="X20">
         <v>1.05</v>
       </c>
-      <c r="X20">
-        <v>1.03</v>
-      </c>
       <c r="Y20">
-        <v>7.7</v>
+        <v>9.5</v>
       </c>
       <c r="Z20">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AA20">
-        <v>2.63</v>
+        <v>3.4</v>
       </c>
       <c r="AB20">
-        <v>2.3</v>
+        <v>1.82</v>
       </c>
       <c r="AC20">
-        <v>1.58</v>
+        <v>1.88</v>
       </c>
       <c r="AD20">
-        <v>4.45</v>
+        <v>1.02</v>
       </c>
       <c r="AE20">
-        <v>1.16</v>
+        <v>1.02</v>
       </c>
       <c r="AF20">
-        <v>1.98</v>
+        <v>1.68</v>
       </c>
       <c r="AG20">
-        <v>1.74</v>
+        <v>2.05</v>
       </c>
       <c r="AH20">
-        <v>9.5</v>
+        <v>5.5</v>
       </c>
       <c r="AI20">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AJ20" t="s">
         <v>113</v>
@@ -3050,7 +3050,7 @@
         <v>46</v>
       </c>
       <c r="C21" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D21" t="s">
         <v>54</v>
@@ -3077,76 +3077,76 @@
         <v>111</v>
       </c>
       <c r="L21">
-        <v>2.16</v>
+        <v>2.04</v>
       </c>
       <c r="M21">
-        <v>3.21</v>
+        <v>3.15</v>
       </c>
       <c r="N21">
-        <v>2.9</v>
+        <v>3.55</v>
       </c>
       <c r="O21">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="P21">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="Q21">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="R21">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="S21">
-        <v>2.87</v>
+        <v>2.5</v>
       </c>
       <c r="T21">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="U21">
-        <v>1.43</v>
+        <v>1.26</v>
       </c>
       <c r="V21">
-        <v>6.5</v>
+        <v>8.5</v>
       </c>
       <c r="W21">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X21">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y21">
-        <v>9.5</v>
+        <v>8</v>
       </c>
       <c r="Z21">
-        <v>1.27</v>
+        <v>1.47</v>
       </c>
       <c r="AA21">
-        <v>3.4</v>
+        <v>2.56</v>
       </c>
       <c r="AB21">
-        <v>1.82</v>
+        <v>2.4</v>
       </c>
       <c r="AC21">
-        <v>1.88</v>
+        <v>1.53</v>
       </c>
       <c r="AD21">
-        <v>1.02</v>
+        <v>4.7</v>
       </c>
       <c r="AE21">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="AF21">
-        <v>1.68</v>
+        <v>2.06</v>
       </c>
       <c r="AG21">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="AH21">
-        <v>5.5</v>
+        <v>9</v>
       </c>
       <c r="AI21">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="AJ21" t="s">
         <v>113</v>
@@ -3193,76 +3193,76 @@
         <v>111</v>
       </c>
       <c r="L22">
-        <v>2.53</v>
+        <v>1.98</v>
       </c>
       <c r="M22">
-        <v>3.3</v>
+        <v>3.39</v>
       </c>
       <c r="N22">
-        <v>2.37</v>
+        <v>3.12</v>
       </c>
       <c r="O22">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="P22">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="Q22">
-        <v>1.93</v>
+        <v>2.25</v>
       </c>
       <c r="R22">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S22">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="T22">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="U22">
+        <v>1.52</v>
+      </c>
+      <c r="V22">
+        <v>5.5</v>
+      </c>
+      <c r="W22">
+        <v>1.13</v>
+      </c>
+      <c r="X22">
+        <v>1.03</v>
+      </c>
+      <c r="Y22">
+        <v>11.5</v>
+      </c>
+      <c r="Z22">
+        <v>1.2</v>
+      </c>
+      <c r="AA22">
+        <v>4.1</v>
+      </c>
+      <c r="AB22">
+        <v>1.61</v>
+      </c>
+      <c r="AC22">
+        <v>2.15</v>
+      </c>
+      <c r="AD22">
+        <v>2.7</v>
+      </c>
+      <c r="AE22">
         <v>1.46</v>
       </c>
-      <c r="V22">
-        <v>6</v>
-      </c>
-      <c r="W22">
-        <v>1.11</v>
-      </c>
-      <c r="X22">
-        <v>1.05</v>
-      </c>
-      <c r="Y22">
-        <v>9.5</v>
-      </c>
-      <c r="Z22">
-        <v>1.25</v>
-      </c>
-      <c r="AA22">
-        <v>3.75</v>
-      </c>
-      <c r="AB22">
-        <v>1.75</v>
-      </c>
-      <c r="AC22">
-        <v>1.95</v>
-      </c>
-      <c r="AD22">
-        <v>3</v>
-      </c>
-      <c r="AE22">
-        <v>1.38</v>
-      </c>
       <c r="AF22">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="AG22">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AH22">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="AI22">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AJ22" t="s">
         <v>113</v>
@@ -3282,7 +3282,7 @@
         <v>46</v>
       </c>
       <c r="C23" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D23" t="s">
         <v>54</v>
@@ -3309,76 +3309,76 @@
         <v>111</v>
       </c>
       <c r="L23">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="M23">
-        <v>4.12</v>
+        <v>4.1</v>
       </c>
       <c r="N23">
-        <v>6.72</v>
+        <v>5.6</v>
       </c>
       <c r="O23">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P23">
-        <v>8.25</v>
+        <v>11.75</v>
       </c>
       <c r="Q23">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="R23">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="S23">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="T23">
-        <v>2.91</v>
+        <v>2.75</v>
       </c>
       <c r="U23">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="V23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W23">
         <v>1.08</v>
       </c>
       <c r="X23">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="Z23">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AA23">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="AB23">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="AC23">
-        <v>1.7</v>
+        <v>1.84</v>
       </c>
       <c r="AD23">
-        <v>3.55</v>
+        <v>3.14</v>
       </c>
       <c r="AE23">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AF23">
-        <v>2.19</v>
+        <v>1.87</v>
       </c>
       <c r="AG23">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AH23">
-        <v>6.75</v>
+        <v>5.3</v>
       </c>
       <c r="AI23">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AJ23" t="s">
         <v>113</v>
@@ -3398,7 +3398,7 @@
         <v>46</v>
       </c>
       <c r="C24" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D24" t="s">
         <v>54</v>
@@ -3425,76 +3425,76 @@
         <v>111</v>
       </c>
       <c r="L24">
-        <v>1.98</v>
+        <v>1.48</v>
       </c>
       <c r="M24">
-        <v>3.39</v>
+        <v>4.12</v>
       </c>
       <c r="N24">
-        <v>3.12</v>
+        <v>6.72</v>
       </c>
       <c r="O24">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="P24">
-        <v>11.5</v>
+        <v>8.25</v>
       </c>
       <c r="Q24">
-        <v>2.25</v>
+        <v>3.5</v>
       </c>
       <c r="R24">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="S24">
-        <v>3.2</v>
+        <v>2.62</v>
       </c>
       <c r="T24">
-        <v>2.35</v>
+        <v>2.9</v>
       </c>
       <c r="U24">
-        <v>1.52</v>
+        <v>1.36</v>
       </c>
       <c r="V24">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="W24">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="X24">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y24">
-        <v>11.5</v>
+        <v>8.5</v>
       </c>
       <c r="Z24">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AA24">
-        <v>4.1</v>
+        <v>3</v>
       </c>
       <c r="AB24">
-        <v>1.61</v>
+        <v>2.05</v>
       </c>
       <c r="AC24">
-        <v>2.15</v>
+        <v>1.7</v>
       </c>
       <c r="AD24">
-        <v>2.55</v>
+        <v>3.6</v>
       </c>
       <c r="AE24">
-        <v>1.46</v>
+        <v>1.25</v>
       </c>
       <c r="AF24">
-        <v>1.57</v>
+        <v>2.05</v>
       </c>
       <c r="AG24">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="AH24">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="AI24">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AJ24" t="s">
         <v>113</v>
@@ -3657,76 +3657,76 @@
         <v>111</v>
       </c>
       <c r="L26">
-        <v>1.99</v>
+        <v>1.29</v>
       </c>
       <c r="M26">
-        <v>3.25</v>
+        <v>4.8</v>
       </c>
       <c r="N26">
-        <v>3.25</v>
+        <v>7.3</v>
       </c>
       <c r="O26">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="P26">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="Q26">
+        <v>0</v>
+      </c>
+      <c r="R26">
+        <v>0</v>
+      </c>
+      <c r="S26">
+        <v>0</v>
+      </c>
+      <c r="T26">
+        <v>0</v>
+      </c>
+      <c r="U26">
+        <v>0</v>
+      </c>
+      <c r="V26">
+        <v>0</v>
+      </c>
+      <c r="W26">
+        <v>0</v>
+      </c>
+      <c r="X26">
+        <v>0</v>
+      </c>
+      <c r="Y26">
+        <v>0</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+      <c r="AA26">
+        <v>0</v>
+      </c>
+      <c r="AB26">
+        <v>1.57</v>
+      </c>
+      <c r="AC26">
+        <v>2.4</v>
+      </c>
+      <c r="AD26">
         <v>2.3</v>
       </c>
-      <c r="R26">
-        <v>1.3</v>
-      </c>
-      <c r="S26">
-        <v>3.4</v>
-      </c>
-      <c r="T26">
-        <v>2.5</v>
-      </c>
-      <c r="U26">
-        <v>1.5</v>
-      </c>
-      <c r="V26">
-        <v>6</v>
-      </c>
-      <c r="W26">
-        <v>1.13</v>
-      </c>
-      <c r="X26">
-        <v>1.05</v>
-      </c>
-      <c r="Y26">
-        <v>9.5</v>
-      </c>
-      <c r="Z26">
-        <v>1.22</v>
-      </c>
-      <c r="AA26">
-        <v>4.2</v>
-      </c>
-      <c r="AB26">
-        <v>1.65</v>
-      </c>
-      <c r="AC26">
-        <v>2.1</v>
-      </c>
-      <c r="AD26">
-        <v>2.62</v>
-      </c>
       <c r="AE26">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AF26">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG26">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH26">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AI26">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AJ26" t="s">
         <v>113</v>
@@ -3889,76 +3889,76 @@
         <v>111</v>
       </c>
       <c r="L28">
-        <v>1.29</v>
+        <v>1.99</v>
       </c>
       <c r="M28">
-        <v>4.8</v>
+        <v>3.25</v>
       </c>
       <c r="N28">
-        <v>7.3</v>
+        <v>3.25</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AB28">
+        <v>1.65</v>
+      </c>
+      <c r="AC28">
+        <v>2.1</v>
+      </c>
+      <c r="AD28">
+        <v>2.62</v>
+      </c>
+      <c r="AE28">
+        <v>1.48</v>
+      </c>
+      <c r="AF28">
         <v>1.57</v>
       </c>
-      <c r="AC28">
-        <v>2.4</v>
-      </c>
-      <c r="AD28">
-        <v>2.3</v>
-      </c>
-      <c r="AE28">
-        <v>1.53</v>
-      </c>
-      <c r="AF28">
-        <v>0</v>
-      </c>
       <c r="AG28">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH28">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AI28">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AJ28" t="s">
         <v>113</v>

--- a/jogos_2025-07-16.xlsx
+++ b/jogos_2025-07-16.xlsx
@@ -169,15 +169,15 @@
     <t>Norway Eliteserien</t>
   </si>
   <si>
+    <t>USA MLS Next Pro</t>
+  </si>
+  <si>
     <t>USA MLS</t>
   </si>
   <si>
     <t>USA USL Championship</t>
   </si>
   <si>
-    <t>USA MLS Next Pro</t>
-  </si>
-  <si>
     <t>2025</t>
   </si>
   <si>
@@ -187,12 +187,12 @@
     <t>Atlético Mineiro</t>
   </si>
   <si>
+    <t>Juventude</t>
+  </si>
+  <si>
     <t>Bahia</t>
   </si>
   <si>
-    <t>Juventude</t>
-  </si>
-  <si>
     <t>Fredrikstad</t>
   </si>
   <si>
@@ -205,63 +205,63 @@
     <t>Santos</t>
   </si>
   <si>
+    <t>New York City II</t>
+  </si>
+  <si>
+    <t>Atlanta United FC</t>
+  </si>
+  <si>
     <t>Orlando City</t>
   </si>
   <si>
-    <t>Atlanta United FC</t>
+    <t>Charlotte</t>
+  </si>
+  <si>
+    <t>Hartford Athletic</t>
+  </si>
+  <si>
+    <t>Philadelphia Union</t>
   </si>
   <si>
     <t>New York RB</t>
   </si>
   <si>
-    <t>Philadelphia Union</t>
-  </si>
-  <si>
     <t>FC Cincinnati</t>
   </si>
   <si>
-    <t>Charlotte</t>
-  </si>
-  <si>
-    <t>Hartford Athletic</t>
-  </si>
-  <si>
-    <t>New York City II</t>
-  </si>
-  <si>
     <t>St. Louis City II</t>
   </si>
   <si>
+    <t>Nashville SC</t>
+  </si>
+  <si>
     <t>Minnesota United</t>
   </si>
   <si>
+    <t>Botafogo</t>
+  </si>
+  <si>
+    <t>Tulsa Roughnecks</t>
+  </si>
+  <si>
+    <t>Bragantino</t>
+  </si>
+  <si>
     <t>Houston Dynamo</t>
   </si>
   <si>
-    <t>Bragantino</t>
-  </si>
-  <si>
-    <t>Nashville SC</t>
-  </si>
-  <si>
-    <t>Tulsa Roughnecks</t>
-  </si>
-  <si>
-    <t>Botafogo</t>
-  </si>
-  <si>
     <t>Seattle Sounders</t>
   </si>
   <si>
+    <t>Portland Timbers</t>
+  </si>
+  <si>
+    <t>SJ Earthquakes</t>
+  </si>
+  <si>
     <t>San Diego</t>
   </si>
   <si>
-    <t>SJ Earthquakes</t>
-  </si>
-  <si>
-    <t>Portland Timbers</t>
-  </si>
-  <si>
     <t>LA Galaxy</t>
   </si>
   <si>
@@ -271,12 +271,12 @@
     <t>Sport Recife</t>
   </si>
   <si>
+    <t>Vasco da Gama</t>
+  </si>
+  <si>
     <t>Internacional</t>
   </si>
   <si>
-    <t>Vasco da Gama</t>
-  </si>
-  <si>
     <t>FK Bodo - Glimt</t>
   </si>
   <si>
@@ -289,61 +289,61 @@
     <t>Flamengo</t>
   </si>
   <si>
+    <t>Toronto II</t>
+  </si>
+  <si>
+    <t>Chicago Fire</t>
+  </si>
+  <si>
     <t>New York City</t>
   </si>
   <si>
-    <t>Chicago Fire</t>
+    <t>DC United</t>
+  </si>
+  <si>
+    <t>Tampa Bay Rowdies</t>
+  </si>
+  <si>
+    <t>Montreal Impact</t>
   </si>
   <si>
     <t>New England Revolution</t>
   </si>
   <si>
-    <t>Montreal Impact</t>
-  </si>
-  <si>
     <t>Inter Miami</t>
   </si>
   <si>
-    <t>DC United</t>
-  </si>
-  <si>
-    <t>Tampa Bay Rowdies</t>
-  </si>
-  <si>
-    <t>Toronto II</t>
-  </si>
-  <si>
     <t>LA Galaxy II</t>
   </si>
   <si>
+    <t>Columbus Crew</t>
+  </si>
+  <si>
     <t>Los Angeles FC</t>
   </si>
   <si>
+    <t>Vitória</t>
+  </si>
+  <si>
+    <t>Monterey Bay</t>
+  </si>
+  <si>
+    <t>São Paulo</t>
+  </si>
+  <si>
     <t>Vancouver Whitecaps</t>
   </si>
   <si>
-    <t>São Paulo</t>
-  </si>
-  <si>
-    <t>Columbus Crew</t>
-  </si>
-  <si>
-    <t>Monterey Bay</t>
-  </si>
-  <si>
-    <t>Vitória</t>
-  </si>
-  <si>
     <t>Colorado Rapids</t>
   </si>
   <si>
+    <t>Real Salt Lake</t>
+  </si>
+  <si>
+    <t>FC Dallas</t>
+  </si>
+  <si>
     <t>Toronto</t>
-  </si>
-  <si>
-    <t>FC Dallas</t>
-  </si>
-  <si>
-    <t>Real Salt Lake</t>
   </si>
   <si>
     <t>Austin</t>
@@ -989,13 +989,13 @@
         <v>111</v>
       </c>
       <c r="L3">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="M3">
-        <v>4.4</v>
+        <v>4.36</v>
       </c>
       <c r="N3">
-        <v>6.25</v>
+        <v>6.55</v>
       </c>
       <c r="O3">
         <v>1.33</v>
@@ -1102,43 +1102,43 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L4">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="M4">
-        <v>3.2</v>
+        <v>3.11</v>
       </c>
       <c r="N4">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="O4">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="P4">
         <v>0</v>
       </c>
       <c r="Q4">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="R4">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S4">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T4">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V4">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="W4">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X4">
         <v>0</v>
@@ -1153,10 +1153,10 @@
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="AC4">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AD4">
         <v>0</v>
@@ -1165,10 +1165,10 @@
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG4">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AH4">
         <v>0</v>
@@ -1221,40 +1221,40 @@
         <v>112</v>
       </c>
       <c r="L5">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="M5">
-        <v>3.11</v>
+        <v>3.09</v>
       </c>
       <c r="N5">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="P5">
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X5">
         <v>0</v>
@@ -1269,22 +1269,22 @@
         <v>0</v>
       </c>
       <c r="AB5">
+        <v>2.35</v>
+      </c>
+      <c r="AC5">
+        <v>1.57</v>
+      </c>
+      <c r="AD5">
+        <v>0</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
         <v>2</v>
       </c>
-      <c r="AC5">
-        <v>1.73</v>
-      </c>
-      <c r="AD5">
-        <v>0</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
-        <v>0</v>
-      </c>
       <c r="AG5">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH5">
         <v>0</v>
@@ -1346,43 +1346,43 @@
         <v>1.64</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="AB6">
         <v>1.8</v>
@@ -1391,22 +1391,22 @@
         <v>1.9</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AI6">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AJ6" t="s">
         <v>113</v>
@@ -1453,10 +1453,10 @@
         <v>111</v>
       </c>
       <c r="L7">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="M7">
-        <v>4.33</v>
+        <v>4.15</v>
       </c>
       <c r="N7">
         <v>8</v>
@@ -1471,25 +1471,25 @@
         <v>4.33</v>
       </c>
       <c r="R7">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="S7">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="T7">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="U7">
         <v>1.36</v>
       </c>
       <c r="V7">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="W7">
         <v>1.07</v>
       </c>
       <c r="X7">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y7">
         <v>8.5</v>
@@ -1498,25 +1498,25 @@
         <v>1.33</v>
       </c>
       <c r="AA7">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AB7">
         <v>2</v>
       </c>
       <c r="AC7">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AD7">
-        <v>3.81</v>
+        <v>3.75</v>
       </c>
       <c r="AE7">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AF7">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AG7">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AH7">
         <v>7.5</v>
@@ -1569,13 +1569,13 @@
         <v>111</v>
       </c>
       <c r="L8">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="M8">
-        <v>3.1</v>
+        <v>2.97</v>
       </c>
       <c r="N8">
-        <v>3</v>
+        <v>3.23</v>
       </c>
       <c r="O8">
         <v>1.91</v>
@@ -1587,13 +1587,13 @@
         <v>2.2</v>
       </c>
       <c r="R8">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="S8">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="T8">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="U8">
         <v>1.29</v>
@@ -1602,43 +1602,43 @@
         <v>9</v>
       </c>
       <c r="W8">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X8">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="Y8">
-        <v>8.5</v>
+        <v>6.25</v>
       </c>
       <c r="Z8">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AA8">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="AB8">
         <v>2.55</v>
       </c>
       <c r="AC8">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AD8">
-        <v>5.11</v>
+        <v>5</v>
       </c>
       <c r="AE8">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF8">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AG8">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AH8">
-        <v>9.75</v>
+        <v>10.5</v>
       </c>
       <c r="AI8">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AJ8" t="s">
         <v>113</v>
@@ -1685,10 +1685,10 @@
         <v>111</v>
       </c>
       <c r="L9">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="M9">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="N9">
         <v>1.92</v>
@@ -1703,49 +1703,49 @@
         <v>1.57</v>
       </c>
       <c r="R9">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="S9">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="T9">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="U9">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="V9">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="W9">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X9">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="Y9">
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="Z9">
         <v>1.38</v>
       </c>
       <c r="AA9">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AB9">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AC9">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="AD9">
-        <v>3.8</v>
+        <v>4.29</v>
       </c>
       <c r="AE9">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AF9">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="AG9">
         <v>1.75</v>
@@ -1754,7 +1754,7 @@
         <v>8</v>
       </c>
       <c r="AI9">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AJ9" t="s">
         <v>113</v>
@@ -1801,76 +1801,76 @@
         <v>111</v>
       </c>
       <c r="L10">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M10">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N10">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="O10">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="P10">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Q10">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="R10">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="S10">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T10">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U10">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="V10">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="W10">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X10">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y10">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z10">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AA10">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AB10">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC10">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD10">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE10">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF10">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG10">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH10">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AI10">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="s">
         <v>113</v>
@@ -1890,7 +1890,7 @@
         <v>44</v>
       </c>
       <c r="C11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D11" t="s">
         <v>54</v>
@@ -1971,10 +1971,10 @@
         <v>2.36</v>
       </c>
       <c r="AD11">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AE11">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AF11">
         <v>1.49</v>
@@ -2006,7 +2006,7 @@
         <v>44</v>
       </c>
       <c r="C12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D12" t="s">
         <v>54</v>
@@ -2033,76 +2033,76 @@
         <v>111</v>
       </c>
       <c r="L12">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="M12">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="N12">
-        <v>3.87</v>
+        <v>3.83</v>
       </c>
       <c r="O12">
+        <v>1.52</v>
+      </c>
+      <c r="P12">
+        <v>13</v>
+      </c>
+      <c r="Q12">
+        <v>2.65</v>
+      </c>
+      <c r="R12">
+        <v>1.27</v>
+      </c>
+      <c r="S12">
+        <v>3.4</v>
+      </c>
+      <c r="T12">
+        <v>2.15</v>
+      </c>
+      <c r="U12">
         <v>1.6</v>
       </c>
-      <c r="P12">
-        <v>10.5</v>
-      </c>
-      <c r="Q12">
-        <v>2.55</v>
-      </c>
-      <c r="R12">
-        <v>1.33</v>
-      </c>
-      <c r="S12">
-        <v>3</v>
-      </c>
-      <c r="T12">
-        <v>2.5</v>
-      </c>
-      <c r="U12">
-        <v>1.46</v>
-      </c>
       <c r="V12">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="W12">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X12">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y12">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="Z12">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AA12">
-        <v>3.8</v>
+        <v>4.75</v>
       </c>
       <c r="AB12">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AC12">
-        <v>1.95</v>
+        <v>2.27</v>
       </c>
       <c r="AD12">
-        <v>2.95</v>
+        <v>2.4</v>
       </c>
       <c r="AE12">
-        <v>1.38</v>
+        <v>1.57</v>
       </c>
       <c r="AF12">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AG12">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AH12">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="AI12">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AJ12" t="s">
         <v>113</v>
@@ -2122,7 +2122,7 @@
         <v>44</v>
       </c>
       <c r="C13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D13" t="s">
         <v>54</v>
@@ -2149,25 +2149,25 @@
         <v>111</v>
       </c>
       <c r="L13">
-        <v>1.38</v>
+        <v>1.61</v>
       </c>
       <c r="M13">
-        <v>4.3</v>
+        <v>3.81</v>
       </c>
       <c r="N13">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="O13">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="P13">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Q13">
-        <v>2.95</v>
+        <v>2.6</v>
       </c>
       <c r="R13">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S13">
         <v>3.4</v>
@@ -2194,25 +2194,25 @@
         <v>1.2</v>
       </c>
       <c r="AA13">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AB13">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AC13">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AD13">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="AE13">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AF13">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AG13">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AH13">
         <v>4.33</v>
@@ -2238,7 +2238,7 @@
         <v>44</v>
       </c>
       <c r="C14" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D14" t="s">
         <v>54</v>
@@ -2265,76 +2265,76 @@
         <v>111</v>
       </c>
       <c r="L14">
-        <v>2.06</v>
+        <v>2.85</v>
       </c>
       <c r="M14">
-        <v>3.6</v>
+        <v>3.28</v>
       </c>
       <c r="N14">
-        <v>2.82</v>
+        <v>2.32</v>
       </c>
       <c r="O14">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="P14">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Q14">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="R14">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="S14">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="T14">
-        <v>2.2</v>
+        <v>2.69</v>
       </c>
       <c r="U14">
-        <v>1.6</v>
+        <v>1.42</v>
       </c>
       <c r="V14">
-        <v>4.8</v>
+        <v>6.95</v>
       </c>
       <c r="W14">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X14">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y14">
         <v>10</v>
       </c>
       <c r="Z14">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AA14">
-        <v>4.75</v>
+        <v>3.66</v>
       </c>
       <c r="AB14">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AC14">
-        <v>2.35</v>
+        <v>1.95</v>
       </c>
       <c r="AD14">
-        <v>2.1</v>
+        <v>3.04</v>
       </c>
       <c r="AE14">
-        <v>1.67</v>
+        <v>1.33</v>
       </c>
       <c r="AF14">
-        <v>1.47</v>
+        <v>1.64</v>
       </c>
       <c r="AG14">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="AH14">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="AI14">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AJ14" t="s">
         <v>113</v>
@@ -2354,7 +2354,7 @@
         <v>44</v>
       </c>
       <c r="C15" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D15" t="s">
         <v>54</v>
@@ -2381,25 +2381,25 @@
         <v>111</v>
       </c>
       <c r="L15">
-        <v>1.61</v>
+        <v>1.38</v>
       </c>
       <c r="M15">
-        <v>3.81</v>
+        <v>4.3</v>
       </c>
       <c r="N15">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="O15">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="P15">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Q15">
-        <v>2.6</v>
+        <v>2.95</v>
       </c>
       <c r="R15">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S15">
         <v>3.4</v>
@@ -2426,25 +2426,25 @@
         <v>1.2</v>
       </c>
       <c r="AA15">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AB15">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AC15">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AD15">
-        <v>2.48</v>
+        <v>2.55</v>
       </c>
       <c r="AE15">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AF15">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AG15">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AH15">
         <v>4.33</v>
@@ -2497,22 +2497,22 @@
         <v>111</v>
       </c>
       <c r="L16">
+        <v>1.74</v>
+      </c>
+      <c r="M16">
+        <v>3.5</v>
+      </c>
+      <c r="N16">
+        <v>3.87</v>
+      </c>
+      <c r="O16">
+        <v>1.6</v>
+      </c>
+      <c r="P16">
+        <v>10.5</v>
+      </c>
+      <c r="Q16">
         <v>2.55</v>
-      </c>
-      <c r="M16">
-        <v>3.3</v>
-      </c>
-      <c r="N16">
-        <v>2.49</v>
-      </c>
-      <c r="O16">
-        <v>1.95</v>
-      </c>
-      <c r="P16">
-        <v>12.5</v>
-      </c>
-      <c r="Q16">
-        <v>1.92</v>
       </c>
       <c r="R16">
         <v>1.33</v>
@@ -2521,52 +2521,52 @@
         <v>3</v>
       </c>
       <c r="T16">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="U16">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="V16">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="W16">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X16">
         <v>1.05</v>
       </c>
       <c r="Y16">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="Z16">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AA16">
-        <v>3.58</v>
+        <v>3.8</v>
       </c>
       <c r="AB16">
-        <v>1.82</v>
+        <v>1.68</v>
       </c>
       <c r="AC16">
-        <v>1.89</v>
+        <v>2.05</v>
       </c>
       <c r="AD16">
         <v>2.95</v>
       </c>
       <c r="AE16">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="AF16">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AG16">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AH16">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AI16">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AJ16" t="s">
         <v>113</v>
@@ -2586,7 +2586,7 @@
         <v>44</v>
       </c>
       <c r="C17" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D17" t="s">
         <v>54</v>
@@ -2613,76 +2613,76 @@
         <v>111</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="M17">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH17">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AI17">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AJ17" t="s">
         <v>113</v>
@@ -2702,7 +2702,7 @@
         <v>45</v>
       </c>
       <c r="C18" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D18" t="s">
         <v>54</v>
@@ -2818,7 +2818,7 @@
         <v>46</v>
       </c>
       <c r="C19" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D19" t="s">
         <v>54</v>
@@ -2845,76 +2845,76 @@
         <v>111</v>
       </c>
       <c r="L19">
-        <v>2.53</v>
+        <v>1.98</v>
       </c>
       <c r="M19">
-        <v>3.3</v>
+        <v>3.39</v>
       </c>
       <c r="N19">
-        <v>2.37</v>
+        <v>3.12</v>
       </c>
       <c r="O19">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="P19">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="Q19">
-        <v>1.93</v>
+        <v>2.25</v>
       </c>
       <c r="R19">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S19">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="T19">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="U19">
+        <v>1.52</v>
+      </c>
+      <c r="V19">
+        <v>5.5</v>
+      </c>
+      <c r="W19">
+        <v>1.13</v>
+      </c>
+      <c r="X19">
+        <v>1.03</v>
+      </c>
+      <c r="Y19">
+        <v>11.5</v>
+      </c>
+      <c r="Z19">
+        <v>1.2</v>
+      </c>
+      <c r="AA19">
+        <v>4.1</v>
+      </c>
+      <c r="AB19">
+        <v>1.54</v>
+      </c>
+      <c r="AC19">
+        <v>2.3</v>
+      </c>
+      <c r="AD19">
+        <v>2.7</v>
+      </c>
+      <c r="AE19">
         <v>1.46</v>
       </c>
-      <c r="V19">
-        <v>6</v>
-      </c>
-      <c r="W19">
-        <v>1.11</v>
-      </c>
-      <c r="X19">
-        <v>1.05</v>
-      </c>
-      <c r="Y19">
-        <v>9.5</v>
-      </c>
-      <c r="Z19">
-        <v>1.25</v>
-      </c>
-      <c r="AA19">
-        <v>3.75</v>
-      </c>
-      <c r="AB19">
-        <v>1.75</v>
-      </c>
-      <c r="AC19">
-        <v>1.95</v>
-      </c>
-      <c r="AD19">
-        <v>3</v>
-      </c>
-      <c r="AE19">
-        <v>1.38</v>
-      </c>
       <c r="AF19">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="AG19">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AH19">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="AI19">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AJ19" t="s">
         <v>113</v>
@@ -2934,7 +2934,7 @@
         <v>46</v>
       </c>
       <c r="C20" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D20" t="s">
         <v>54</v>
@@ -2961,40 +2961,40 @@
         <v>111</v>
       </c>
       <c r="L20">
-        <v>2.16</v>
+        <v>2.53</v>
       </c>
       <c r="M20">
-        <v>3.21</v>
+        <v>3.3</v>
       </c>
       <c r="N20">
-        <v>2.9</v>
+        <v>2.37</v>
       </c>
       <c r="O20">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="P20">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="Q20">
-        <v>2.15</v>
+        <v>1.93</v>
       </c>
       <c r="R20">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S20">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="T20">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="U20">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="V20">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="W20">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X20">
         <v>1.05</v>
@@ -3003,34 +3003,34 @@
         <v>9.5</v>
       </c>
       <c r="Z20">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AA20">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="AB20">
-        <v>1.82</v>
+        <v>1.66</v>
       </c>
       <c r="AC20">
-        <v>1.88</v>
+        <v>2.08</v>
       </c>
       <c r="AD20">
-        <v>1.02</v>
+        <v>3</v>
       </c>
       <c r="AE20">
-        <v>1.02</v>
+        <v>1.38</v>
       </c>
       <c r="AF20">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="AG20">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH20">
         <v>5.5</v>
       </c>
       <c r="AI20">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AJ20" t="s">
         <v>113</v>
@@ -3077,76 +3077,76 @@
         <v>111</v>
       </c>
       <c r="L21">
-        <v>2.04</v>
+        <v>1.39</v>
       </c>
       <c r="M21">
-        <v>3.15</v>
+        <v>3.7</v>
       </c>
       <c r="N21">
-        <v>3.55</v>
+        <v>6.9</v>
       </c>
       <c r="O21">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="P21">
+        <v>8.25</v>
+      </c>
+      <c r="Q21">
+        <v>3.5</v>
+      </c>
+      <c r="R21">
+        <v>1.4</v>
+      </c>
+      <c r="S21">
+        <v>2.62</v>
+      </c>
+      <c r="T21">
+        <v>2.91</v>
+      </c>
+      <c r="U21">
+        <v>1.38</v>
+      </c>
+      <c r="V21">
         <v>7</v>
       </c>
-      <c r="Q21">
-        <v>2.5</v>
-      </c>
-      <c r="R21">
-        <v>1.44</v>
-      </c>
-      <c r="S21">
-        <v>2.5</v>
-      </c>
-      <c r="T21">
-        <v>3.3</v>
-      </c>
-      <c r="U21">
-        <v>1.26</v>
-      </c>
-      <c r="V21">
+      <c r="W21">
+        <v>1.07</v>
+      </c>
+      <c r="X21">
+        <v>1.06</v>
+      </c>
+      <c r="Y21">
         <v>8.5</v>
       </c>
-      <c r="W21">
-        <v>1.05</v>
-      </c>
-      <c r="X21">
-        <v>1.03</v>
-      </c>
-      <c r="Y21">
-        <v>8</v>
-      </c>
       <c r="Z21">
-        <v>1.47</v>
+        <v>1.35</v>
       </c>
       <c r="AA21">
-        <v>2.56</v>
+        <v>3.1</v>
       </c>
       <c r="AB21">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="AC21">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AD21">
-        <v>4.7</v>
+        <v>3.85</v>
       </c>
       <c r="AE21">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="AF21">
-        <v>2.06</v>
+        <v>2.27</v>
       </c>
       <c r="AG21">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AH21">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AI21">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AJ21" t="s">
         <v>113</v>
@@ -3166,7 +3166,7 @@
         <v>46</v>
       </c>
       <c r="C22" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D22" t="s">
         <v>54</v>
@@ -3193,76 +3193,76 @@
         <v>111</v>
       </c>
       <c r="L22">
-        <v>1.98</v>
+        <v>1.5</v>
       </c>
       <c r="M22">
-        <v>3.39</v>
+        <v>3.7</v>
       </c>
       <c r="N22">
-        <v>3.12</v>
+        <v>5.67</v>
       </c>
       <c r="O22">
-        <v>1.73</v>
+        <v>1.41</v>
       </c>
       <c r="P22">
-        <v>11.5</v>
+        <v>11.75</v>
       </c>
       <c r="Q22">
-        <v>2.25</v>
+        <v>3.1</v>
       </c>
       <c r="R22">
+        <v>1.36</v>
+      </c>
+      <c r="S22">
+        <v>2.94</v>
+      </c>
+      <c r="T22">
+        <v>2.76</v>
+      </c>
+      <c r="U22">
+        <v>1.4</v>
+      </c>
+      <c r="V22">
+        <v>6</v>
+      </c>
+      <c r="W22">
+        <v>1.09</v>
+      </c>
+      <c r="X22">
+        <v>1.01</v>
+      </c>
+      <c r="Y22">
+        <v>9</v>
+      </c>
+      <c r="Z22">
         <v>1.3</v>
       </c>
-      <c r="S22">
-        <v>3.2</v>
-      </c>
-      <c r="T22">
-        <v>2.35</v>
-      </c>
-      <c r="U22">
-        <v>1.52</v>
-      </c>
-      <c r="V22">
-        <v>5.5</v>
-      </c>
-      <c r="W22">
-        <v>1.13</v>
-      </c>
-      <c r="X22">
-        <v>1.03</v>
-      </c>
-      <c r="Y22">
-        <v>11.5</v>
-      </c>
-      <c r="Z22">
-        <v>1.2</v>
-      </c>
       <c r="AA22">
-        <v>4.1</v>
+        <v>3.33</v>
       </c>
       <c r="AB22">
-        <v>1.61</v>
+        <v>1.91</v>
       </c>
       <c r="AC22">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AD22">
-        <v>2.7</v>
+        <v>3.28</v>
       </c>
       <c r="AE22">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AF22">
-        <v>1.57</v>
+        <v>1.91</v>
       </c>
       <c r="AG22">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AH22">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="AI22">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AJ22" t="s">
         <v>113</v>
@@ -3282,7 +3282,7 @@
         <v>46</v>
       </c>
       <c r="C23" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D23" t="s">
         <v>54</v>
@@ -3309,76 +3309,76 @@
         <v>111</v>
       </c>
       <c r="L23">
+        <v>2.2</v>
+      </c>
+      <c r="M23">
+        <v>3.1</v>
+      </c>
+      <c r="N23">
+        <v>3.05</v>
+      </c>
+      <c r="O23">
+        <v>1.73</v>
+      </c>
+      <c r="P23">
+        <v>7</v>
+      </c>
+      <c r="Q23">
+        <v>2.5</v>
+      </c>
+      <c r="R23">
+        <v>1.5</v>
+      </c>
+      <c r="S23">
+        <v>2.37</v>
+      </c>
+      <c r="T23">
+        <v>3.45</v>
+      </c>
+      <c r="U23">
+        <v>1.3</v>
+      </c>
+      <c r="V23">
+        <v>9.75</v>
+      </c>
+      <c r="W23">
+        <v>1.05</v>
+      </c>
+      <c r="X23">
+        <v>1.07</v>
+      </c>
+      <c r="Y23">
+        <v>7</v>
+      </c>
+      <c r="Z23">
         <v>1.48</v>
       </c>
-      <c r="M23">
-        <v>4.1</v>
-      </c>
-      <c r="N23">
-        <v>5.6</v>
-      </c>
-      <c r="O23">
-        <v>1.41</v>
-      </c>
-      <c r="P23">
-        <v>11.75</v>
-      </c>
-      <c r="Q23">
-        <v>3.1</v>
-      </c>
-      <c r="R23">
-        <v>1.32</v>
-      </c>
-      <c r="S23">
-        <v>2.95</v>
-      </c>
-      <c r="T23">
-        <v>2.75</v>
-      </c>
-      <c r="U23">
-        <v>1.37</v>
-      </c>
-      <c r="V23">
-        <v>6</v>
-      </c>
-      <c r="W23">
-        <v>1.08</v>
-      </c>
-      <c r="X23">
-        <v>1.01</v>
-      </c>
-      <c r="Y23">
-        <v>10</v>
-      </c>
-      <c r="Z23">
-        <v>1.29</v>
-      </c>
       <c r="AA23">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="AB23">
-        <v>1.87</v>
+        <v>2.4</v>
       </c>
       <c r="AC23">
-        <v>1.84</v>
+        <v>1.53</v>
       </c>
       <c r="AD23">
-        <v>3.14</v>
+        <v>4.7</v>
       </c>
       <c r="AE23">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="AF23">
-        <v>1.87</v>
+        <v>2.18</v>
       </c>
       <c r="AG23">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AH23">
-        <v>5.3</v>
+        <v>7.2</v>
       </c>
       <c r="AI23">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AJ23" t="s">
         <v>113</v>
@@ -3398,7 +3398,7 @@
         <v>46</v>
       </c>
       <c r="C24" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D24" t="s">
         <v>54</v>
@@ -3425,76 +3425,76 @@
         <v>111</v>
       </c>
       <c r="L24">
-        <v>1.48</v>
+        <v>2.16</v>
       </c>
       <c r="M24">
-        <v>4.12</v>
+        <v>3.21</v>
       </c>
       <c r="N24">
-        <v>6.72</v>
+        <v>2.9</v>
       </c>
       <c r="O24">
-        <v>1.4</v>
+        <v>1.82</v>
       </c>
       <c r="P24">
-        <v>8.25</v>
+        <v>9.5</v>
       </c>
       <c r="Q24">
-        <v>3.5</v>
+        <v>2.15</v>
       </c>
       <c r="R24">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="S24">
-        <v>2.62</v>
+        <v>2.87</v>
       </c>
       <c r="T24">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="U24">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="V24">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="W24">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X24">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y24">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="Z24">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AA24">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="AB24">
+        <v>1.82</v>
+      </c>
+      <c r="AC24">
+        <v>1.88</v>
+      </c>
+      <c r="AD24">
+        <v>1.02</v>
+      </c>
+      <c r="AE24">
+        <v>1.02</v>
+      </c>
+      <c r="AF24">
+        <v>1.68</v>
+      </c>
+      <c r="AG24">
         <v>2.05</v>
       </c>
-      <c r="AC24">
-        <v>1.7</v>
-      </c>
-      <c r="AD24">
-        <v>3.6</v>
-      </c>
-      <c r="AE24">
-        <v>1.25</v>
-      </c>
-      <c r="AF24">
-        <v>2.05</v>
-      </c>
-      <c r="AG24">
-        <v>1.7</v>
-      </c>
       <c r="AH24">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="AI24">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AJ24" t="s">
         <v>113</v>
@@ -3514,7 +3514,7 @@
         <v>47</v>
       </c>
       <c r="C25" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D25" t="s">
         <v>54</v>
@@ -3595,10 +3595,10 @@
         <v>1.94</v>
       </c>
       <c r="AD25">
-        <v>3.35</v>
+        <v>2.25</v>
       </c>
       <c r="AE25">
-        <v>1.3</v>
+        <v>1.57</v>
       </c>
       <c r="AF25">
         <v>2.05</v>
@@ -3630,7 +3630,7 @@
         <v>48</v>
       </c>
       <c r="C26" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D26" t="s">
         <v>54</v>
@@ -3657,76 +3657,76 @@
         <v>111</v>
       </c>
       <c r="L26">
-        <v>1.29</v>
+        <v>1.99</v>
       </c>
       <c r="M26">
-        <v>4.8</v>
+        <v>3.25</v>
       </c>
       <c r="N26">
-        <v>7.3</v>
+        <v>3.25</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AB26">
+        <v>1.54</v>
+      </c>
+      <c r="AC26">
+        <v>2.3</v>
+      </c>
+      <c r="AD26">
+        <v>2.62</v>
+      </c>
+      <c r="AE26">
+        <v>1.48</v>
+      </c>
+      <c r="AF26">
         <v>1.57</v>
       </c>
-      <c r="AC26">
-        <v>2.4</v>
-      </c>
-      <c r="AD26">
-        <v>2.3</v>
-      </c>
-      <c r="AE26">
-        <v>1.53</v>
-      </c>
-      <c r="AF26">
-        <v>0</v>
-      </c>
       <c r="AG26">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH26">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AI26">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AJ26" t="s">
         <v>113</v>
@@ -3746,7 +3746,7 @@
         <v>48</v>
       </c>
       <c r="C27" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D27" t="s">
         <v>54</v>
@@ -3862,7 +3862,7 @@
         <v>48</v>
       </c>
       <c r="C28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D28" t="s">
         <v>54</v>
@@ -3889,76 +3889,76 @@
         <v>111</v>
       </c>
       <c r="L28">
-        <v>1.99</v>
+        <v>1.29</v>
       </c>
       <c r="M28">
-        <v>3.25</v>
+        <v>4.8</v>
       </c>
       <c r="N28">
-        <v>3.25</v>
+        <v>7.3</v>
       </c>
       <c r="O28">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="P28">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="Q28">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="R28">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S28">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T28">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U28">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V28">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W28">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X28">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y28">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="Z28">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AA28">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AB28">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AC28">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AD28">
-        <v>2.62</v>
+        <v>2.05</v>
       </c>
       <c r="AE28">
-        <v>1.48</v>
+        <v>1.68</v>
       </c>
       <c r="AF28">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG28">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH28">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AI28">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AJ28" t="s">
         <v>113</v>
@@ -3978,7 +3978,7 @@
         <v>48</v>
       </c>
       <c r="C29" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D29" t="s">
         <v>54</v>
@@ -4053,7 +4053,7 @@
         <v>3.8</v>
       </c>
       <c r="AB29">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AC29">
         <v>2</v>

--- a/jogos_2025-07-16.xlsx
+++ b/jogos_2025-07-16.xlsx
@@ -169,12 +169,12 @@
     <t>Norway Eliteserien</t>
   </si>
   <si>
+    <t>USA MLS</t>
+  </si>
+  <si>
     <t>USA MLS Next Pro</t>
   </si>
   <si>
-    <t>USA MLS</t>
-  </si>
-  <si>
     <t>USA USL Championship</t>
   </si>
   <si>
@@ -184,15 +184,15 @@
     <t>Grêmio</t>
   </si>
   <si>
+    <t>Bahia</t>
+  </si>
+  <si>
+    <t>Juventude</t>
+  </si>
+  <si>
     <t>Atlético Mineiro</t>
   </si>
   <si>
-    <t>Juventude</t>
-  </si>
-  <si>
-    <t>Bahia</t>
-  </si>
-  <si>
     <t>Fredrikstad</t>
   </si>
   <si>
@@ -205,78 +205,78 @@
     <t>Santos</t>
   </si>
   <si>
+    <t>New York RB</t>
+  </si>
+  <si>
+    <t>FC Cincinnati</t>
+  </si>
+  <si>
     <t>New York City II</t>
   </si>
   <si>
+    <t>Hartford Athletic</t>
+  </si>
+  <si>
     <t>Atlanta United FC</t>
   </si>
   <si>
     <t>Orlando City</t>
   </si>
   <si>
+    <t>Philadelphia Union</t>
+  </si>
+  <si>
     <t>Charlotte</t>
   </si>
   <si>
-    <t>Hartford Athletic</t>
-  </si>
-  <si>
-    <t>Philadelphia Union</t>
-  </si>
-  <si>
-    <t>New York RB</t>
-  </si>
-  <si>
-    <t>FC Cincinnati</t>
-  </si>
-  <si>
     <t>St. Louis City II</t>
   </si>
   <si>
     <t>Nashville SC</t>
   </si>
   <si>
+    <t>Tulsa Roughnecks</t>
+  </si>
+  <si>
+    <t>Bragantino</t>
+  </si>
+  <si>
     <t>Minnesota United</t>
   </si>
   <si>
     <t>Botafogo</t>
   </si>
   <si>
-    <t>Tulsa Roughnecks</t>
-  </si>
-  <si>
-    <t>Bragantino</t>
-  </si>
-  <si>
     <t>Houston Dynamo</t>
   </si>
   <si>
     <t>Seattle Sounders</t>
   </si>
   <si>
+    <t>LA Galaxy</t>
+  </si>
+  <si>
     <t>Portland Timbers</t>
   </si>
   <si>
+    <t>San Diego</t>
+  </si>
+  <si>
     <t>SJ Earthquakes</t>
   </si>
   <si>
-    <t>San Diego</t>
-  </si>
-  <si>
-    <t>LA Galaxy</t>
-  </si>
-  <si>
     <t>Fortaleza</t>
   </si>
   <si>
+    <t>Internacional</t>
+  </si>
+  <si>
+    <t>Vasco da Gama</t>
+  </si>
+  <si>
     <t>Sport Recife</t>
   </si>
   <si>
-    <t>Vasco da Gama</t>
-  </si>
-  <si>
-    <t>Internacional</t>
-  </si>
-  <si>
     <t>FK Bodo - Glimt</t>
   </si>
   <si>
@@ -289,64 +289,64 @@
     <t>Flamengo</t>
   </si>
   <si>
+    <t>New England Revolution</t>
+  </si>
+  <si>
+    <t>Inter Miami</t>
+  </si>
+  <si>
     <t>Toronto II</t>
   </si>
   <si>
+    <t>Tampa Bay Rowdies</t>
+  </si>
+  <si>
     <t>Chicago Fire</t>
   </si>
   <si>
     <t>New York City</t>
   </si>
   <si>
+    <t>Montreal Impact</t>
+  </si>
+  <si>
     <t>DC United</t>
   </si>
   <si>
-    <t>Tampa Bay Rowdies</t>
-  </si>
-  <si>
-    <t>Montreal Impact</t>
-  </si>
-  <si>
-    <t>New England Revolution</t>
-  </si>
-  <si>
-    <t>Inter Miami</t>
-  </si>
-  <si>
     <t>LA Galaxy II</t>
   </si>
   <si>
     <t>Columbus Crew</t>
   </si>
   <si>
+    <t>Monterey Bay</t>
+  </si>
+  <si>
+    <t>São Paulo</t>
+  </si>
+  <si>
     <t>Los Angeles FC</t>
   </si>
   <si>
     <t>Vitória</t>
   </si>
   <si>
-    <t>Monterey Bay</t>
-  </si>
-  <si>
-    <t>São Paulo</t>
-  </si>
-  <si>
     <t>Vancouver Whitecaps</t>
   </si>
   <si>
     <t>Colorado Rapids</t>
   </si>
   <si>
+    <t>Austin</t>
+  </si>
+  <si>
     <t>Real Salt Lake</t>
   </si>
   <si>
+    <t>Toronto</t>
+  </si>
+  <si>
     <t>FC Dallas</t>
-  </si>
-  <si>
-    <t>Toronto</t>
-  </si>
-  <si>
-    <t>Austin</t>
   </si>
   <si>
     <t>incomplete</t>
@@ -986,43 +986,43 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L3">
-        <v>1.47</v>
+        <v>2.49</v>
       </c>
       <c r="M3">
-        <v>4.36</v>
+        <v>3.28</v>
       </c>
       <c r="N3">
-        <v>6.55</v>
+        <v>3</v>
       </c>
       <c r="O3">
-        <v>1.33</v>
+        <v>1.83</v>
       </c>
       <c r="P3">
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="R3">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="S3">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="T3">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="U3">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="V3">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="W3">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X3">
         <v>0</v>
@@ -1037,10 +1037,10 @@
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="AC3">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -1049,10 +1049,10 @@
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AG3">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -1105,13 +1105,13 @@
         <v>112</v>
       </c>
       <c r="L4">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="M4">
-        <v>3.11</v>
+        <v>3.25</v>
       </c>
       <c r="N4">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="O4">
         <v>0</v>
@@ -1218,43 +1218,43 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="L5">
-        <v>2.44</v>
+        <v>1.5</v>
       </c>
       <c r="M5">
-        <v>3.09</v>
+        <v>4.4</v>
       </c>
       <c r="N5">
-        <v>2.9</v>
+        <v>6.5</v>
       </c>
       <c r="O5">
-        <v>1.83</v>
+        <v>1.33</v>
       </c>
       <c r="P5">
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>2.3</v>
+        <v>3.6</v>
       </c>
       <c r="R5">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="S5">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="T5">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="U5">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="V5">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="W5">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X5">
         <v>0</v>
@@ -1269,10 +1269,10 @@
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>2.35</v>
+        <v>1.95</v>
       </c>
       <c r="AC5">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="AD5">
         <v>0</v>
@@ -1281,10 +1281,10 @@
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AG5">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AH5">
         <v>0</v>
@@ -1453,10 +1453,10 @@
         <v>111</v>
       </c>
       <c r="L7">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="M7">
-        <v>4.15</v>
+        <v>4.5</v>
       </c>
       <c r="N7">
         <v>8</v>
@@ -1471,58 +1471,58 @@
         <v>4.33</v>
       </c>
       <c r="R7">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S7">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="T7">
-        <v>3.15</v>
+        <v>2.93</v>
       </c>
       <c r="U7">
         <v>1.36</v>
       </c>
       <c r="V7">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="W7">
+        <v>1.06</v>
+      </c>
+      <c r="X7">
+        <v>1.06</v>
+      </c>
+      <c r="Y7">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="Z7">
+        <v>1.36</v>
+      </c>
+      <c r="AA7">
+        <v>2.9</v>
+      </c>
+      <c r="AB7">
+        <v>2.05</v>
+      </c>
+      <c r="AC7">
+        <v>1.73</v>
+      </c>
+      <c r="AD7">
+        <v>3.9</v>
+      </c>
+      <c r="AE7">
+        <v>1.21</v>
+      </c>
+      <c r="AF7">
+        <v>2.45</v>
+      </c>
+      <c r="AG7">
+        <v>1.56</v>
+      </c>
+      <c r="AH7">
+        <v>8</v>
+      </c>
+      <c r="AI7">
         <v>1.07</v>
-      </c>
-      <c r="X7">
-        <v>1.05</v>
-      </c>
-      <c r="Y7">
-        <v>8.5</v>
-      </c>
-      <c r="Z7">
-        <v>1.33</v>
-      </c>
-      <c r="AA7">
-        <v>3.1</v>
-      </c>
-      <c r="AB7">
-        <v>2</v>
-      </c>
-      <c r="AC7">
-        <v>1.75</v>
-      </c>
-      <c r="AD7">
-        <v>3.75</v>
-      </c>
-      <c r="AE7">
-        <v>1.22</v>
-      </c>
-      <c r="AF7">
-        <v>2.3</v>
-      </c>
-      <c r="AG7">
-        <v>1.55</v>
-      </c>
-      <c r="AH7">
-        <v>7.5</v>
-      </c>
-      <c r="AI7">
-        <v>1.08</v>
       </c>
       <c r="AJ7" t="s">
         <v>113</v>
@@ -1569,13 +1569,13 @@
         <v>111</v>
       </c>
       <c r="L8">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="M8">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="N8">
-        <v>3.23</v>
+        <v>3.1</v>
       </c>
       <c r="O8">
         <v>1.91</v>
@@ -1587,58 +1587,58 @@
         <v>2.2</v>
       </c>
       <c r="R8">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="S8">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="T8">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="U8">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="V8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W8">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X8">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Y8">
         <v>6.25</v>
       </c>
       <c r="Z8">
+        <v>1.5</v>
+      </c>
+      <c r="AA8">
+        <v>2.38</v>
+      </c>
+      <c r="AB8">
+        <v>2.6</v>
+      </c>
+      <c r="AC8">
         <v>1.44</v>
       </c>
-      <c r="AA8">
-        <v>2.55</v>
-      </c>
-      <c r="AB8">
-        <v>2.55</v>
-      </c>
-      <c r="AC8">
-        <v>1.5</v>
-      </c>
       <c r="AD8">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AE8">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AF8">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AG8">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AH8">
-        <v>10.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AI8">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AJ8" t="s">
         <v>113</v>
@@ -1691,7 +1691,7 @@
         <v>3.4</v>
       </c>
       <c r="N9">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="O9">
         <v>2.63</v>
@@ -1703,58 +1703,58 @@
         <v>1.57</v>
       </c>
       <c r="R9">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S9">
         <v>2.7</v>
       </c>
       <c r="T9">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="U9">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="V9">
-        <v>7.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W9">
         <v>1.06</v>
       </c>
       <c r="X9">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y9">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="Z9">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AA9">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AB9">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AC9">
-        <v>1.71</v>
+        <v>1.57</v>
       </c>
       <c r="AD9">
-        <v>4.29</v>
+        <v>4</v>
       </c>
       <c r="AE9">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AF9">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AG9">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AH9">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="AI9">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AJ9" t="s">
         <v>113</v>
@@ -1801,76 +1801,76 @@
         <v>111</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH10">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AI10">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AJ10" t="s">
         <v>113</v>
@@ -1890,7 +1890,7 @@
         <v>44</v>
       </c>
       <c r="C11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D11" t="s">
         <v>54</v>
@@ -1917,22 +1917,22 @@
         <v>111</v>
       </c>
       <c r="L11">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="M11">
-        <v>3.63</v>
+        <v>3.6</v>
       </c>
       <c r="N11">
-        <v>2.91</v>
+        <v>2.82</v>
       </c>
       <c r="O11">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="P11">
         <v>13</v>
       </c>
       <c r="Q11">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="R11">
         <v>1.27</v>
@@ -1944,10 +1944,10 @@
         <v>2.2</v>
       </c>
       <c r="U11">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="V11">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="W11">
         <v>1.15</v>
@@ -1965,22 +1965,22 @@
         <v>4.75</v>
       </c>
       <c r="AB11">
-        <v>1.59</v>
+        <v>1.37</v>
       </c>
       <c r="AC11">
-        <v>2.36</v>
+        <v>2.94</v>
       </c>
       <c r="AD11">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AE11">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="AF11">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="AG11">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AH11">
         <v>4.2</v>
@@ -2033,76 +2033,76 @@
         <v>111</v>
       </c>
       <c r="L12">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M12">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N12">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="O12">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="P12">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Q12">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="R12">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="S12">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T12">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U12">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="V12">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="W12">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X12">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y12">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z12">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AA12">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AB12">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AC12">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AD12">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE12">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF12">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG12">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH12">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AI12">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="s">
         <v>113</v>
@@ -2122,7 +2122,7 @@
         <v>44</v>
       </c>
       <c r="C13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D13" t="s">
         <v>54</v>
@@ -2149,76 +2149,76 @@
         <v>111</v>
       </c>
       <c r="L13">
-        <v>1.61</v>
+        <v>2.55</v>
       </c>
       <c r="M13">
-        <v>3.81</v>
+        <v>3.3</v>
       </c>
       <c r="N13">
-        <v>4.2</v>
+        <v>2.49</v>
       </c>
       <c r="O13">
-        <v>1.53</v>
+        <v>1.95</v>
       </c>
       <c r="P13">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Q13">
-        <v>2.6</v>
+        <v>1.92</v>
       </c>
       <c r="R13">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="S13">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="T13">
-        <v>2.25</v>
+        <v>2.7</v>
       </c>
       <c r="U13">
-        <v>1.57</v>
+        <v>1.42</v>
       </c>
       <c r="V13">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W13">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="X13">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y13">
         <v>10</v>
       </c>
       <c r="Z13">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AA13">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="AB13">
-        <v>1.57</v>
+        <v>1.82</v>
       </c>
       <c r="AC13">
-        <v>2.25</v>
+        <v>1.89</v>
       </c>
       <c r="AD13">
-        <v>2.3</v>
+        <v>3.04</v>
       </c>
       <c r="AE13">
-        <v>1.54</v>
+        <v>1.33</v>
       </c>
       <c r="AF13">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AG13">
         <v>2.15</v>
       </c>
       <c r="AH13">
-        <v>4.33</v>
+        <v>5.5</v>
       </c>
       <c r="AI13">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AJ13" t="s">
         <v>113</v>
@@ -2238,7 +2238,7 @@
         <v>44</v>
       </c>
       <c r="C14" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D14" t="s">
         <v>54</v>
@@ -2265,76 +2265,76 @@
         <v>111</v>
       </c>
       <c r="L14">
-        <v>2.85</v>
+        <v>2</v>
       </c>
       <c r="M14">
-        <v>3.28</v>
+        <v>3.63</v>
       </c>
       <c r="N14">
-        <v>2.32</v>
+        <v>2.91</v>
       </c>
       <c r="O14">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="P14">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Q14">
-        <v>1.92</v>
+        <v>2.15</v>
       </c>
       <c r="R14">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="S14">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="T14">
-        <v>2.69</v>
+        <v>2.2</v>
       </c>
       <c r="U14">
-        <v>1.42</v>
+        <v>1.58</v>
       </c>
       <c r="V14">
-        <v>6.95</v>
+        <v>5</v>
       </c>
       <c r="W14">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="X14">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y14">
         <v>10</v>
       </c>
       <c r="Z14">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AA14">
-        <v>3.66</v>
+        <v>4.75</v>
       </c>
       <c r="AB14">
-        <v>1.8</v>
+        <v>1.59</v>
       </c>
       <c r="AC14">
-        <v>1.95</v>
+        <v>2.36</v>
       </c>
       <c r="AD14">
-        <v>3.04</v>
+        <v>2.1</v>
       </c>
       <c r="AE14">
-        <v>1.33</v>
+        <v>1.65</v>
       </c>
       <c r="AF14">
-        <v>1.64</v>
+        <v>1.49</v>
       </c>
       <c r="AG14">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AH14">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="AI14">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="AJ14" t="s">
         <v>113</v>
@@ -2354,7 +2354,7 @@
         <v>44</v>
       </c>
       <c r="C15" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D15" t="s">
         <v>54</v>
@@ -2381,40 +2381,40 @@
         <v>111</v>
       </c>
       <c r="L15">
-        <v>1.38</v>
+        <v>1.73</v>
       </c>
       <c r="M15">
-        <v>4.3</v>
+        <v>3.55</v>
       </c>
       <c r="N15">
-        <v>6</v>
+        <v>3.83</v>
       </c>
       <c r="O15">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="P15">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Q15">
-        <v>2.95</v>
+        <v>2.65</v>
       </c>
       <c r="R15">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S15">
         <v>3.4</v>
       </c>
       <c r="T15">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="U15">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="V15">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="W15">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X15">
         <v>1.04</v>
@@ -2423,34 +2423,34 @@
         <v>10</v>
       </c>
       <c r="Z15">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AA15">
-        <v>4.33</v>
+        <v>4.75</v>
       </c>
       <c r="AB15">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="AC15">
-        <v>2.35</v>
+        <v>2.27</v>
       </c>
       <c r="AD15">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="AE15">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AF15">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AG15">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AH15">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="AI15">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AJ15" t="s">
         <v>113</v>
@@ -2470,7 +2470,7 @@
         <v>44</v>
       </c>
       <c r="C16" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D16" t="s">
         <v>54</v>
@@ -2497,64 +2497,64 @@
         <v>111</v>
       </c>
       <c r="L16">
-        <v>1.74</v>
+        <v>1.38</v>
       </c>
       <c r="M16">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="N16">
-        <v>3.87</v>
+        <v>6</v>
       </c>
       <c r="O16">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="P16">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="Q16">
+        <v>2.95</v>
+      </c>
+      <c r="R16">
+        <v>1.28</v>
+      </c>
+      <c r="S16">
+        <v>3.4</v>
+      </c>
+      <c r="T16">
+        <v>2.25</v>
+      </c>
+      <c r="U16">
+        <v>1.57</v>
+      </c>
+      <c r="V16">
+        <v>5</v>
+      </c>
+      <c r="W16">
+        <v>1.14</v>
+      </c>
+      <c r="X16">
+        <v>1.04</v>
+      </c>
+      <c r="Y16">
+        <v>10</v>
+      </c>
+      <c r="Z16">
+        <v>1.2</v>
+      </c>
+      <c r="AA16">
+        <v>4.33</v>
+      </c>
+      <c r="AB16">
+        <v>1.52</v>
+      </c>
+      <c r="AC16">
+        <v>2.35</v>
+      </c>
+      <c r="AD16">
         <v>2.55</v>
       </c>
-      <c r="R16">
-        <v>1.33</v>
-      </c>
-      <c r="S16">
-        <v>3</v>
-      </c>
-      <c r="T16">
-        <v>2.5</v>
-      </c>
-      <c r="U16">
-        <v>1.46</v>
-      </c>
-      <c r="V16">
-        <v>6</v>
-      </c>
-      <c r="W16">
-        <v>1.11</v>
-      </c>
-      <c r="X16">
-        <v>1.05</v>
-      </c>
-      <c r="Y16">
-        <v>9.5</v>
-      </c>
-      <c r="Z16">
-        <v>1.25</v>
-      </c>
-      <c r="AA16">
-        <v>3.8</v>
-      </c>
-      <c r="AB16">
-        <v>1.68</v>
-      </c>
-      <c r="AC16">
-        <v>2.05</v>
-      </c>
-      <c r="AD16">
-        <v>2.95</v>
-      </c>
       <c r="AE16">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AF16">
         <v>1.7</v>
@@ -2563,10 +2563,10 @@
         <v>2</v>
       </c>
       <c r="AH16">
-        <v>5.5</v>
+        <v>4.33</v>
       </c>
       <c r="AI16">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AJ16" t="s">
         <v>113</v>
@@ -2586,7 +2586,7 @@
         <v>44</v>
       </c>
       <c r="C17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D17" t="s">
         <v>54</v>
@@ -2613,22 +2613,22 @@
         <v>111</v>
       </c>
       <c r="L17">
-        <v>2.06</v>
+        <v>1.61</v>
       </c>
       <c r="M17">
-        <v>3.6</v>
+        <v>3.81</v>
       </c>
       <c r="N17">
-        <v>2.82</v>
+        <v>4.2</v>
       </c>
       <c r="O17">
-        <v>1.82</v>
+        <v>1.53</v>
       </c>
       <c r="P17">
         <v>13</v>
       </c>
       <c r="Q17">
-        <v>2.05</v>
+        <v>2.6</v>
       </c>
       <c r="R17">
         <v>1.27</v>
@@ -2637,16 +2637,16 @@
         <v>3.4</v>
       </c>
       <c r="T17">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="U17">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="V17">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="W17">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X17">
         <v>1.04</v>
@@ -2655,34 +2655,34 @@
         <v>10</v>
       </c>
       <c r="Z17">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AA17">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="AB17">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AC17">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AD17">
-        <v>2.04</v>
+        <v>2.3</v>
       </c>
       <c r="AE17">
-        <v>1.69</v>
+        <v>1.54</v>
       </c>
       <c r="AF17">
-        <v>1.47</v>
+        <v>1.61</v>
       </c>
       <c r="AG17">
-        <v>2.45</v>
+        <v>2.15</v>
       </c>
       <c r="AH17">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AI17">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AJ17" t="s">
         <v>113</v>
@@ -2702,7 +2702,7 @@
         <v>45</v>
       </c>
       <c r="C18" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D18" t="s">
         <v>54</v>
@@ -2818,7 +2818,7 @@
         <v>46</v>
       </c>
       <c r="C19" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D19" t="s">
         <v>54</v>
@@ -2934,7 +2934,7 @@
         <v>46</v>
       </c>
       <c r="C20" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D20" t="s">
         <v>54</v>
@@ -2961,76 +2961,76 @@
         <v>111</v>
       </c>
       <c r="L20">
-        <v>2.53</v>
+        <v>1.48</v>
       </c>
       <c r="M20">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="N20">
-        <v>2.37</v>
+        <v>5.6</v>
       </c>
       <c r="O20">
-        <v>2</v>
+        <v>1.41</v>
       </c>
       <c r="P20">
-        <v>10</v>
+        <v>11.75</v>
       </c>
       <c r="Q20">
-        <v>1.93</v>
+        <v>3.1</v>
       </c>
       <c r="R20">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S20">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="T20">
-        <v>2.5</v>
+        <v>2.76</v>
       </c>
       <c r="U20">
-        <v>1.46</v>
+        <v>1.35</v>
       </c>
       <c r="V20">
         <v>6</v>
       </c>
       <c r="W20">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X20">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>9.5</v>
+        <v>9.85</v>
       </c>
       <c r="Z20">
         <v>1.25</v>
       </c>
       <c r="AA20">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="AB20">
-        <v>1.66</v>
+        <v>1.87</v>
       </c>
       <c r="AC20">
-        <v>2.08</v>
+        <v>1.84</v>
       </c>
       <c r="AD20">
-        <v>3</v>
+        <v>3.28</v>
       </c>
       <c r="AE20">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AF20">
-        <v>1.63</v>
+        <v>1.91</v>
       </c>
       <c r="AG20">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AH20">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="AI20">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AJ20" t="s">
         <v>113</v>
@@ -3077,76 +3077,76 @@
         <v>111</v>
       </c>
       <c r="L21">
-        <v>1.39</v>
+        <v>2.19</v>
       </c>
       <c r="M21">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="N21">
-        <v>6.9</v>
+        <v>3.48</v>
       </c>
       <c r="O21">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="P21">
-        <v>8.25</v>
+        <v>7</v>
       </c>
       <c r="Q21">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="R21">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="S21">
-        <v>2.62</v>
+        <v>2.51</v>
       </c>
       <c r="T21">
-        <v>2.91</v>
+        <v>3.4</v>
       </c>
       <c r="U21">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="V21">
-        <v>7</v>
+        <v>9.1</v>
       </c>
       <c r="W21">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X21">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Y21">
-        <v>8.5</v>
+        <v>7.19</v>
       </c>
       <c r="Z21">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="AA21">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="AB21">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="AC21">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AD21">
-        <v>3.85</v>
+        <v>4.75</v>
       </c>
       <c r="AE21">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AF21">
-        <v>2.27</v>
+        <v>2.1</v>
       </c>
       <c r="AG21">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AH21">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AI21">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AJ21" t="s">
         <v>113</v>
@@ -3166,7 +3166,7 @@
         <v>46</v>
       </c>
       <c r="C22" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D22" t="s">
         <v>54</v>
@@ -3193,76 +3193,76 @@
         <v>111</v>
       </c>
       <c r="L22">
-        <v>1.5</v>
+        <v>2.53</v>
       </c>
       <c r="M22">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="N22">
-        <v>5.67</v>
+        <v>2.37</v>
       </c>
       <c r="O22">
-        <v>1.41</v>
+        <v>2</v>
       </c>
       <c r="P22">
-        <v>11.75</v>
+        <v>10</v>
       </c>
       <c r="Q22">
-        <v>3.1</v>
+        <v>1.93</v>
       </c>
       <c r="R22">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S22">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="T22">
-        <v>2.76</v>
+        <v>2.5</v>
       </c>
       <c r="U22">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="V22">
         <v>6</v>
       </c>
       <c r="W22">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X22">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y22">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="Z22">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AA22">
-        <v>3.33</v>
+        <v>3.75</v>
       </c>
       <c r="AB22">
-        <v>1.91</v>
+        <v>1.66</v>
       </c>
       <c r="AC22">
-        <v>1.85</v>
+        <v>2.08</v>
       </c>
       <c r="AD22">
-        <v>3.28</v>
+        <v>3</v>
       </c>
       <c r="AE22">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AF22">
-        <v>1.91</v>
+        <v>1.63</v>
       </c>
       <c r="AG22">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AH22">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="AI22">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AJ22" t="s">
         <v>113</v>
@@ -3309,76 +3309,76 @@
         <v>111</v>
       </c>
       <c r="L23">
-        <v>2.2</v>
+        <v>1.44</v>
       </c>
       <c r="M23">
+        <v>4.2</v>
+      </c>
+      <c r="N23">
+        <v>6.86</v>
+      </c>
+      <c r="O23">
+        <v>1.4</v>
+      </c>
+      <c r="P23">
+        <v>8.25</v>
+      </c>
+      <c r="Q23">
+        <v>3.5</v>
+      </c>
+      <c r="R23">
+        <v>1.4</v>
+      </c>
+      <c r="S23">
+        <v>2.8</v>
+      </c>
+      <c r="T23">
+        <v>2.9</v>
+      </c>
+      <c r="U23">
+        <v>1.36</v>
+      </c>
+      <c r="V23">
+        <v>7.5</v>
+      </c>
+      <c r="W23">
+        <v>1.07</v>
+      </c>
+      <c r="X23">
+        <v>1.02</v>
+      </c>
+      <c r="Y23">
+        <v>9.5</v>
+      </c>
+      <c r="Z23">
+        <v>1.33</v>
+      </c>
+      <c r="AA23">
         <v>3.1</v>
       </c>
-      <c r="N23">
-        <v>3.05</v>
-      </c>
-      <c r="O23">
-        <v>1.73</v>
-      </c>
-      <c r="P23">
-        <v>7</v>
-      </c>
-      <c r="Q23">
-        <v>2.5</v>
-      </c>
-      <c r="R23">
-        <v>1.5</v>
-      </c>
-      <c r="S23">
-        <v>2.37</v>
-      </c>
-      <c r="T23">
-        <v>3.45</v>
-      </c>
-      <c r="U23">
-        <v>1.3</v>
-      </c>
-      <c r="V23">
-        <v>9.75</v>
-      </c>
-      <c r="W23">
-        <v>1.05</v>
-      </c>
-      <c r="X23">
+      <c r="AB23">
+        <v>2.09</v>
+      </c>
+      <c r="AC23">
+        <v>1.7</v>
+      </c>
+      <c r="AD23">
+        <v>3.75</v>
+      </c>
+      <c r="AE23">
+        <v>1.25</v>
+      </c>
+      <c r="AF23">
+        <v>2.25</v>
+      </c>
+      <c r="AG23">
+        <v>1.57</v>
+      </c>
+      <c r="AH23">
+        <v>6.7</v>
+      </c>
+      <c r="AI23">
         <v>1.07</v>
-      </c>
-      <c r="Y23">
-        <v>7</v>
-      </c>
-      <c r="Z23">
-        <v>1.48</v>
-      </c>
-      <c r="AA23">
-        <v>2.6</v>
-      </c>
-      <c r="AB23">
-        <v>2.4</v>
-      </c>
-      <c r="AC23">
-        <v>1.53</v>
-      </c>
-      <c r="AD23">
-        <v>4.7</v>
-      </c>
-      <c r="AE23">
-        <v>1.16</v>
-      </c>
-      <c r="AF23">
-        <v>2.18</v>
-      </c>
-      <c r="AG23">
-        <v>1.67</v>
-      </c>
-      <c r="AH23">
-        <v>7.2</v>
-      </c>
-      <c r="AI23">
-        <v>1.06</v>
       </c>
       <c r="AJ23" t="s">
         <v>113</v>
@@ -3398,7 +3398,7 @@
         <v>46</v>
       </c>
       <c r="C24" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D24" t="s">
         <v>54</v>
@@ -3514,7 +3514,7 @@
         <v>47</v>
       </c>
       <c r="C25" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D25" t="s">
         <v>54</v>
@@ -3630,7 +3630,7 @@
         <v>48</v>
       </c>
       <c r="C26" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D26" t="s">
         <v>54</v>
@@ -3657,16 +3657,16 @@
         <v>111</v>
       </c>
       <c r="L26">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="M26">
-        <v>3.25</v>
+        <v>3.41</v>
       </c>
       <c r="N26">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="O26">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="P26">
         <v>10.5</v>
@@ -3675,22 +3675,22 @@
         <v>2.3</v>
       </c>
       <c r="R26">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S26">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="T26">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="U26">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="V26">
         <v>6</v>
       </c>
       <c r="W26">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X26">
         <v>1.05</v>
@@ -3699,34 +3699,34 @@
         <v>9.5</v>
       </c>
       <c r="Z26">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AA26">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="AB26">
-        <v>1.54</v>
+        <v>1.72</v>
       </c>
       <c r="AC26">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AD26">
-        <v>2.62</v>
+        <v>2.95</v>
       </c>
       <c r="AE26">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="AF26">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AG26">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AH26">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="AI26">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AJ26" t="s">
         <v>113</v>
@@ -3746,7 +3746,7 @@
         <v>48</v>
       </c>
       <c r="C27" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D27" t="s">
         <v>54</v>
@@ -3773,76 +3773,76 @@
         <v>111</v>
       </c>
       <c r="L27">
-        <v>1.59</v>
+        <v>1.99</v>
       </c>
       <c r="M27">
-        <v>3.95</v>
+        <v>3.25</v>
       </c>
       <c r="N27">
+        <v>3.25</v>
+      </c>
+      <c r="O27">
+        <v>1.67</v>
+      </c>
+      <c r="P27">
+        <v>10.5</v>
+      </c>
+      <c r="Q27">
+        <v>2.3</v>
+      </c>
+      <c r="R27">
+        <v>1.3</v>
+      </c>
+      <c r="S27">
+        <v>3.4</v>
+      </c>
+      <c r="T27">
+        <v>2.5</v>
+      </c>
+      <c r="U27">
+        <v>1.5</v>
+      </c>
+      <c r="V27">
+        <v>6</v>
+      </c>
+      <c r="W27">
+        <v>1.13</v>
+      </c>
+      <c r="X27">
+        <v>1.05</v>
+      </c>
+      <c r="Y27">
+        <v>9.5</v>
+      </c>
+      <c r="Z27">
+        <v>1.22</v>
+      </c>
+      <c r="AA27">
         <v>4.2</v>
       </c>
-      <c r="O27">
-        <v>1.51</v>
-      </c>
-      <c r="P27">
-        <v>17.5</v>
-      </c>
-      <c r="Q27">
-        <v>2.55</v>
-      </c>
-      <c r="R27">
-        <v>1.2</v>
-      </c>
-      <c r="S27">
-        <v>4.1</v>
-      </c>
-      <c r="T27">
-        <v>1.93</v>
-      </c>
-      <c r="U27">
-        <v>1.77</v>
-      </c>
-      <c r="V27">
-        <v>4</v>
-      </c>
-      <c r="W27">
-        <v>1.21</v>
-      </c>
-      <c r="X27">
-        <v>1.01</v>
-      </c>
-      <c r="Y27">
-        <v>23</v>
-      </c>
-      <c r="Z27">
-        <v>1.11</v>
-      </c>
-      <c r="AA27">
-        <v>6.25</v>
-      </c>
       <c r="AB27">
-        <v>1.36</v>
+        <v>1.54</v>
       </c>
       <c r="AC27">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="AD27">
-        <v>1.9</v>
+        <v>2.62</v>
       </c>
       <c r="AE27">
-        <v>1.8</v>
+        <v>1.48</v>
       </c>
       <c r="AF27">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AG27">
-        <v>2.55</v>
+        <v>2.25</v>
       </c>
       <c r="AH27">
-        <v>3.1</v>
+        <v>4.75</v>
       </c>
       <c r="AI27">
-        <v>1.35</v>
+        <v>1.18</v>
       </c>
       <c r="AJ27" t="s">
         <v>113</v>
@@ -3862,7 +3862,7 @@
         <v>48</v>
       </c>
       <c r="C28" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D28" t="s">
         <v>54</v>
@@ -3978,7 +3978,7 @@
         <v>48</v>
       </c>
       <c r="C29" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D29" t="s">
         <v>54</v>
@@ -4005,76 +4005,76 @@
         <v>111</v>
       </c>
       <c r="L29">
-        <v>1.94</v>
+        <v>1.59</v>
       </c>
       <c r="M29">
-        <v>3.41</v>
+        <v>3.95</v>
       </c>
       <c r="N29">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="O29">
-        <v>1.71</v>
+        <v>1.51</v>
       </c>
       <c r="P29">
-        <v>10.5</v>
+        <v>17.5</v>
       </c>
       <c r="Q29">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="R29">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="S29">
+        <v>4.1</v>
+      </c>
+      <c r="T29">
+        <v>1.93</v>
+      </c>
+      <c r="U29">
+        <v>1.77</v>
+      </c>
+      <c r="V29">
+        <v>4</v>
+      </c>
+      <c r="W29">
+        <v>1.21</v>
+      </c>
+      <c r="X29">
+        <v>1.01</v>
+      </c>
+      <c r="Y29">
+        <v>23</v>
+      </c>
+      <c r="Z29">
+        <v>1.11</v>
+      </c>
+      <c r="AA29">
+        <v>6.25</v>
+      </c>
+      <c r="AB29">
+        <v>1.36</v>
+      </c>
+      <c r="AC29">
+        <v>2.9</v>
+      </c>
+      <c r="AD29">
+        <v>1.9</v>
+      </c>
+      <c r="AE29">
+        <v>1.8</v>
+      </c>
+      <c r="AF29">
+        <v>1.44</v>
+      </c>
+      <c r="AG29">
+        <v>2.55</v>
+      </c>
+      <c r="AH29">
         <v>3.1</v>
       </c>
-      <c r="T29">
-        <v>2.45</v>
-      </c>
-      <c r="U29">
-        <v>1.47</v>
-      </c>
-      <c r="V29">
-        <v>6</v>
-      </c>
-      <c r="W29">
-        <v>1.11</v>
-      </c>
-      <c r="X29">
-        <v>1.05</v>
-      </c>
-      <c r="Y29">
-        <v>9.5</v>
-      </c>
-      <c r="Z29">
-        <v>1.25</v>
-      </c>
-      <c r="AA29">
-        <v>3.8</v>
-      </c>
-      <c r="AB29">
-        <v>1.72</v>
-      </c>
-      <c r="AC29">
-        <v>2</v>
-      </c>
-      <c r="AD29">
-        <v>2.95</v>
-      </c>
-      <c r="AE29">
-        <v>1.38</v>
-      </c>
-      <c r="AF29">
-        <v>1.65</v>
-      </c>
-      <c r="AG29">
-        <v>2.1</v>
-      </c>
-      <c r="AH29">
-        <v>5.5</v>
-      </c>
       <c r="AI29">
-        <v>1.14</v>
+        <v>1.35</v>
       </c>
       <c r="AJ29" t="s">
         <v>113</v>

--- a/jogos_2025-07-16.xlsx
+++ b/jogos_2025-07-16.xlsx
@@ -172,24 +172,24 @@
     <t>USA MLS</t>
   </si>
   <si>
+    <t>USA USL Championship</t>
+  </si>
+  <si>
     <t>USA MLS Next Pro</t>
   </si>
   <si>
-    <t>USA USL Championship</t>
-  </si>
-  <si>
     <t>2025</t>
   </si>
   <si>
     <t>Grêmio</t>
   </si>
   <si>
+    <t>Juventude</t>
+  </si>
+  <si>
     <t>Bahia</t>
   </si>
   <si>
-    <t>Juventude</t>
-  </si>
-  <si>
     <t>Atlético Mineiro</t>
   </si>
   <si>
@@ -208,72 +208,72 @@
     <t>New York RB</t>
   </si>
   <si>
+    <t>Philadelphia Union</t>
+  </si>
+  <si>
+    <t>Orlando City</t>
+  </si>
+  <si>
+    <t>Atlanta United FC</t>
+  </si>
+  <si>
     <t>FC Cincinnati</t>
   </si>
   <si>
+    <t>Charlotte</t>
+  </si>
+  <si>
+    <t>Hartford Athletic</t>
+  </si>
+  <si>
     <t>New York City II</t>
   </si>
   <si>
-    <t>Hartford Athletic</t>
-  </si>
-  <si>
-    <t>Atlanta United FC</t>
-  </si>
-  <si>
-    <t>Orlando City</t>
-  </si>
-  <si>
-    <t>Philadelphia Union</t>
-  </si>
-  <si>
-    <t>Charlotte</t>
-  </si>
-  <si>
     <t>St. Louis City II</t>
   </si>
   <si>
+    <t>Botafogo</t>
+  </si>
+  <si>
+    <t>Minnesota United</t>
+  </si>
+  <si>
     <t>Nashville SC</t>
   </si>
   <si>
+    <t>Houston Dynamo</t>
+  </si>
+  <si>
+    <t>Bragantino</t>
+  </si>
+  <si>
     <t>Tulsa Roughnecks</t>
   </si>
   <si>
-    <t>Bragantino</t>
-  </si>
-  <si>
-    <t>Minnesota United</t>
-  </si>
-  <si>
-    <t>Botafogo</t>
-  </si>
-  <si>
-    <t>Houston Dynamo</t>
-  </si>
-  <si>
     <t>Seattle Sounders</t>
   </si>
   <si>
+    <t>San Diego</t>
+  </si>
+  <si>
+    <t>SJ Earthquakes</t>
+  </si>
+  <si>
     <t>LA Galaxy</t>
   </si>
   <si>
     <t>Portland Timbers</t>
   </si>
   <si>
-    <t>San Diego</t>
-  </si>
-  <si>
-    <t>SJ Earthquakes</t>
-  </si>
-  <si>
     <t>Fortaleza</t>
   </si>
   <si>
+    <t>Vasco da Gama</t>
+  </si>
+  <si>
     <t>Internacional</t>
   </si>
   <si>
-    <t>Vasco da Gama</t>
-  </si>
-  <si>
     <t>Sport Recife</t>
   </si>
   <si>
@@ -292,61 +292,61 @@
     <t>New England Revolution</t>
   </si>
   <si>
+    <t>Montreal Impact</t>
+  </si>
+  <si>
+    <t>New York City</t>
+  </si>
+  <si>
+    <t>Chicago Fire</t>
+  </si>
+  <si>
     <t>Inter Miami</t>
   </si>
   <si>
+    <t>DC United</t>
+  </si>
+  <si>
+    <t>Tampa Bay Rowdies</t>
+  </si>
+  <si>
     <t>Toronto II</t>
   </si>
   <si>
-    <t>Tampa Bay Rowdies</t>
-  </si>
-  <si>
-    <t>Chicago Fire</t>
-  </si>
-  <si>
-    <t>New York City</t>
-  </si>
-  <si>
-    <t>Montreal Impact</t>
-  </si>
-  <si>
-    <t>DC United</t>
-  </si>
-  <si>
     <t>LA Galaxy II</t>
   </si>
   <si>
+    <t>Vitória</t>
+  </si>
+  <si>
+    <t>Los Angeles FC</t>
+  </si>
+  <si>
     <t>Columbus Crew</t>
   </si>
   <si>
+    <t>Vancouver Whitecaps</t>
+  </si>
+  <si>
+    <t>São Paulo</t>
+  </si>
+  <si>
     <t>Monterey Bay</t>
   </si>
   <si>
-    <t>São Paulo</t>
-  </si>
-  <si>
-    <t>Los Angeles FC</t>
-  </si>
-  <si>
-    <t>Vitória</t>
-  </si>
-  <si>
-    <t>Vancouver Whitecaps</t>
-  </si>
-  <si>
     <t>Colorado Rapids</t>
   </si>
   <si>
+    <t>Toronto</t>
+  </si>
+  <si>
+    <t>FC Dallas</t>
+  </si>
+  <si>
     <t>Austin</t>
   </si>
   <si>
     <t>Real Salt Lake</t>
-  </si>
-  <si>
-    <t>Toronto</t>
-  </si>
-  <si>
-    <t>FC Dallas</t>
   </si>
   <si>
     <t>incomplete</t>
@@ -989,40 +989,40 @@
         <v>112</v>
       </c>
       <c r="L3">
-        <v>2.49</v>
+        <v>2.23</v>
       </c>
       <c r="M3">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="N3">
-        <v>3</v>
+        <v>2.79</v>
       </c>
       <c r="O3">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="P3">
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="R3">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S3">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V3">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="W3">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X3">
         <v>0</v>
@@ -1037,10 +1037,10 @@
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="AC3">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -1049,10 +1049,10 @@
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -1105,40 +1105,40 @@
         <v>112</v>
       </c>
       <c r="L4">
-        <v>2.38</v>
+        <v>2.49</v>
       </c>
       <c r="M4">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="N4">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="P4">
         <v>0</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X4">
         <v>0</v>
@@ -1153,22 +1153,22 @@
         <v>0</v>
       </c>
       <c r="AB4">
+        <v>2.35</v>
+      </c>
+      <c r="AC4">
+        <v>1.57</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
         <v>2</v>
       </c>
-      <c r="AC4">
-        <v>1.73</v>
-      </c>
-      <c r="AD4">
-        <v>0</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>0</v>
-      </c>
       <c r="AG4">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH4">
         <v>0</v>
@@ -1218,16 +1218,16 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L5">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="M5">
         <v>4.4</v>
       </c>
       <c r="N5">
-        <v>6.5</v>
+        <v>6.55</v>
       </c>
       <c r="O5">
         <v>1.33</v>
@@ -1453,13 +1453,13 @@
         <v>111</v>
       </c>
       <c r="L7">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="M7">
-        <v>4.5</v>
+        <v>3.93</v>
       </c>
       <c r="N7">
-        <v>8</v>
+        <v>7.3</v>
       </c>
       <c r="O7">
         <v>1.29</v>
@@ -1471,13 +1471,13 @@
         <v>4.33</v>
       </c>
       <c r="R7">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S7">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="T7">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="U7">
         <v>1.36</v>
@@ -1486,43 +1486,43 @@
         <v>8</v>
       </c>
       <c r="W7">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X7">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y7">
-        <v>9.300000000000001</v>
+        <v>9</v>
       </c>
       <c r="Z7">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AA7">
-        <v>2.9</v>
+        <v>3.02</v>
       </c>
       <c r="AB7">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="AC7">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AD7">
-        <v>3.9</v>
+        <v>3.72</v>
       </c>
       <c r="AE7">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AF7">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="AG7">
         <v>1.56</v>
       </c>
       <c r="AH7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AI7">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AJ7" t="s">
         <v>113</v>
@@ -1569,13 +1569,13 @@
         <v>111</v>
       </c>
       <c r="L8">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="M8">
-        <v>3</v>
+        <v>3.09</v>
       </c>
       <c r="N8">
-        <v>3.1</v>
+        <v>2.58</v>
       </c>
       <c r="O8">
         <v>1.91</v>
@@ -1590,55 +1590,55 @@
         <v>1.57</v>
       </c>
       <c r="S8">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="T8">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="U8">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="V8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W8">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X8">
         <v>1.1</v>
       </c>
       <c r="Y8">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="Z8">
         <v>1.5</v>
       </c>
       <c r="AA8">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AB8">
         <v>2.6</v>
       </c>
       <c r="AC8">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AD8">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AE8">
         <v>1.12</v>
       </c>
       <c r="AF8">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AG8">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AH8">
-        <v>9.300000000000001</v>
+        <v>13</v>
       </c>
       <c r="AI8">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AJ8" t="s">
         <v>113</v>
@@ -1685,13 +1685,13 @@
         <v>111</v>
       </c>
       <c r="L9">
-        <v>4.2</v>
+        <v>3.67</v>
       </c>
       <c r="M9">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N9">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="O9">
         <v>2.63</v>
@@ -1703,43 +1703,43 @@
         <v>1.57</v>
       </c>
       <c r="R9">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S9">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="T9">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="U9">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="V9">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W9">
         <v>1.06</v>
       </c>
       <c r="X9">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Y9">
         <v>7.5</v>
       </c>
       <c r="Z9">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="AA9">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="AB9">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AC9">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AD9">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AE9">
         <v>1.2</v>
@@ -1748,10 +1748,10 @@
         <v>2</v>
       </c>
       <c r="AG9">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AH9">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="AI9">
         <v>1.06</v>
@@ -1917,40 +1917,40 @@
         <v>111</v>
       </c>
       <c r="L11">
-        <v>2.06</v>
+        <v>1.38</v>
       </c>
       <c r="M11">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="N11">
-        <v>2.82</v>
+        <v>6</v>
       </c>
       <c r="O11">
-        <v>1.82</v>
+        <v>1.44</v>
       </c>
       <c r="P11">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Q11">
-        <v>2.05</v>
+        <v>2.95</v>
       </c>
       <c r="R11">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S11">
         <v>3.4</v>
       </c>
       <c r="T11">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="U11">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="V11">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="W11">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X11">
         <v>1.04</v>
@@ -1959,34 +1959,34 @@
         <v>10</v>
       </c>
       <c r="Z11">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AA11">
-        <v>4.75</v>
+        <v>4.33</v>
       </c>
       <c r="AB11">
-        <v>1.37</v>
+        <v>1.52</v>
       </c>
       <c r="AC11">
-        <v>2.94</v>
+        <v>2.35</v>
       </c>
       <c r="AD11">
-        <v>2.04</v>
+        <v>2.55</v>
       </c>
       <c r="AE11">
-        <v>1.69</v>
+        <v>1.5</v>
       </c>
       <c r="AF11">
-        <v>1.47</v>
+        <v>1.7</v>
       </c>
       <c r="AG11">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="AH11">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AI11">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AJ11" t="s">
         <v>113</v>
@@ -2006,7 +2006,7 @@
         <v>44</v>
       </c>
       <c r="C12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D12" t="s">
         <v>54</v>
@@ -2033,76 +2033,76 @@
         <v>111</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH12">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AI12">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AJ12" t="s">
         <v>113</v>
@@ -2122,7 +2122,7 @@
         <v>44</v>
       </c>
       <c r="C13" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D13" t="s">
         <v>54</v>
@@ -2149,76 +2149,76 @@
         <v>111</v>
       </c>
       <c r="L13">
-        <v>2.55</v>
+        <v>2</v>
       </c>
       <c r="M13">
-        <v>3.3</v>
+        <v>3.63</v>
       </c>
       <c r="N13">
-        <v>2.49</v>
+        <v>2.91</v>
       </c>
       <c r="O13">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="P13">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Q13">
-        <v>1.92</v>
+        <v>2.15</v>
       </c>
       <c r="R13">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="S13">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="T13">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="U13">
-        <v>1.42</v>
+        <v>1.58</v>
       </c>
       <c r="V13">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W13">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="X13">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y13">
         <v>10</v>
       </c>
       <c r="Z13">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AA13">
-        <v>3.7</v>
+        <v>4.75</v>
       </c>
       <c r="AB13">
-        <v>1.82</v>
+        <v>1.59</v>
       </c>
       <c r="AC13">
-        <v>1.89</v>
+        <v>2.36</v>
       </c>
       <c r="AD13">
-        <v>3.04</v>
+        <v>2.1</v>
       </c>
       <c r="AE13">
-        <v>1.33</v>
+        <v>1.65</v>
       </c>
       <c r="AF13">
-        <v>1.67</v>
+        <v>1.49</v>
       </c>
       <c r="AG13">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="AH13">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="AI13">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="AJ13" t="s">
         <v>113</v>
@@ -2265,22 +2265,22 @@
         <v>111</v>
       </c>
       <c r="L14">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="M14">
-        <v>3.63</v>
+        <v>3.6</v>
       </c>
       <c r="N14">
-        <v>2.91</v>
+        <v>2.82</v>
       </c>
       <c r="O14">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="P14">
         <v>13</v>
       </c>
       <c r="Q14">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="R14">
         <v>1.27</v>
@@ -2292,10 +2292,10 @@
         <v>2.2</v>
       </c>
       <c r="U14">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="V14">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="W14">
         <v>1.15</v>
@@ -2313,22 +2313,22 @@
         <v>4.75</v>
       </c>
       <c r="AB14">
-        <v>1.59</v>
+        <v>1.37</v>
       </c>
       <c r="AC14">
-        <v>2.36</v>
+        <v>2.94</v>
       </c>
       <c r="AD14">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AE14">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="AF14">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="AG14">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AH14">
         <v>4.2</v>
@@ -2381,22 +2381,22 @@
         <v>111</v>
       </c>
       <c r="L15">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="M15">
-        <v>3.55</v>
+        <v>3.81</v>
       </c>
       <c r="N15">
-        <v>3.83</v>
+        <v>4.2</v>
       </c>
       <c r="O15">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="P15">
         <v>13</v>
       </c>
       <c r="Q15">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="R15">
         <v>1.27</v>
@@ -2405,16 +2405,16 @@
         <v>3.4</v>
       </c>
       <c r="T15">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="U15">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="V15">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="W15">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X15">
         <v>1.04</v>
@@ -2423,34 +2423,34 @@
         <v>10</v>
       </c>
       <c r="Z15">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AA15">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="AB15">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AC15">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AD15">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AE15">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AF15">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AG15">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AH15">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AI15">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AJ15" t="s">
         <v>113</v>
@@ -2470,7 +2470,7 @@
         <v>44</v>
       </c>
       <c r="C16" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D16" t="s">
         <v>54</v>
@@ -2497,76 +2497,76 @@
         <v>111</v>
       </c>
       <c r="L16">
-        <v>1.38</v>
+        <v>2.43</v>
       </c>
       <c r="M16">
-        <v>4.3</v>
+        <v>3.45</v>
       </c>
       <c r="N16">
-        <v>6</v>
+        <v>2.52</v>
       </c>
       <c r="O16">
-        <v>1.44</v>
+        <v>1.95</v>
       </c>
       <c r="P16">
         <v>12.5</v>
       </c>
       <c r="Q16">
-        <v>2.95</v>
+        <v>1.92</v>
       </c>
       <c r="R16">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="S16">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="T16">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="U16">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="V16">
-        <v>5</v>
+        <v>6.45</v>
       </c>
       <c r="W16">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="X16">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y16">
         <v>10</v>
       </c>
       <c r="Z16">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AA16">
-        <v>4.33</v>
+        <v>3.6</v>
       </c>
       <c r="AB16">
-        <v>1.52</v>
+        <v>1.73</v>
       </c>
       <c r="AC16">
-        <v>2.35</v>
+        <v>1.91</v>
       </c>
       <c r="AD16">
-        <v>2.55</v>
+        <v>2.92</v>
       </c>
       <c r="AE16">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AF16">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AG16">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AH16">
-        <v>4.33</v>
+        <v>5.3</v>
       </c>
       <c r="AI16">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AJ16" t="s">
         <v>113</v>
@@ -2586,7 +2586,7 @@
         <v>44</v>
       </c>
       <c r="C17" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D17" t="s">
         <v>54</v>
@@ -2613,73 +2613,73 @@
         <v>111</v>
       </c>
       <c r="L17">
-        <v>1.61</v>
+        <v>1.74</v>
       </c>
       <c r="M17">
-        <v>3.81</v>
+        <v>3.7</v>
       </c>
       <c r="N17">
-        <v>4.2</v>
+        <v>3.94</v>
       </c>
       <c r="O17">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="P17">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Q17">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="R17">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="S17">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="T17">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="U17">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="V17">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="W17">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X17">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y17">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z17">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AA17">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="AB17">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AC17">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AD17">
+        <v>2.2</v>
+      </c>
+      <c r="AE17">
+        <v>1.55</v>
+      </c>
+      <c r="AF17">
+        <v>1.5</v>
+      </c>
+      <c r="AG17">
         <v>2.3</v>
       </c>
-      <c r="AE17">
-        <v>1.54</v>
-      </c>
-      <c r="AF17">
-        <v>1.61</v>
-      </c>
-      <c r="AG17">
-        <v>2.15</v>
-      </c>
       <c r="AH17">
-        <v>4.33</v>
+        <v>3.8</v>
       </c>
       <c r="AI17">
         <v>1.2</v>
@@ -2702,7 +2702,7 @@
         <v>45</v>
       </c>
       <c r="C18" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D18" t="s">
         <v>54</v>
@@ -2729,40 +2729,40 @@
         <v>111</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M18">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="P18">
         <v>0</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X18">
         <v>0</v>
@@ -2771,34 +2771,34 @@
         <v>0</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH18">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AI18">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AJ18" t="s">
         <v>113</v>
@@ -2818,7 +2818,7 @@
         <v>46</v>
       </c>
       <c r="C19" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D19" t="s">
         <v>54</v>
@@ -2845,76 +2845,76 @@
         <v>111</v>
       </c>
       <c r="L19">
-        <v>1.98</v>
+        <v>1.51</v>
       </c>
       <c r="M19">
-        <v>3.39</v>
+        <v>3.53</v>
       </c>
       <c r="N19">
-        <v>3.12</v>
+        <v>5.8</v>
       </c>
       <c r="O19">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="P19">
-        <v>11.5</v>
+        <v>8.25</v>
       </c>
       <c r="Q19">
-        <v>2.25</v>
+        <v>3.5</v>
       </c>
       <c r="R19">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="S19">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="T19">
-        <v>2.35</v>
+        <v>3.22</v>
       </c>
       <c r="U19">
-        <v>1.52</v>
+        <v>1.34</v>
       </c>
       <c r="V19">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="W19">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="X19">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y19">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="Z19">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="AA19">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
       <c r="AB19">
-        <v>1.54</v>
+        <v>1.92</v>
       </c>
       <c r="AC19">
-        <v>2.3</v>
+        <v>1.78</v>
       </c>
       <c r="AD19">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="AE19">
-        <v>1.46</v>
+        <v>1.25</v>
       </c>
       <c r="AF19">
-        <v>1.57</v>
+        <v>2.15</v>
       </c>
       <c r="AG19">
-        <v>2.2</v>
+        <v>1.65</v>
       </c>
       <c r="AH19">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="AI19">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="AJ19" t="s">
         <v>113</v>
@@ -2934,7 +2934,7 @@
         <v>46</v>
       </c>
       <c r="C20" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D20" t="s">
         <v>54</v>
@@ -2961,76 +2961,76 @@
         <v>111</v>
       </c>
       <c r="L20">
-        <v>1.48</v>
+        <v>2.53</v>
       </c>
       <c r="M20">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="N20">
-        <v>5.6</v>
+        <v>2.37</v>
       </c>
       <c r="O20">
-        <v>1.41</v>
+        <v>2</v>
       </c>
       <c r="P20">
-        <v>11.75</v>
+        <v>10</v>
       </c>
       <c r="Q20">
-        <v>3.1</v>
+        <v>1.93</v>
       </c>
       <c r="R20">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S20">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="T20">
-        <v>2.76</v>
+        <v>2.5</v>
       </c>
       <c r="U20">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="V20">
         <v>6</v>
       </c>
       <c r="W20">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X20">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y20">
-        <v>9.85</v>
+        <v>9.5</v>
       </c>
       <c r="Z20">
         <v>1.25</v>
       </c>
       <c r="AA20">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="AB20">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="AC20">
-        <v>1.84</v>
+        <v>1.93</v>
       </c>
       <c r="AD20">
-        <v>3.28</v>
+        <v>3</v>
       </c>
       <c r="AE20">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AF20">
-        <v>1.91</v>
+        <v>1.63</v>
       </c>
       <c r="AG20">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AH20">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="AI20">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AJ20" t="s">
         <v>113</v>
@@ -3050,7 +3050,7 @@
         <v>46</v>
       </c>
       <c r="C21" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D21" t="s">
         <v>54</v>
@@ -3077,76 +3077,76 @@
         <v>111</v>
       </c>
       <c r="L21">
-        <v>2.19</v>
+        <v>1.98</v>
       </c>
       <c r="M21">
-        <v>3.2</v>
+        <v>3.39</v>
       </c>
       <c r="N21">
-        <v>3.48</v>
+        <v>3.12</v>
       </c>
       <c r="O21">
         <v>1.73</v>
       </c>
       <c r="P21">
-        <v>7</v>
+        <v>11.5</v>
       </c>
       <c r="Q21">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="R21">
+        <v>1.3</v>
+      </c>
+      <c r="S21">
+        <v>3.2</v>
+      </c>
+      <c r="T21">
+        <v>2.35</v>
+      </c>
+      <c r="U21">
         <v>1.52</v>
       </c>
-      <c r="S21">
-        <v>2.51</v>
-      </c>
-      <c r="T21">
-        <v>3.4</v>
-      </c>
-      <c r="U21">
-        <v>1.27</v>
-      </c>
       <c r="V21">
-        <v>9.1</v>
+        <v>5.5</v>
       </c>
       <c r="W21">
+        <v>1.13</v>
+      </c>
+      <c r="X21">
         <v>1.03</v>
       </c>
-      <c r="X21">
-        <v>1.1</v>
-      </c>
       <c r="Y21">
-        <v>7.19</v>
+        <v>11.5</v>
       </c>
       <c r="Z21">
-        <v>1.43</v>
+        <v>1.2</v>
       </c>
       <c r="AA21">
-        <v>2.6</v>
+        <v>4.1</v>
       </c>
       <c r="AB21">
-        <v>2.4</v>
+        <v>1.54</v>
       </c>
       <c r="AC21">
-        <v>1.53</v>
+        <v>2.3</v>
       </c>
       <c r="AD21">
-        <v>4.75</v>
+        <v>2.7</v>
       </c>
       <c r="AE21">
-        <v>1.17</v>
+        <v>1.46</v>
       </c>
       <c r="AF21">
-        <v>2.1</v>
+        <v>1.57</v>
       </c>
       <c r="AG21">
-        <v>1.74</v>
+        <v>2.2</v>
       </c>
       <c r="AH21">
-        <v>7.2</v>
+        <v>4.5</v>
       </c>
       <c r="AI21">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="AJ21" t="s">
         <v>113</v>
@@ -3193,40 +3193,40 @@
         <v>111</v>
       </c>
       <c r="L22">
-        <v>2.53</v>
+        <v>2.16</v>
       </c>
       <c r="M22">
-        <v>3.3</v>
+        <v>3.21</v>
       </c>
       <c r="N22">
-        <v>2.37</v>
+        <v>2.9</v>
       </c>
       <c r="O22">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="P22">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="Q22">
-        <v>1.93</v>
+        <v>2.15</v>
       </c>
       <c r="R22">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S22">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="T22">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="U22">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="V22">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="W22">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X22">
         <v>1.05</v>
@@ -3235,34 +3235,34 @@
         <v>9.5</v>
       </c>
       <c r="Z22">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AA22">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="AB22">
-        <v>1.66</v>
+        <v>1.82</v>
       </c>
       <c r="AC22">
-        <v>2.08</v>
+        <v>1.88</v>
       </c>
       <c r="AD22">
-        <v>3</v>
+        <v>1.02</v>
       </c>
       <c r="AE22">
-        <v>1.38</v>
+        <v>1.02</v>
       </c>
       <c r="AF22">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="AG22">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH22">
         <v>5.5</v>
       </c>
       <c r="AI22">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AJ22" t="s">
         <v>113</v>
@@ -3309,76 +3309,76 @@
         <v>111</v>
       </c>
       <c r="L23">
-        <v>1.44</v>
+        <v>2.12</v>
       </c>
       <c r="M23">
-        <v>4.2</v>
+        <v>3.09</v>
       </c>
       <c r="N23">
-        <v>6.86</v>
+        <v>3.09</v>
       </c>
       <c r="O23">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="P23">
-        <v>8.25</v>
+        <v>7</v>
       </c>
       <c r="Q23">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="R23">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="S23">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="T23">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="U23">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="V23">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="W23">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="X23">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="Y23">
+        <v>6.5</v>
+      </c>
+      <c r="Z23">
+        <v>1.43</v>
+      </c>
+      <c r="AA23">
+        <v>2.6</v>
+      </c>
+      <c r="AB23">
+        <v>2.4</v>
+      </c>
+      <c r="AC23">
+        <v>1.5</v>
+      </c>
+      <c r="AD23">
+        <v>4.75</v>
+      </c>
+      <c r="AE23">
+        <v>1.18</v>
+      </c>
+      <c r="AF23">
+        <v>2.1</v>
+      </c>
+      <c r="AG23">
+        <v>1.7</v>
+      </c>
+      <c r="AH23">
         <v>9.5</v>
       </c>
-      <c r="Z23">
-        <v>1.33</v>
-      </c>
-      <c r="AA23">
-        <v>3.1</v>
-      </c>
-      <c r="AB23">
-        <v>2.09</v>
-      </c>
-      <c r="AC23">
-        <v>1.7</v>
-      </c>
-      <c r="AD23">
-        <v>3.75</v>
-      </c>
-      <c r="AE23">
-        <v>1.25</v>
-      </c>
-      <c r="AF23">
-        <v>2.25</v>
-      </c>
-      <c r="AG23">
-        <v>1.57</v>
-      </c>
-      <c r="AH23">
-        <v>6.7</v>
-      </c>
       <c r="AI23">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AJ23" t="s">
         <v>113</v>
@@ -3398,7 +3398,7 @@
         <v>46</v>
       </c>
       <c r="C24" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D24" t="s">
         <v>54</v>
@@ -3425,76 +3425,76 @@
         <v>111</v>
       </c>
       <c r="L24">
-        <v>2.16</v>
+        <v>1.52</v>
       </c>
       <c r="M24">
-        <v>3.21</v>
+        <v>3.9</v>
       </c>
       <c r="N24">
-        <v>2.9</v>
+        <v>5.4</v>
       </c>
       <c r="O24">
-        <v>1.82</v>
+        <v>1.41</v>
       </c>
       <c r="P24">
-        <v>9.5</v>
+        <v>11.75</v>
       </c>
       <c r="Q24">
-        <v>2.15</v>
+        <v>3.1</v>
       </c>
       <c r="R24">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S24">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="T24">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="U24">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="V24">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="W24">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X24">
         <v>1.05</v>
       </c>
       <c r="Y24">
-        <v>9.5</v>
+        <v>9.9</v>
       </c>
       <c r="Z24">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AA24">
         <v>3.4</v>
       </c>
       <c r="AB24">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="AC24">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AD24">
-        <v>1.02</v>
+        <v>3.35</v>
       </c>
       <c r="AE24">
-        <v>1.02</v>
+        <v>1.27</v>
       </c>
       <c r="AF24">
-        <v>1.68</v>
+        <v>2.01</v>
       </c>
       <c r="AG24">
-        <v>2.05</v>
+        <v>1.74</v>
       </c>
       <c r="AH24">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="AI24">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AJ24" t="s">
         <v>113</v>
@@ -3657,76 +3657,76 @@
         <v>111</v>
       </c>
       <c r="L26">
-        <v>1.94</v>
+        <v>1.29</v>
       </c>
       <c r="M26">
-        <v>3.41</v>
+        <v>4.8</v>
       </c>
       <c r="N26">
-        <v>3.2</v>
+        <v>7.3</v>
       </c>
       <c r="O26">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="P26">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="Q26">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="R26">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S26">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T26">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="U26">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="V26">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W26">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X26">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y26">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="Z26">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AA26">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AB26">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="AC26">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AD26">
-        <v>2.95</v>
+        <v>2.05</v>
       </c>
       <c r="AE26">
-        <v>1.38</v>
+        <v>1.68</v>
       </c>
       <c r="AF26">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG26">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH26">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AI26">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AJ26" t="s">
         <v>113</v>
@@ -3773,76 +3773,76 @@
         <v>111</v>
       </c>
       <c r="L27">
-        <v>1.99</v>
+        <v>1.59</v>
       </c>
       <c r="M27">
-        <v>3.25</v>
+        <v>3.95</v>
       </c>
       <c r="N27">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="O27">
-        <v>1.67</v>
+        <v>1.51</v>
       </c>
       <c r="P27">
-        <v>10.5</v>
+        <v>17.5</v>
       </c>
       <c r="Q27">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="R27">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="S27">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="T27">
-        <v>2.5</v>
+        <v>1.93</v>
       </c>
       <c r="U27">
-        <v>1.5</v>
+        <v>1.77</v>
       </c>
       <c r="V27">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="W27">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="X27">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y27">
-        <v>9.5</v>
+        <v>23</v>
       </c>
       <c r="Z27">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="AA27">
-        <v>4.2</v>
+        <v>6.25</v>
       </c>
       <c r="AB27">
-        <v>1.54</v>
+        <v>1.34</v>
       </c>
       <c r="AC27">
-        <v>2.3</v>
+        <v>3.09</v>
       </c>
       <c r="AD27">
-        <v>2.62</v>
+        <v>1.9</v>
       </c>
       <c r="AE27">
-        <v>1.48</v>
+        <v>1.8</v>
       </c>
       <c r="AF27">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AG27">
-        <v>2.25</v>
+        <v>2.55</v>
       </c>
       <c r="AH27">
-        <v>4.75</v>
+        <v>3.1</v>
       </c>
       <c r="AI27">
-        <v>1.18</v>
+        <v>1.35</v>
       </c>
       <c r="AJ27" t="s">
         <v>113</v>
@@ -3889,76 +3889,76 @@
         <v>111</v>
       </c>
       <c r="L28">
-        <v>1.29</v>
+        <v>1.94</v>
       </c>
       <c r="M28">
-        <v>4.8</v>
+        <v>3.41</v>
       </c>
       <c r="N28">
-        <v>7.3</v>
+        <v>3.2</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AB28">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="AC28">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AD28">
-        <v>2.05</v>
+        <v>2.95</v>
       </c>
       <c r="AE28">
-        <v>1.68</v>
+        <v>1.38</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH28">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AI28">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AJ28" t="s">
         <v>113</v>
@@ -4005,76 +4005,76 @@
         <v>111</v>
       </c>
       <c r="L29">
-        <v>1.59</v>
+        <v>1.99</v>
       </c>
       <c r="M29">
-        <v>3.95</v>
+        <v>3.25</v>
       </c>
       <c r="N29">
+        <v>3.25</v>
+      </c>
+      <c r="O29">
+        <v>1.67</v>
+      </c>
+      <c r="P29">
+        <v>10.5</v>
+      </c>
+      <c r="Q29">
+        <v>2.3</v>
+      </c>
+      <c r="R29">
+        <v>1.3</v>
+      </c>
+      <c r="S29">
+        <v>3.4</v>
+      </c>
+      <c r="T29">
+        <v>2.5</v>
+      </c>
+      <c r="U29">
+        <v>1.5</v>
+      </c>
+      <c r="V29">
+        <v>6</v>
+      </c>
+      <c r="W29">
+        <v>1.13</v>
+      </c>
+      <c r="X29">
+        <v>1.05</v>
+      </c>
+      <c r="Y29">
+        <v>9.5</v>
+      </c>
+      <c r="Z29">
+        <v>1.22</v>
+      </c>
+      <c r="AA29">
         <v>4.2</v>
       </c>
-      <c r="O29">
-        <v>1.51</v>
-      </c>
-      <c r="P29">
-        <v>17.5</v>
-      </c>
-      <c r="Q29">
-        <v>2.55</v>
-      </c>
-      <c r="R29">
-        <v>1.2</v>
-      </c>
-      <c r="S29">
-        <v>4.1</v>
-      </c>
-      <c r="T29">
-        <v>1.93</v>
-      </c>
-      <c r="U29">
-        <v>1.77</v>
-      </c>
-      <c r="V29">
-        <v>4</v>
-      </c>
-      <c r="W29">
-        <v>1.21</v>
-      </c>
-      <c r="X29">
-        <v>1.01</v>
-      </c>
-      <c r="Y29">
-        <v>23</v>
-      </c>
-      <c r="Z29">
-        <v>1.11</v>
-      </c>
-      <c r="AA29">
-        <v>6.25</v>
-      </c>
       <c r="AB29">
-        <v>1.36</v>
+        <v>1.54</v>
       </c>
       <c r="AC29">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="AD29">
-        <v>1.9</v>
+        <v>2.62</v>
       </c>
       <c r="AE29">
-        <v>1.8</v>
+        <v>1.48</v>
       </c>
       <c r="AF29">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AG29">
-        <v>2.55</v>
+        <v>2.25</v>
       </c>
       <c r="AH29">
-        <v>3.1</v>
+        <v>4.75</v>
       </c>
       <c r="AI29">
-        <v>1.35</v>
+        <v>1.18</v>
       </c>
       <c r="AJ29" t="s">
         <v>113</v>

--- a/jogos_2025-07-16.xlsx
+++ b/jogos_2025-07-16.xlsx
@@ -172,12 +172,12 @@
     <t>USA MLS</t>
   </si>
   <si>
+    <t>USA MLS Next Pro</t>
+  </si>
+  <si>
     <t>USA USL Championship</t>
   </si>
   <si>
-    <t>USA MLS Next Pro</t>
-  </si>
-  <si>
     <t>2025</t>
   </si>
   <si>
@@ -208,60 +208,60 @@
     <t>New York RB</t>
   </si>
   <si>
+    <t>New York City II</t>
+  </si>
+  <si>
+    <t>Atlanta United FC</t>
+  </si>
+  <si>
+    <t>Hartford Athletic</t>
+  </si>
+  <si>
+    <t>Charlotte</t>
+  </si>
+  <si>
+    <t>Orlando City</t>
+  </si>
+  <si>
+    <t>FC Cincinnati</t>
+  </si>
+  <si>
     <t>Philadelphia Union</t>
   </si>
   <si>
-    <t>Orlando City</t>
-  </si>
-  <si>
-    <t>Atlanta United FC</t>
-  </si>
-  <si>
-    <t>FC Cincinnati</t>
-  </si>
-  <si>
-    <t>Charlotte</t>
-  </si>
-  <si>
-    <t>Hartford Athletic</t>
-  </si>
-  <si>
-    <t>New York City II</t>
-  </si>
-  <si>
     <t>St. Louis City II</t>
   </si>
   <si>
+    <t>Houston Dynamo</t>
+  </si>
+  <si>
+    <t>Minnesota United</t>
+  </si>
+  <si>
+    <t>Tulsa Roughnecks</t>
+  </si>
+  <si>
+    <t>Bragantino</t>
+  </si>
+  <si>
+    <t>Nashville SC</t>
+  </si>
+  <si>
     <t>Botafogo</t>
   </si>
   <si>
-    <t>Minnesota United</t>
-  </si>
-  <si>
-    <t>Nashville SC</t>
-  </si>
-  <si>
-    <t>Houston Dynamo</t>
-  </si>
-  <si>
-    <t>Bragantino</t>
-  </si>
-  <si>
-    <t>Tulsa Roughnecks</t>
-  </si>
-  <si>
     <t>Seattle Sounders</t>
   </si>
   <si>
+    <t>LA Galaxy</t>
+  </si>
+  <si>
     <t>San Diego</t>
   </si>
   <si>
     <t>SJ Earthquakes</t>
   </si>
   <si>
-    <t>LA Galaxy</t>
-  </si>
-  <si>
     <t>Portland Timbers</t>
   </si>
   <si>
@@ -292,58 +292,58 @@
     <t>New England Revolution</t>
   </si>
   <si>
+    <t>Toronto II</t>
+  </si>
+  <si>
+    <t>Chicago Fire</t>
+  </si>
+  <si>
+    <t>Tampa Bay Rowdies</t>
+  </si>
+  <si>
+    <t>DC United</t>
+  </si>
+  <si>
+    <t>New York City</t>
+  </si>
+  <si>
+    <t>Inter Miami</t>
+  </si>
+  <si>
     <t>Montreal Impact</t>
   </si>
   <si>
-    <t>New York City</t>
-  </si>
-  <si>
-    <t>Chicago Fire</t>
-  </si>
-  <si>
-    <t>Inter Miami</t>
-  </si>
-  <si>
-    <t>DC United</t>
-  </si>
-  <si>
-    <t>Tampa Bay Rowdies</t>
-  </si>
-  <si>
-    <t>Toronto II</t>
-  </si>
-  <si>
     <t>LA Galaxy II</t>
   </si>
   <si>
+    <t>Vancouver Whitecaps</t>
+  </si>
+  <si>
+    <t>Los Angeles FC</t>
+  </si>
+  <si>
+    <t>Monterey Bay</t>
+  </si>
+  <si>
+    <t>São Paulo</t>
+  </si>
+  <si>
+    <t>Columbus Crew</t>
+  </si>
+  <si>
     <t>Vitória</t>
   </si>
   <si>
-    <t>Los Angeles FC</t>
-  </si>
-  <si>
-    <t>Columbus Crew</t>
-  </si>
-  <si>
-    <t>Vancouver Whitecaps</t>
-  </si>
-  <si>
-    <t>São Paulo</t>
-  </si>
-  <si>
-    <t>Monterey Bay</t>
-  </si>
-  <si>
     <t>Colorado Rapids</t>
   </si>
   <si>
+    <t>Austin</t>
+  </si>
+  <si>
     <t>Toronto</t>
   </si>
   <si>
     <t>FC Dallas</t>
-  </si>
-  <si>
-    <t>Austin</t>
   </si>
   <si>
     <t>Real Salt Lake</t>
@@ -995,7 +995,7 @@
         <v>3.3</v>
       </c>
       <c r="N3">
-        <v>2.79</v>
+        <v>3.3</v>
       </c>
       <c r="O3">
         <v>0</v>
@@ -1108,7 +1108,7 @@
         <v>2.49</v>
       </c>
       <c r="M4">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="N4">
         <v>2.9</v>
@@ -1224,7 +1224,7 @@
         <v>1.49</v>
       </c>
       <c r="M5">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="N5">
         <v>6.55</v>
@@ -1453,13 +1453,13 @@
         <v>111</v>
       </c>
       <c r="L7">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="M7">
-        <v>3.93</v>
+        <v>4.1</v>
       </c>
       <c r="N7">
-        <v>7.3</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="O7">
         <v>1.29</v>
@@ -1477,7 +1477,7 @@
         <v>2.7</v>
       </c>
       <c r="T7">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="U7">
         <v>1.36</v>
@@ -1486,43 +1486,43 @@
         <v>8</v>
       </c>
       <c r="W7">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X7">
         <v>1</v>
       </c>
       <c r="Y7">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="Z7">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AA7">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="AB7">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AC7">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AD7">
-        <v>3.72</v>
+        <v>3.62</v>
       </c>
       <c r="AE7">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AF7">
-        <v>2.47</v>
+        <v>2.25</v>
       </c>
       <c r="AG7">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AH7">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="AI7">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AJ7" t="s">
         <v>113</v>
@@ -1569,13 +1569,13 @@
         <v>111</v>
       </c>
       <c r="L8">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="M8">
-        <v>3.09</v>
+        <v>2.75</v>
       </c>
       <c r="N8">
-        <v>2.58</v>
+        <v>3.25</v>
       </c>
       <c r="O8">
         <v>1.91</v>
@@ -1587,58 +1587,58 @@
         <v>2.2</v>
       </c>
       <c r="R8">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="S8">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="T8">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="U8">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="V8">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="W8">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X8">
+        <v>1.13</v>
+      </c>
+      <c r="Y8">
+        <v>5.75</v>
+      </c>
+      <c r="Z8">
+        <v>1.6</v>
+      </c>
+      <c r="AA8">
+        <v>2.29</v>
+      </c>
+      <c r="AB8">
+        <v>2.96</v>
+      </c>
+      <c r="AC8">
+        <v>1.42</v>
+      </c>
+      <c r="AD8">
+        <v>5.25</v>
+      </c>
+      <c r="AE8">
         <v>1.1</v>
       </c>
-      <c r="Y8">
-        <v>6.5</v>
-      </c>
-      <c r="Z8">
-        <v>1.5</v>
-      </c>
-      <c r="AA8">
-        <v>2.4</v>
-      </c>
-      <c r="AB8">
-        <v>2.6</v>
-      </c>
-      <c r="AC8">
-        <v>1.43</v>
-      </c>
-      <c r="AD8">
-        <v>5</v>
-      </c>
-      <c r="AE8">
-        <v>1.12</v>
-      </c>
       <c r="AF8">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AG8">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AH8">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AI8">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="AJ8" t="s">
         <v>113</v>
@@ -1685,13 +1685,13 @@
         <v>111</v>
       </c>
       <c r="L9">
-        <v>3.67</v>
+        <v>3.9</v>
       </c>
       <c r="M9">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="N9">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="O9">
         <v>2.63</v>
@@ -1703,58 +1703,58 @@
         <v>1.57</v>
       </c>
       <c r="R9">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="S9">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="T9">
-        <v>3.4</v>
+        <v>3.46</v>
       </c>
       <c r="U9">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="V9">
-        <v>8.300000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W9">
         <v>1.06</v>
       </c>
       <c r="X9">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="Y9">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="Z9">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="AA9">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="AB9">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AC9">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AD9">
-        <v>3.9</v>
+        <v>4.45</v>
       </c>
       <c r="AE9">
         <v>1.2</v>
       </c>
       <c r="AF9">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AG9">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AH9">
         <v>9.5</v>
       </c>
       <c r="AI9">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AJ9" t="s">
         <v>113</v>
@@ -1890,7 +1890,7 @@
         <v>44</v>
       </c>
       <c r="C11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D11" t="s">
         <v>54</v>
@@ -1917,73 +1917,73 @@
         <v>111</v>
       </c>
       <c r="L11">
-        <v>1.38</v>
+        <v>1.63</v>
       </c>
       <c r="M11">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="N11">
-        <v>6</v>
+        <v>3.9</v>
       </c>
       <c r="O11">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="P11">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="Q11">
-        <v>2.95</v>
+        <v>2.4</v>
       </c>
       <c r="R11">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="S11">
-        <v>3.4</v>
+        <v>3.22</v>
       </c>
       <c r="T11">
+        <v>2.2</v>
+      </c>
+      <c r="U11">
+        <v>1.5</v>
+      </c>
+      <c r="V11">
+        <v>4.75</v>
+      </c>
+      <c r="W11">
+        <v>1.15</v>
+      </c>
+      <c r="X11">
+        <v>1.01</v>
+      </c>
+      <c r="Y11">
+        <v>11</v>
+      </c>
+      <c r="Z11">
+        <v>1.18</v>
+      </c>
+      <c r="AA11">
+        <v>4.5</v>
+      </c>
+      <c r="AB11">
+        <v>1.53</v>
+      </c>
+      <c r="AC11">
         <v>2.25</v>
       </c>
-      <c r="U11">
-        <v>1.57</v>
-      </c>
-      <c r="V11">
-        <v>5</v>
-      </c>
-      <c r="W11">
-        <v>1.14</v>
-      </c>
-      <c r="X11">
-        <v>1.04</v>
-      </c>
-      <c r="Y11">
-        <v>10</v>
-      </c>
-      <c r="Z11">
-        <v>1.2</v>
-      </c>
-      <c r="AA11">
-        <v>4.33</v>
-      </c>
-      <c r="AB11">
-        <v>1.52</v>
-      </c>
-      <c r="AC11">
-        <v>2.35</v>
-      </c>
       <c r="AD11">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="AE11">
         <v>1.5</v>
       </c>
       <c r="AF11">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AG11">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AH11">
-        <v>4.33</v>
+        <v>3.9</v>
       </c>
       <c r="AI11">
         <v>1.2</v>
@@ -2033,22 +2033,22 @@
         <v>111</v>
       </c>
       <c r="L12">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="M12">
-        <v>3.55</v>
+        <v>3.63</v>
       </c>
       <c r="N12">
-        <v>3.83</v>
+        <v>2.91</v>
       </c>
       <c r="O12">
-        <v>1.52</v>
+        <v>1.75</v>
       </c>
       <c r="P12">
         <v>13</v>
       </c>
       <c r="Q12">
-        <v>2.65</v>
+        <v>2.15</v>
       </c>
       <c r="R12">
         <v>1.27</v>
@@ -2057,13 +2057,13 @@
         <v>3.4</v>
       </c>
       <c r="T12">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="U12">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="V12">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="W12">
         <v>1.15</v>
@@ -2081,22 +2081,22 @@
         <v>4.75</v>
       </c>
       <c r="AB12">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="AC12">
-        <v>2.27</v>
+        <v>2.36</v>
       </c>
       <c r="AD12">
+        <v>2.1</v>
+      </c>
+      <c r="AE12">
+        <v>1.65</v>
+      </c>
+      <c r="AF12">
+        <v>1.49</v>
+      </c>
+      <c r="AG12">
         <v>2.4</v>
-      </c>
-      <c r="AE12">
-        <v>1.57</v>
-      </c>
-      <c r="AF12">
-        <v>1.57</v>
-      </c>
-      <c r="AG12">
-        <v>2.25</v>
       </c>
       <c r="AH12">
         <v>4.2</v>
@@ -2122,7 +2122,7 @@
         <v>44</v>
       </c>
       <c r="C13" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D13" t="s">
         <v>54</v>
@@ -2149,76 +2149,76 @@
         <v>111</v>
       </c>
       <c r="L13">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="M13">
-        <v>3.63</v>
+        <v>3.3</v>
       </c>
       <c r="N13">
-        <v>2.91</v>
+        <v>2.39</v>
       </c>
       <c r="O13">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="P13">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Q13">
-        <v>2.15</v>
+        <v>1.92</v>
       </c>
       <c r="R13">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="S13">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="T13">
-        <v>2.2</v>
+        <v>2.63</v>
       </c>
       <c r="U13">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="V13">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="W13">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X13">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y13">
         <v>10</v>
       </c>
       <c r="Z13">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AA13">
-        <v>4.75</v>
+        <v>3.6</v>
       </c>
       <c r="AB13">
-        <v>1.59</v>
+        <v>1.79</v>
       </c>
       <c r="AC13">
-        <v>2.36</v>
+        <v>1.85</v>
       </c>
       <c r="AD13">
-        <v>2.1</v>
+        <v>2.96</v>
       </c>
       <c r="AE13">
-        <v>1.65</v>
+        <v>1.38</v>
       </c>
       <c r="AF13">
-        <v>1.49</v>
+        <v>1.62</v>
       </c>
       <c r="AG13">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="AH13">
-        <v>4.2</v>
+        <v>5.46</v>
       </c>
       <c r="AI13">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AJ13" t="s">
         <v>113</v>
@@ -2265,22 +2265,22 @@
         <v>111</v>
       </c>
       <c r="L14">
-        <v>2.06</v>
+        <v>1.61</v>
       </c>
       <c r="M14">
-        <v>3.6</v>
+        <v>3.81</v>
       </c>
       <c r="N14">
-        <v>2.82</v>
+        <v>4.2</v>
       </c>
       <c r="O14">
-        <v>1.82</v>
+        <v>1.53</v>
       </c>
       <c r="P14">
         <v>13</v>
       </c>
       <c r="Q14">
-        <v>2.05</v>
+        <v>2.6</v>
       </c>
       <c r="R14">
         <v>1.27</v>
@@ -2289,16 +2289,16 @@
         <v>3.4</v>
       </c>
       <c r="T14">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="U14">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="V14">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="W14">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X14">
         <v>1.04</v>
@@ -2307,34 +2307,34 @@
         <v>10</v>
       </c>
       <c r="Z14">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AA14">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="AB14">
-        <v>1.37</v>
+        <v>1.57</v>
       </c>
       <c r="AC14">
-        <v>2.94</v>
+        <v>2.25</v>
       </c>
       <c r="AD14">
-        <v>2.04</v>
+        <v>2.3</v>
       </c>
       <c r="AE14">
-        <v>1.69</v>
+        <v>1.54</v>
       </c>
       <c r="AF14">
-        <v>1.47</v>
+        <v>1.61</v>
       </c>
       <c r="AG14">
-        <v>2.45</v>
+        <v>2.15</v>
       </c>
       <c r="AH14">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AI14">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AJ14" t="s">
         <v>113</v>
@@ -2381,22 +2381,22 @@
         <v>111</v>
       </c>
       <c r="L15">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="M15">
-        <v>3.81</v>
+        <v>3.55</v>
       </c>
       <c r="N15">
-        <v>4.2</v>
+        <v>3.83</v>
       </c>
       <c r="O15">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="P15">
         <v>13</v>
       </c>
       <c r="Q15">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="R15">
         <v>1.27</v>
@@ -2405,16 +2405,16 @@
         <v>3.4</v>
       </c>
       <c r="T15">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="U15">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="V15">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="W15">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X15">
         <v>1.04</v>
@@ -2423,34 +2423,34 @@
         <v>10</v>
       </c>
       <c r="Z15">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AA15">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="AB15">
+        <v>1.56</v>
+      </c>
+      <c r="AC15">
+        <v>2.27</v>
+      </c>
+      <c r="AD15">
+        <v>2.4</v>
+      </c>
+      <c r="AE15">
         <v>1.57</v>
       </c>
-      <c r="AC15">
+      <c r="AF15">
+        <v>1.57</v>
+      </c>
+      <c r="AG15">
         <v>2.25</v>
       </c>
-      <c r="AD15">
-        <v>2.3</v>
-      </c>
-      <c r="AE15">
-        <v>1.54</v>
-      </c>
-      <c r="AF15">
-        <v>1.61</v>
-      </c>
-      <c r="AG15">
-        <v>2.15</v>
-      </c>
       <c r="AH15">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="AI15">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AJ15" t="s">
         <v>113</v>
@@ -2470,7 +2470,7 @@
         <v>44</v>
       </c>
       <c r="C16" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D16" t="s">
         <v>54</v>
@@ -2497,76 +2497,76 @@
         <v>111</v>
       </c>
       <c r="L16">
-        <v>2.43</v>
+        <v>2.06</v>
       </c>
       <c r="M16">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="N16">
-        <v>2.52</v>
+        <v>2.82</v>
       </c>
       <c r="O16">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="P16">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Q16">
-        <v>1.92</v>
+        <v>2.05</v>
       </c>
       <c r="R16">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="S16">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="T16">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="U16">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="V16">
-        <v>6.45</v>
+        <v>4.8</v>
       </c>
       <c r="W16">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="X16">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y16">
         <v>10</v>
       </c>
       <c r="Z16">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AA16">
-        <v>3.6</v>
+        <v>4.75</v>
       </c>
       <c r="AB16">
-        <v>1.73</v>
+        <v>1.37</v>
       </c>
       <c r="AC16">
-        <v>1.91</v>
+        <v>2.94</v>
       </c>
       <c r="AD16">
-        <v>2.92</v>
+        <v>2.04</v>
       </c>
       <c r="AE16">
-        <v>1.33</v>
+        <v>1.69</v>
       </c>
       <c r="AF16">
-        <v>1.62</v>
+        <v>1.47</v>
       </c>
       <c r="AG16">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="AH16">
-        <v>5.3</v>
+        <v>4.2</v>
       </c>
       <c r="AI16">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AJ16" t="s">
         <v>113</v>
@@ -2586,7 +2586,7 @@
         <v>44</v>
       </c>
       <c r="C17" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D17" t="s">
         <v>54</v>
@@ -2613,73 +2613,73 @@
         <v>111</v>
       </c>
       <c r="L17">
-        <v>1.74</v>
+        <v>1.38</v>
       </c>
       <c r="M17">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="N17">
-        <v>3.94</v>
+        <v>6</v>
       </c>
       <c r="O17">
+        <v>1.44</v>
+      </c>
+      <c r="P17">
+        <v>12.5</v>
+      </c>
+      <c r="Q17">
+        <v>2.95</v>
+      </c>
+      <c r="R17">
+        <v>1.28</v>
+      </c>
+      <c r="S17">
+        <v>3.4</v>
+      </c>
+      <c r="T17">
+        <v>2.25</v>
+      </c>
+      <c r="U17">
         <v>1.57</v>
       </c>
-      <c r="P17">
-        <v>0</v>
-      </c>
-      <c r="Q17">
-        <v>2.4</v>
-      </c>
-      <c r="R17">
-        <v>1.22</v>
-      </c>
-      <c r="S17">
-        <v>3.6</v>
-      </c>
-      <c r="T17">
-        <v>2.2</v>
-      </c>
-      <c r="U17">
-        <v>1.55</v>
-      </c>
       <c r="V17">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="W17">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z17">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AA17">
-        <v>4.3</v>
+        <v>4.33</v>
       </c>
       <c r="AB17">
+        <v>1.52</v>
+      </c>
+      <c r="AC17">
+        <v>2.35</v>
+      </c>
+      <c r="AD17">
+        <v>2.55</v>
+      </c>
+      <c r="AE17">
         <v>1.5</v>
       </c>
-      <c r="AC17">
-        <v>2.3</v>
-      </c>
-      <c r="AD17">
-        <v>2.2</v>
-      </c>
-      <c r="AE17">
-        <v>1.55</v>
-      </c>
       <c r="AF17">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AG17">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AH17">
-        <v>3.8</v>
+        <v>4.33</v>
       </c>
       <c r="AI17">
         <v>1.2</v>
@@ -2702,7 +2702,7 @@
         <v>45</v>
       </c>
       <c r="C18" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D18" t="s">
         <v>54</v>
@@ -2729,10 +2729,10 @@
         <v>111</v>
       </c>
       <c r="L18">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="M18">
-        <v>4.3</v>
+        <v>3.99</v>
       </c>
       <c r="N18">
         <v>4.6</v>
@@ -2747,10 +2747,10 @@
         <v>2.75</v>
       </c>
       <c r="R18">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="S18">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="T18">
         <v>2</v>
@@ -2771,22 +2771,22 @@
         <v>0</v>
       </c>
       <c r="Z18">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AA18">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AB18">
         <v>1.37</v>
       </c>
       <c r="AC18">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="AD18">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AE18">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AF18">
         <v>1.45</v>
@@ -2795,10 +2795,10 @@
         <v>2.45</v>
       </c>
       <c r="AH18">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AI18">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AJ18" t="s">
         <v>113</v>
@@ -2818,7 +2818,7 @@
         <v>46</v>
       </c>
       <c r="C19" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D19" t="s">
         <v>54</v>
@@ -2845,76 +2845,76 @@
         <v>111</v>
       </c>
       <c r="L19">
-        <v>1.51</v>
+        <v>2.16</v>
       </c>
       <c r="M19">
-        <v>3.53</v>
+        <v>3.21</v>
       </c>
       <c r="N19">
-        <v>5.8</v>
+        <v>2.9</v>
       </c>
       <c r="O19">
-        <v>1.4</v>
+        <v>1.82</v>
       </c>
       <c r="P19">
-        <v>8.25</v>
+        <v>9.5</v>
       </c>
       <c r="Q19">
-        <v>3.5</v>
+        <v>2.15</v>
       </c>
       <c r="R19">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="S19">
-        <v>2.67</v>
+        <v>2.87</v>
       </c>
       <c r="T19">
-        <v>3.22</v>
+        <v>2.6</v>
       </c>
       <c r="U19">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="V19">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="W19">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X19">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y19">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="Z19">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AA19">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="AB19">
-        <v>1.92</v>
+        <v>1.82</v>
       </c>
       <c r="AC19">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="AD19">
-        <v>3.6</v>
+        <v>1.02</v>
       </c>
       <c r="AE19">
-        <v>1.25</v>
+        <v>1.02</v>
       </c>
       <c r="AF19">
-        <v>2.15</v>
+        <v>1.68</v>
       </c>
       <c r="AG19">
-        <v>1.65</v>
+        <v>2.05</v>
       </c>
       <c r="AH19">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="AI19">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AJ19" t="s">
         <v>113</v>
@@ -3050,7 +3050,7 @@
         <v>46</v>
       </c>
       <c r="C21" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D21" t="s">
         <v>54</v>
@@ -3077,76 +3077,76 @@
         <v>111</v>
       </c>
       <c r="L21">
-        <v>1.98</v>
+        <v>1.51</v>
       </c>
       <c r="M21">
-        <v>3.39</v>
+        <v>3.78</v>
       </c>
       <c r="N21">
-        <v>3.12</v>
+        <v>5.82</v>
       </c>
       <c r="O21">
-        <v>1.73</v>
+        <v>1.41</v>
       </c>
       <c r="P21">
-        <v>11.5</v>
+        <v>11.75</v>
       </c>
       <c r="Q21">
-        <v>2.25</v>
+        <v>3.1</v>
       </c>
       <c r="R21">
+        <v>1.36</v>
+      </c>
+      <c r="S21">
+        <v>2.9</v>
+      </c>
+      <c r="T21">
+        <v>2.89</v>
+      </c>
+      <c r="U21">
+        <v>1.37</v>
+      </c>
+      <c r="V21">
+        <v>7</v>
+      </c>
+      <c r="W21">
+        <v>1.03</v>
+      </c>
+      <c r="X21">
+        <v>1.05</v>
+      </c>
+      <c r="Y21">
+        <v>9</v>
+      </c>
+      <c r="Z21">
         <v>1.3</v>
       </c>
-      <c r="S21">
-        <v>3.2</v>
-      </c>
-      <c r="T21">
-        <v>2.35</v>
-      </c>
-      <c r="U21">
-        <v>1.52</v>
-      </c>
-      <c r="V21">
-        <v>5.5</v>
-      </c>
-      <c r="W21">
-        <v>1.13</v>
-      </c>
-      <c r="X21">
-        <v>1.03</v>
-      </c>
-      <c r="Y21">
-        <v>11.5</v>
-      </c>
-      <c r="Z21">
-        <v>1.2</v>
-      </c>
       <c r="AA21">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="AB21">
-        <v>1.54</v>
+        <v>2.07</v>
       </c>
       <c r="AC21">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="AD21">
-        <v>2.7</v>
+        <v>3.45</v>
       </c>
       <c r="AE21">
-        <v>1.46</v>
+        <v>1.29</v>
       </c>
       <c r="AF21">
-        <v>1.57</v>
+        <v>2.04</v>
       </c>
       <c r="AG21">
-        <v>2.2</v>
+        <v>1.79</v>
       </c>
       <c r="AH21">
-        <v>4.5</v>
+        <v>6.9</v>
       </c>
       <c r="AI21">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AJ21" t="s">
         <v>113</v>
@@ -3166,7 +3166,7 @@
         <v>46</v>
       </c>
       <c r="C22" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D22" t="s">
         <v>54</v>
@@ -3193,76 +3193,76 @@
         <v>111</v>
       </c>
       <c r="L22">
-        <v>2.16</v>
+        <v>2.28</v>
       </c>
       <c r="M22">
-        <v>3.21</v>
+        <v>3</v>
       </c>
       <c r="N22">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="O22">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="P22">
+        <v>7</v>
+      </c>
+      <c r="Q22">
+        <v>2.5</v>
+      </c>
+      <c r="R22">
+        <v>1.6</v>
+      </c>
+      <c r="S22">
+        <v>2.23</v>
+      </c>
+      <c r="T22">
+        <v>3.5</v>
+      </c>
+      <c r="U22">
+        <v>1.22</v>
+      </c>
+      <c r="V22">
+        <v>9.1</v>
+      </c>
+      <c r="W22">
+        <v>1</v>
+      </c>
+      <c r="X22">
+        <v>1.14</v>
+      </c>
+      <c r="Y22">
+        <v>6</v>
+      </c>
+      <c r="Z22">
+        <v>1.55</v>
+      </c>
+      <c r="AA22">
+        <v>2.25</v>
+      </c>
+      <c r="AB22">
+        <v>2.7</v>
+      </c>
+      <c r="AC22">
+        <v>1.4</v>
+      </c>
+      <c r="AD22">
+        <v>5.95</v>
+      </c>
+      <c r="AE22">
+        <v>1.12</v>
+      </c>
+      <c r="AF22">
+        <v>2.25</v>
+      </c>
+      <c r="AG22">
+        <v>1.57</v>
+      </c>
+      <c r="AH22">
         <v>9.5</v>
       </c>
-      <c r="Q22">
-        <v>2.15</v>
-      </c>
-      <c r="R22">
-        <v>1.36</v>
-      </c>
-      <c r="S22">
-        <v>2.87</v>
-      </c>
-      <c r="T22">
-        <v>2.6</v>
-      </c>
-      <c r="U22">
-        <v>1.43</v>
-      </c>
-      <c r="V22">
-        <v>6.5</v>
-      </c>
-      <c r="W22">
-        <v>1.1</v>
-      </c>
-      <c r="X22">
-        <v>1.05</v>
-      </c>
-      <c r="Y22">
-        <v>9.5</v>
-      </c>
-      <c r="Z22">
-        <v>1.27</v>
-      </c>
-      <c r="AA22">
-        <v>3.4</v>
-      </c>
-      <c r="AB22">
-        <v>1.82</v>
-      </c>
-      <c r="AC22">
-        <v>1.88</v>
-      </c>
-      <c r="AD22">
-        <v>1.02</v>
-      </c>
-      <c r="AE22">
-        <v>1.02</v>
-      </c>
-      <c r="AF22">
-        <v>1.68</v>
-      </c>
-      <c r="AG22">
-        <v>2.05</v>
-      </c>
-      <c r="AH22">
-        <v>5.5</v>
-      </c>
       <c r="AI22">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="AJ22" t="s">
         <v>113</v>
@@ -3282,7 +3282,7 @@
         <v>46</v>
       </c>
       <c r="C23" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D23" t="s">
         <v>54</v>
@@ -3309,76 +3309,76 @@
         <v>111</v>
       </c>
       <c r="L23">
-        <v>2.12</v>
+        <v>1.98</v>
       </c>
       <c r="M23">
-        <v>3.09</v>
+        <v>3.39</v>
       </c>
       <c r="N23">
-        <v>3.09</v>
+        <v>3.12</v>
       </c>
       <c r="O23">
         <v>1.73</v>
       </c>
       <c r="P23">
-        <v>7</v>
+        <v>11.5</v>
       </c>
       <c r="Q23">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="R23">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="S23">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="T23">
-        <v>3.3</v>
+        <v>2.35</v>
       </c>
       <c r="U23">
-        <v>1.29</v>
+        <v>1.52</v>
       </c>
       <c r="V23">
-        <v>9</v>
+        <v>5.5</v>
       </c>
       <c r="W23">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="X23">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="Y23">
-        <v>6.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z23">
-        <v>1.43</v>
+        <v>1.2</v>
       </c>
       <c r="AA23">
-        <v>2.6</v>
+        <v>4.1</v>
       </c>
       <c r="AB23">
-        <v>2.4</v>
+        <v>1.54</v>
       </c>
       <c r="AC23">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="AD23">
-        <v>4.75</v>
+        <v>2.7</v>
       </c>
       <c r="AE23">
+        <v>1.46</v>
+      </c>
+      <c r="AF23">
+        <v>1.57</v>
+      </c>
+      <c r="AG23">
+        <v>2.2</v>
+      </c>
+      <c r="AH23">
+        <v>4.5</v>
+      </c>
+      <c r="AI23">
         <v>1.18</v>
-      </c>
-      <c r="AF23">
-        <v>2.1</v>
-      </c>
-      <c r="AG23">
-        <v>1.7</v>
-      </c>
-      <c r="AH23">
-        <v>9.5</v>
-      </c>
-      <c r="AI23">
-        <v>1.05</v>
       </c>
       <c r="AJ23" t="s">
         <v>113</v>
@@ -3398,7 +3398,7 @@
         <v>46</v>
       </c>
       <c r="C24" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D24" t="s">
         <v>54</v>
@@ -3425,76 +3425,76 @@
         <v>111</v>
       </c>
       <c r="L24">
-        <v>1.52</v>
+        <v>1.39</v>
       </c>
       <c r="M24">
-        <v>3.9</v>
+        <v>4.52</v>
       </c>
       <c r="N24">
-        <v>5.4</v>
+        <v>6.9</v>
       </c>
       <c r="O24">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P24">
-        <v>11.75</v>
+        <v>8.25</v>
       </c>
       <c r="Q24">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="R24">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="S24">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="T24">
-        <v>2.8</v>
+        <v>3.17</v>
       </c>
       <c r="U24">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="V24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W24">
         <v>1.07</v>
       </c>
       <c r="X24">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y24">
-        <v>9.9</v>
+        <v>10.5</v>
       </c>
       <c r="Z24">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AA24">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="AB24">
-        <v>1.9</v>
+        <v>2.12</v>
       </c>
       <c r="AC24">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AD24">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="AE24">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AF24">
-        <v>2.01</v>
+        <v>2.4</v>
       </c>
       <c r="AG24">
-        <v>1.74</v>
+        <v>1.53</v>
       </c>
       <c r="AH24">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="AI24">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AJ24" t="s">
         <v>113</v>
@@ -3657,76 +3657,76 @@
         <v>111</v>
       </c>
       <c r="L26">
-        <v>1.29</v>
+        <v>1.94</v>
       </c>
       <c r="M26">
-        <v>4.8</v>
+        <v>3.41</v>
       </c>
       <c r="N26">
-        <v>7.3</v>
+        <v>3.2</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AB26">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="AC26">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AD26">
-        <v>2.05</v>
+        <v>2.95</v>
       </c>
       <c r="AE26">
-        <v>1.68</v>
+        <v>1.38</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH26">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AI26">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AJ26" t="s">
         <v>113</v>
@@ -3773,76 +3773,76 @@
         <v>111</v>
       </c>
       <c r="L27">
-        <v>1.59</v>
+        <v>1.29</v>
       </c>
       <c r="M27">
-        <v>3.95</v>
+        <v>4.8</v>
       </c>
       <c r="N27">
-        <v>4.2</v>
+        <v>7.3</v>
       </c>
       <c r="O27">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="P27">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="Q27">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="R27">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="S27">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="T27">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="U27">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="V27">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W27">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="X27">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y27">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="Z27">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AA27">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="AB27">
-        <v>1.34</v>
+        <v>1.57</v>
       </c>
       <c r="AC27">
-        <v>3.09</v>
+        <v>2.4</v>
       </c>
       <c r="AD27">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AE27">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="AF27">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AG27">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AH27">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AI27">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AJ27" t="s">
         <v>113</v>
@@ -3889,76 +3889,76 @@
         <v>111</v>
       </c>
       <c r="L28">
-        <v>1.94</v>
+        <v>1.59</v>
       </c>
       <c r="M28">
-        <v>3.41</v>
+        <v>3.95</v>
       </c>
       <c r="N28">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="O28">
-        <v>1.71</v>
+        <v>1.51</v>
       </c>
       <c r="P28">
-        <v>10.5</v>
+        <v>17.5</v>
       </c>
       <c r="Q28">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="R28">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="S28">
+        <v>4.1</v>
+      </c>
+      <c r="T28">
+        <v>1.93</v>
+      </c>
+      <c r="U28">
+        <v>1.77</v>
+      </c>
+      <c r="V28">
+        <v>4</v>
+      </c>
+      <c r="W28">
+        <v>1.21</v>
+      </c>
+      <c r="X28">
+        <v>1.01</v>
+      </c>
+      <c r="Y28">
+        <v>23</v>
+      </c>
+      <c r="Z28">
+        <v>1.11</v>
+      </c>
+      <c r="AA28">
+        <v>6.25</v>
+      </c>
+      <c r="AB28">
+        <v>1.34</v>
+      </c>
+      <c r="AC28">
+        <v>3.09</v>
+      </c>
+      <c r="AD28">
+        <v>1.9</v>
+      </c>
+      <c r="AE28">
+        <v>1.8</v>
+      </c>
+      <c r="AF28">
+        <v>1.44</v>
+      </c>
+      <c r="AG28">
+        <v>2.55</v>
+      </c>
+      <c r="AH28">
         <v>3.1</v>
       </c>
-      <c r="T28">
-        <v>2.45</v>
-      </c>
-      <c r="U28">
-        <v>1.47</v>
-      </c>
-      <c r="V28">
-        <v>6</v>
-      </c>
-      <c r="W28">
-        <v>1.11</v>
-      </c>
-      <c r="X28">
-        <v>1.05</v>
-      </c>
-      <c r="Y28">
-        <v>9.5</v>
-      </c>
-      <c r="Z28">
-        <v>1.25</v>
-      </c>
-      <c r="AA28">
-        <v>3.8</v>
-      </c>
-      <c r="AB28">
-        <v>1.72</v>
-      </c>
-      <c r="AC28">
-        <v>2</v>
-      </c>
-      <c r="AD28">
-        <v>2.95</v>
-      </c>
-      <c r="AE28">
-        <v>1.38</v>
-      </c>
-      <c r="AF28">
-        <v>1.65</v>
-      </c>
-      <c r="AG28">
-        <v>2.1</v>
-      </c>
-      <c r="AH28">
-        <v>5.5</v>
-      </c>
       <c r="AI28">
-        <v>1.14</v>
+        <v>1.35</v>
       </c>
       <c r="AJ28" t="s">
         <v>113</v>

--- a/jogos_2025-07-16.xlsx
+++ b/jogos_2025-07-16.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="116">
   <si>
     <t>Date</t>
   </si>
@@ -172,27 +172,27 @@
     <t>USA MLS</t>
   </si>
   <si>
+    <t>USA USL Championship</t>
+  </si>
+  <si>
     <t>USA MLS Next Pro</t>
   </si>
   <si>
-    <t>USA USL Championship</t>
-  </si>
-  <si>
     <t>2025</t>
   </si>
   <si>
     <t>Grêmio</t>
   </si>
   <si>
+    <t>Atlético Mineiro</t>
+  </si>
+  <si>
     <t>Juventude</t>
   </si>
   <si>
     <t>Bahia</t>
   </si>
   <si>
-    <t>Atlético Mineiro</t>
-  </si>
-  <si>
     <t>Fredrikstad</t>
   </si>
   <si>
@@ -205,78 +205,78 @@
     <t>Santos</t>
   </si>
   <si>
+    <t>Philadelphia Union</t>
+  </si>
+  <si>
+    <t>FC Cincinnati</t>
+  </si>
+  <si>
+    <t>Hartford Athletic</t>
+  </si>
+  <si>
+    <t>Orlando City</t>
+  </si>
+  <si>
+    <t>Charlotte</t>
+  </si>
+  <si>
     <t>New York RB</t>
   </si>
   <si>
+    <t>Atlanta United FC</t>
+  </si>
+  <si>
     <t>New York City II</t>
   </si>
   <si>
-    <t>Atlanta United FC</t>
-  </si>
-  <si>
-    <t>Hartford Athletic</t>
-  </si>
-  <si>
-    <t>Charlotte</t>
-  </si>
-  <si>
-    <t>Orlando City</t>
-  </si>
-  <si>
-    <t>FC Cincinnati</t>
-  </si>
-  <si>
-    <t>Philadelphia Union</t>
-  </si>
-  <si>
     <t>St. Louis City II</t>
   </si>
   <si>
+    <t>Bragantino</t>
+  </si>
+  <si>
+    <t>Tulsa Roughnecks</t>
+  </si>
+  <si>
+    <t>Botafogo</t>
+  </si>
+  <si>
     <t>Houston Dynamo</t>
   </si>
   <si>
+    <t>Nashville SC</t>
+  </si>
+  <si>
     <t>Minnesota United</t>
   </si>
   <si>
-    <t>Tulsa Roughnecks</t>
-  </si>
-  <si>
-    <t>Bragantino</t>
-  </si>
-  <si>
-    <t>Nashville SC</t>
-  </si>
-  <si>
-    <t>Botafogo</t>
-  </si>
-  <si>
     <t>Seattle Sounders</t>
   </si>
   <si>
+    <t>Portland Timbers</t>
+  </si>
+  <si>
+    <t>San Diego</t>
+  </si>
+  <si>
     <t>LA Galaxy</t>
   </si>
   <si>
-    <t>San Diego</t>
-  </si>
-  <si>
     <t>SJ Earthquakes</t>
   </si>
   <si>
-    <t>Portland Timbers</t>
-  </si>
-  <si>
     <t>Fortaleza</t>
   </si>
   <si>
+    <t>Sport Recife</t>
+  </si>
+  <si>
     <t>Vasco da Gama</t>
   </si>
   <si>
     <t>Internacional</t>
   </si>
   <si>
-    <t>Sport Recife</t>
-  </si>
-  <si>
     <t>FK Bodo - Glimt</t>
   </si>
   <si>
@@ -289,73 +289,79 @@
     <t>Flamengo</t>
   </si>
   <si>
+    <t>Montreal Impact</t>
+  </si>
+  <si>
+    <t>Inter Miami</t>
+  </si>
+  <si>
+    <t>Tampa Bay Rowdies</t>
+  </si>
+  <si>
+    <t>New York City</t>
+  </si>
+  <si>
+    <t>DC United</t>
+  </si>
+  <si>
     <t>New England Revolution</t>
   </si>
   <si>
+    <t>Chicago Fire</t>
+  </si>
+  <si>
     <t>Toronto II</t>
   </si>
   <si>
-    <t>Chicago Fire</t>
-  </si>
-  <si>
-    <t>Tampa Bay Rowdies</t>
-  </si>
-  <si>
-    <t>DC United</t>
-  </si>
-  <si>
-    <t>New York City</t>
-  </si>
-  <si>
-    <t>Inter Miami</t>
-  </si>
-  <si>
-    <t>Montreal Impact</t>
-  </si>
-  <si>
     <t>LA Galaxy II</t>
   </si>
   <si>
+    <t>São Paulo</t>
+  </si>
+  <si>
+    <t>Monterey Bay</t>
+  </si>
+  <si>
+    <t>Vitória</t>
+  </si>
+  <si>
     <t>Vancouver Whitecaps</t>
   </si>
   <si>
+    <t>Columbus Crew</t>
+  </si>
+  <si>
     <t>Los Angeles FC</t>
   </si>
   <si>
-    <t>Monterey Bay</t>
-  </si>
-  <si>
-    <t>São Paulo</t>
-  </si>
-  <si>
-    <t>Columbus Crew</t>
-  </si>
-  <si>
-    <t>Vitória</t>
-  </si>
-  <si>
     <t>Colorado Rapids</t>
   </si>
   <si>
+    <t>Real Salt Lake</t>
+  </si>
+  <si>
+    <t>Toronto</t>
+  </si>
+  <si>
     <t>Austin</t>
   </si>
   <si>
-    <t>Toronto</t>
-  </si>
-  <si>
     <t>FC Dallas</t>
   </si>
   <si>
-    <t>Real Salt Lake</t>
-  </si>
-  <si>
     <t>incomplete</t>
   </si>
   <si>
     <t>suspended</t>
   </si>
   <si>
+    <t>complete</t>
+  </si>
+  <si>
     <t>[]</t>
+  </si>
+  <si>
+    <t>['87']</t>
   </si>
 </sst>
 </file>
@@ -945,10 +951,10 @@
         <v>0</v>
       </c>
       <c r="AJ2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AK2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AL2" s="3">
         <v>45854.45833333334</v>
@@ -989,40 +995,40 @@
         <v>112</v>
       </c>
       <c r="L3">
-        <v>2.23</v>
+        <v>1.49</v>
       </c>
       <c r="M3">
-        <v>3.3</v>
+        <v>5.2</v>
       </c>
       <c r="N3">
-        <v>3.3</v>
+        <v>6.55</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P3">
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X3">
         <v>0</v>
@@ -1037,10 +1043,10 @@
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC3">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -1049,10 +1055,10 @@
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -1061,10 +1067,10 @@
         <v>0</v>
       </c>
       <c r="AJ3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AK3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AL3" s="3">
         <v>45854.5</v>
@@ -1105,40 +1111,40 @@
         <v>112</v>
       </c>
       <c r="L4">
-        <v>2.49</v>
+        <v>2.23</v>
       </c>
       <c r="M4">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N4">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="O4">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="P4">
         <v>0</v>
       </c>
       <c r="Q4">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="R4">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S4">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T4">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V4">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="W4">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X4">
         <v>0</v>
@@ -1153,10 +1159,10 @@
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="AC4">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AD4">
         <v>0</v>
@@ -1165,10 +1171,10 @@
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG4">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AH4">
         <v>0</v>
@@ -1177,10 +1183,10 @@
         <v>0</v>
       </c>
       <c r="AJ4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AK4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AL4" s="3">
         <v>45854.5</v>
@@ -1221,40 +1227,40 @@
         <v>112</v>
       </c>
       <c r="L5">
-        <v>1.49</v>
+        <v>2.49</v>
       </c>
       <c r="M5">
-        <v>5.2</v>
+        <v>3.1</v>
       </c>
       <c r="N5">
-        <v>6.55</v>
+        <v>2.9</v>
       </c>
       <c r="O5">
-        <v>1.33</v>
+        <v>1.83</v>
       </c>
       <c r="P5">
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="R5">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="S5">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="T5">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="U5">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="V5">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="W5">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X5">
         <v>0</v>
@@ -1269,10 +1275,10 @@
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="AC5">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AD5">
         <v>0</v>
@@ -1281,10 +1287,10 @@
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AG5">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AH5">
         <v>0</v>
@@ -1293,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AJ5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AK5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AL5" s="3">
         <v>45854.5</v>
@@ -1325,7 +1331,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -1334,7 +1340,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="L6">
         <v>4.1</v>
@@ -1409,10 +1415,10 @@
         <v>1.09</v>
       </c>
       <c r="AJ6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AK6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AL6" s="3">
         <v>45854.54166666666</v>
@@ -1525,10 +1531,10 @@
         <v>1.08</v>
       </c>
       <c r="AJ7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AK7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AL7" s="3">
         <v>45854.79166666666</v>
@@ -1641,10 +1647,10 @@
         <v>1.03</v>
       </c>
       <c r="AJ8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AK8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AL8" s="3">
         <v>45854.8125</v>
@@ -1757,10 +1763,10 @@
         <v>1.05</v>
       </c>
       <c r="AJ9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AK9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AL9" s="3">
         <v>45854.83333333334</v>
@@ -1801,64 +1807,64 @@
         <v>111</v>
       </c>
       <c r="L10">
-        <v>1.74</v>
+        <v>1.38</v>
       </c>
       <c r="M10">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="N10">
-        <v>3.87</v>
+        <v>6</v>
       </c>
       <c r="O10">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="P10">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="Q10">
+        <v>2.95</v>
+      </c>
+      <c r="R10">
+        <v>1.28</v>
+      </c>
+      <c r="S10">
+        <v>3.4</v>
+      </c>
+      <c r="T10">
+        <v>2.25</v>
+      </c>
+      <c r="U10">
+        <v>1.57</v>
+      </c>
+      <c r="V10">
+        <v>5</v>
+      </c>
+      <c r="W10">
+        <v>1.14</v>
+      </c>
+      <c r="X10">
+        <v>1.04</v>
+      </c>
+      <c r="Y10">
+        <v>10</v>
+      </c>
+      <c r="Z10">
+        <v>1.2</v>
+      </c>
+      <c r="AA10">
+        <v>4.33</v>
+      </c>
+      <c r="AB10">
+        <v>1.52</v>
+      </c>
+      <c r="AC10">
+        <v>2.35</v>
+      </c>
+      <c r="AD10">
         <v>2.55</v>
       </c>
-      <c r="R10">
-        <v>1.33</v>
-      </c>
-      <c r="S10">
-        <v>3</v>
-      </c>
-      <c r="T10">
-        <v>2.5</v>
-      </c>
-      <c r="U10">
-        <v>1.46</v>
-      </c>
-      <c r="V10">
-        <v>6</v>
-      </c>
-      <c r="W10">
-        <v>1.11</v>
-      </c>
-      <c r="X10">
-        <v>1.05</v>
-      </c>
-      <c r="Y10">
-        <v>9.5</v>
-      </c>
-      <c r="Z10">
-        <v>1.25</v>
-      </c>
-      <c r="AA10">
-        <v>3.8</v>
-      </c>
-      <c r="AB10">
-        <v>1.68</v>
-      </c>
-      <c r="AC10">
-        <v>2.05</v>
-      </c>
-      <c r="AD10">
-        <v>2.95</v>
-      </c>
       <c r="AE10">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AF10">
         <v>1.7</v>
@@ -1867,16 +1873,16 @@
         <v>2</v>
       </c>
       <c r="AH10">
-        <v>5.5</v>
+        <v>4.33</v>
       </c>
       <c r="AI10">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AJ10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AK10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AL10" s="3">
         <v>45854.85416666666</v>
@@ -1890,7 +1896,7 @@
         <v>44</v>
       </c>
       <c r="C11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D11" t="s">
         <v>54</v>
@@ -1917,82 +1923,82 @@
         <v>111</v>
       </c>
       <c r="L11">
-        <v>1.63</v>
+        <v>2.06</v>
       </c>
       <c r="M11">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="N11">
-        <v>3.9</v>
+        <v>2.82</v>
       </c>
       <c r="O11">
-        <v>1.57</v>
+        <v>1.82</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q11">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="R11">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="S11">
-        <v>3.22</v>
+        <v>3.4</v>
       </c>
       <c r="T11">
         <v>2.2</v>
       </c>
       <c r="U11">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="V11">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="W11">
         <v>1.15</v>
       </c>
       <c r="X11">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y11">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Z11">
         <v>1.18</v>
       </c>
       <c r="AA11">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="AB11">
-        <v>1.53</v>
+        <v>1.37</v>
       </c>
       <c r="AC11">
-        <v>2.25</v>
+        <v>2.94</v>
       </c>
       <c r="AD11">
+        <v>2.04</v>
+      </c>
+      <c r="AE11">
+        <v>1.69</v>
+      </c>
+      <c r="AF11">
+        <v>1.47</v>
+      </c>
+      <c r="AG11">
         <v>2.45</v>
       </c>
-      <c r="AE11">
-        <v>1.5</v>
-      </c>
-      <c r="AF11">
-        <v>1.55</v>
-      </c>
-      <c r="AG11">
-        <v>2.2</v>
-      </c>
       <c r="AH11">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="AI11">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AJ11" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AK11" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AL11" s="3">
         <v>45854.85416666666</v>
@@ -2006,7 +2012,7 @@
         <v>44</v>
       </c>
       <c r="C12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D12" t="s">
         <v>54</v>
@@ -2033,82 +2039,82 @@
         <v>111</v>
       </c>
       <c r="L12">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="M12">
-        <v>3.63</v>
+        <v>3.3</v>
       </c>
       <c r="N12">
-        <v>2.91</v>
+        <v>2.39</v>
       </c>
       <c r="O12">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="P12">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Q12">
-        <v>2.15</v>
+        <v>1.92</v>
       </c>
       <c r="R12">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="S12">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="T12">
-        <v>2.2</v>
+        <v>2.63</v>
       </c>
       <c r="U12">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="V12">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="W12">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X12">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y12">
         <v>10</v>
       </c>
       <c r="Z12">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AA12">
-        <v>4.75</v>
+        <v>3.6</v>
       </c>
       <c r="AB12">
-        <v>1.59</v>
+        <v>1.79</v>
       </c>
       <c r="AC12">
-        <v>2.36</v>
+        <v>1.85</v>
       </c>
       <c r="AD12">
-        <v>2.1</v>
+        <v>2.96</v>
       </c>
       <c r="AE12">
-        <v>1.65</v>
+        <v>1.38</v>
       </c>
       <c r="AF12">
-        <v>1.49</v>
+        <v>1.62</v>
       </c>
       <c r="AG12">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="AH12">
-        <v>4.2</v>
+        <v>5.46</v>
       </c>
       <c r="AI12">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AJ12" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AK12" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AL12" s="3">
         <v>45854.85416666666</v>
@@ -2122,7 +2128,7 @@
         <v>44</v>
       </c>
       <c r="C13" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D13" t="s">
         <v>54</v>
@@ -2149,82 +2155,82 @@
         <v>111</v>
       </c>
       <c r="L13">
-        <v>2.33</v>
+        <v>1.73</v>
       </c>
       <c r="M13">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="N13">
-        <v>2.39</v>
+        <v>3.83</v>
       </c>
       <c r="O13">
-        <v>1.95</v>
+        <v>1.52</v>
       </c>
       <c r="P13">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Q13">
-        <v>1.92</v>
+        <v>2.65</v>
       </c>
       <c r="R13">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="S13">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="T13">
-        <v>2.63</v>
+        <v>2.15</v>
       </c>
       <c r="U13">
-        <v>1.46</v>
+        <v>1.6</v>
       </c>
       <c r="V13">
-        <v>6.5</v>
+        <v>4.8</v>
       </c>
       <c r="W13">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="X13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y13">
         <v>10</v>
       </c>
       <c r="Z13">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AA13">
-        <v>3.6</v>
+        <v>4.75</v>
       </c>
       <c r="AB13">
-        <v>1.79</v>
+        <v>1.56</v>
       </c>
       <c r="AC13">
-        <v>1.85</v>
+        <v>2.27</v>
       </c>
       <c r="AD13">
-        <v>2.96</v>
+        <v>2.4</v>
       </c>
       <c r="AE13">
-        <v>1.38</v>
+        <v>1.57</v>
       </c>
       <c r="AF13">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG13">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AH13">
-        <v>5.46</v>
+        <v>4.2</v>
       </c>
       <c r="AI13">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AJ13" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AK13" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AL13" s="3">
         <v>45854.85416666666</v>
@@ -2337,10 +2343,10 @@
         <v>1.2</v>
       </c>
       <c r="AJ14" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AK14" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AL14" s="3">
         <v>45854.85416666666</v>
@@ -2381,82 +2387,82 @@
         <v>111</v>
       </c>
       <c r="L15">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="M15">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="N15">
-        <v>3.83</v>
+        <v>3.87</v>
       </c>
       <c r="O15">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="P15">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="Q15">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="R15">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="S15">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="T15">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="U15">
-        <v>1.6</v>
+        <v>1.46</v>
       </c>
       <c r="V15">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="W15">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X15">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y15">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="Z15">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AA15">
-        <v>4.75</v>
+        <v>3.8</v>
       </c>
       <c r="AB15">
-        <v>1.56</v>
+        <v>1.68</v>
       </c>
       <c r="AC15">
-        <v>2.27</v>
+        <v>2.05</v>
       </c>
       <c r="AD15">
-        <v>2.4</v>
+        <v>2.95</v>
       </c>
       <c r="AE15">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AF15">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AG15">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AH15">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="AI15">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AJ15" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AK15" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AL15" s="3">
         <v>45854.85416666666</v>
@@ -2497,22 +2503,22 @@
         <v>111</v>
       </c>
       <c r="L16">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="M16">
-        <v>3.6</v>
+        <v>3.63</v>
       </c>
       <c r="N16">
-        <v>2.82</v>
+        <v>2.91</v>
       </c>
       <c r="O16">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="P16">
         <v>13</v>
       </c>
       <c r="Q16">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="R16">
         <v>1.27</v>
@@ -2524,10 +2530,10 @@
         <v>2.2</v>
       </c>
       <c r="U16">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="V16">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="W16">
         <v>1.15</v>
@@ -2545,22 +2551,22 @@
         <v>4.75</v>
       </c>
       <c r="AB16">
-        <v>1.37</v>
+        <v>1.59</v>
       </c>
       <c r="AC16">
-        <v>2.94</v>
+        <v>2.36</v>
       </c>
       <c r="AD16">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AE16">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AF16">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="AG16">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AH16">
         <v>4.2</v>
@@ -2569,10 +2575,10 @@
         <v>1.22</v>
       </c>
       <c r="AJ16" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AK16" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AL16" s="3">
         <v>45854.85416666666</v>
@@ -2586,7 +2592,7 @@
         <v>44</v>
       </c>
       <c r="C17" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D17" t="s">
         <v>54</v>
@@ -2613,82 +2619,82 @@
         <v>111</v>
       </c>
       <c r="L17">
-        <v>1.38</v>
+        <v>1.63</v>
       </c>
       <c r="M17">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="N17">
-        <v>6</v>
+        <v>3.9</v>
       </c>
       <c r="O17">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="P17">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="Q17">
-        <v>2.95</v>
+        <v>2.4</v>
       </c>
       <c r="R17">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="S17">
-        <v>3.4</v>
+        <v>3.22</v>
       </c>
       <c r="T17">
+        <v>2.2</v>
+      </c>
+      <c r="U17">
+        <v>1.5</v>
+      </c>
+      <c r="V17">
+        <v>4.75</v>
+      </c>
+      <c r="W17">
+        <v>1.15</v>
+      </c>
+      <c r="X17">
+        <v>1.01</v>
+      </c>
+      <c r="Y17">
+        <v>11</v>
+      </c>
+      <c r="Z17">
+        <v>1.18</v>
+      </c>
+      <c r="AA17">
+        <v>4.5</v>
+      </c>
+      <c r="AB17">
+        <v>1.53</v>
+      </c>
+      <c r="AC17">
         <v>2.25</v>
       </c>
-      <c r="U17">
-        <v>1.57</v>
-      </c>
-      <c r="V17">
-        <v>5</v>
-      </c>
-      <c r="W17">
-        <v>1.14</v>
-      </c>
-      <c r="X17">
-        <v>1.04</v>
-      </c>
-      <c r="Y17">
-        <v>10</v>
-      </c>
-      <c r="Z17">
-        <v>1.2</v>
-      </c>
-      <c r="AA17">
-        <v>4.33</v>
-      </c>
-      <c r="AB17">
-        <v>1.52</v>
-      </c>
-      <c r="AC17">
-        <v>2.35</v>
-      </c>
       <c r="AD17">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="AE17">
         <v>1.5</v>
       </c>
       <c r="AF17">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AG17">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AH17">
-        <v>4.33</v>
+        <v>3.9</v>
       </c>
       <c r="AI17">
         <v>1.2</v>
       </c>
       <c r="AJ17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AK17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AL17" s="3">
         <v>45854.85416666666</v>
@@ -2702,7 +2708,7 @@
         <v>45</v>
       </c>
       <c r="C18" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D18" t="s">
         <v>54</v>
@@ -2801,10 +2807,10 @@
         <v>1.25</v>
       </c>
       <c r="AJ18" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AK18" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AL18" s="3">
         <v>45854.875</v>
@@ -2818,7 +2824,7 @@
         <v>46</v>
       </c>
       <c r="C19" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D19" t="s">
         <v>54</v>
@@ -2845,82 +2851,82 @@
         <v>111</v>
       </c>
       <c r="L19">
-        <v>2.16</v>
+        <v>2.28</v>
       </c>
       <c r="M19">
-        <v>3.21</v>
+        <v>3</v>
       </c>
       <c r="N19">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="O19">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="P19">
+        <v>7</v>
+      </c>
+      <c r="Q19">
+        <v>2.5</v>
+      </c>
+      <c r="R19">
+        <v>1.6</v>
+      </c>
+      <c r="S19">
+        <v>2.23</v>
+      </c>
+      <c r="T19">
+        <v>3.5</v>
+      </c>
+      <c r="U19">
+        <v>1.22</v>
+      </c>
+      <c r="V19">
+        <v>9.1</v>
+      </c>
+      <c r="W19">
+        <v>1</v>
+      </c>
+      <c r="X19">
+        <v>1.14</v>
+      </c>
+      <c r="Y19">
+        <v>6</v>
+      </c>
+      <c r="Z19">
+        <v>1.55</v>
+      </c>
+      <c r="AA19">
+        <v>2.25</v>
+      </c>
+      <c r="AB19">
+        <v>2.7</v>
+      </c>
+      <c r="AC19">
+        <v>1.4</v>
+      </c>
+      <c r="AD19">
+        <v>5.95</v>
+      </c>
+      <c r="AE19">
+        <v>1.12</v>
+      </c>
+      <c r="AF19">
+        <v>2.25</v>
+      </c>
+      <c r="AG19">
+        <v>1.57</v>
+      </c>
+      <c r="AH19">
         <v>9.5</v>
       </c>
-      <c r="Q19">
-        <v>2.15</v>
-      </c>
-      <c r="R19">
-        <v>1.36</v>
-      </c>
-      <c r="S19">
-        <v>2.87</v>
-      </c>
-      <c r="T19">
-        <v>2.6</v>
-      </c>
-      <c r="U19">
-        <v>1.43</v>
-      </c>
-      <c r="V19">
-        <v>6.5</v>
-      </c>
-      <c r="W19">
-        <v>1.1</v>
-      </c>
-      <c r="X19">
-        <v>1.05</v>
-      </c>
-      <c r="Y19">
-        <v>9.5</v>
-      </c>
-      <c r="Z19">
-        <v>1.27</v>
-      </c>
-      <c r="AA19">
-        <v>3.4</v>
-      </c>
-      <c r="AB19">
-        <v>1.82</v>
-      </c>
-      <c r="AC19">
-        <v>1.88</v>
-      </c>
-      <c r="AD19">
-        <v>1.02</v>
-      </c>
-      <c r="AE19">
-        <v>1.02</v>
-      </c>
-      <c r="AF19">
-        <v>1.68</v>
-      </c>
-      <c r="AG19">
-        <v>2.05</v>
-      </c>
-      <c r="AH19">
-        <v>5.5</v>
-      </c>
       <c r="AI19">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="AJ19" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AK19" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AL19" s="3">
         <v>45854.89583333334</v>
@@ -2934,7 +2940,7 @@
         <v>46</v>
       </c>
       <c r="C20" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D20" t="s">
         <v>54</v>
@@ -2961,82 +2967,82 @@
         <v>111</v>
       </c>
       <c r="L20">
-        <v>2.53</v>
+        <v>1.51</v>
       </c>
       <c r="M20">
-        <v>3.3</v>
+        <v>3.78</v>
       </c>
       <c r="N20">
-        <v>2.37</v>
+        <v>5.82</v>
       </c>
       <c r="O20">
-        <v>2</v>
+        <v>1.41</v>
       </c>
       <c r="P20">
-        <v>10</v>
+        <v>11.75</v>
       </c>
       <c r="Q20">
-        <v>1.93</v>
+        <v>3.1</v>
       </c>
       <c r="R20">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S20">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="T20">
-        <v>2.5</v>
+        <v>2.89</v>
       </c>
       <c r="U20">
-        <v>1.46</v>
+        <v>1.37</v>
       </c>
       <c r="V20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W20">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="X20">
         <v>1.05</v>
       </c>
       <c r="Y20">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="Z20">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AA20">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="AB20">
-        <v>1.77</v>
+        <v>2.07</v>
       </c>
       <c r="AC20">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AD20">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="AE20">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AF20">
-        <v>1.63</v>
+        <v>2.04</v>
       </c>
       <c r="AG20">
-        <v>2.1</v>
+        <v>1.79</v>
       </c>
       <c r="AH20">
-        <v>5.5</v>
+        <v>6.9</v>
       </c>
       <c r="AI20">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AJ20" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AK20" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AL20" s="3">
         <v>45854.89583333334</v>
@@ -3050,7 +3056,7 @@
         <v>46</v>
       </c>
       <c r="C21" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D21" t="s">
         <v>54</v>
@@ -3077,82 +3083,82 @@
         <v>111</v>
       </c>
       <c r="L21">
-        <v>1.51</v>
+        <v>1.39</v>
       </c>
       <c r="M21">
-        <v>3.78</v>
+        <v>4.52</v>
       </c>
       <c r="N21">
-        <v>5.82</v>
+        <v>6.9</v>
       </c>
       <c r="O21">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P21">
-        <v>11.75</v>
+        <v>8.25</v>
       </c>
       <c r="Q21">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="R21">
+        <v>1.42</v>
+      </c>
+      <c r="S21">
+        <v>2.8</v>
+      </c>
+      <c r="T21">
+        <v>3.17</v>
+      </c>
+      <c r="U21">
         <v>1.36</v>
       </c>
-      <c r="S21">
-        <v>2.9</v>
-      </c>
-      <c r="T21">
-        <v>2.89</v>
-      </c>
-      <c r="U21">
-        <v>1.37</v>
-      </c>
       <c r="V21">
+        <v>8</v>
+      </c>
+      <c r="W21">
+        <v>1.07</v>
+      </c>
+      <c r="X21">
+        <v>1.06</v>
+      </c>
+      <c r="Y21">
+        <v>10.5</v>
+      </c>
+      <c r="Z21">
+        <v>1.38</v>
+      </c>
+      <c r="AA21">
+        <v>3</v>
+      </c>
+      <c r="AB21">
+        <v>2.12</v>
+      </c>
+      <c r="AC21">
+        <v>1.67</v>
+      </c>
+      <c r="AD21">
+        <v>3.65</v>
+      </c>
+      <c r="AE21">
+        <v>1.25</v>
+      </c>
+      <c r="AF21">
+        <v>2.4</v>
+      </c>
+      <c r="AG21">
+        <v>1.53</v>
+      </c>
+      <c r="AH21">
         <v>7</v>
       </c>
-      <c r="W21">
-        <v>1.03</v>
-      </c>
-      <c r="X21">
-        <v>1.05</v>
-      </c>
-      <c r="Y21">
-        <v>9</v>
-      </c>
-      <c r="Z21">
-        <v>1.3</v>
-      </c>
-      <c r="AA21">
-        <v>3.4</v>
-      </c>
-      <c r="AB21">
-        <v>2.07</v>
-      </c>
-      <c r="AC21">
-        <v>1.85</v>
-      </c>
-      <c r="AD21">
-        <v>3.45</v>
-      </c>
-      <c r="AE21">
-        <v>1.29</v>
-      </c>
-      <c r="AF21">
-        <v>2.04</v>
-      </c>
-      <c r="AG21">
-        <v>1.79</v>
-      </c>
-      <c r="AH21">
-        <v>6.9</v>
-      </c>
       <c r="AI21">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AJ21" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AK21" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AL21" s="3">
         <v>45854.89583333334</v>
@@ -3166,7 +3172,7 @@
         <v>46</v>
       </c>
       <c r="C22" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D22" t="s">
         <v>54</v>
@@ -3193,82 +3199,82 @@
         <v>111</v>
       </c>
       <c r="L22">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="M22">
-        <v>3</v>
+        <v>3.21</v>
       </c>
       <c r="N22">
+        <v>2.9</v>
+      </c>
+      <c r="O22">
+        <v>1.82</v>
+      </c>
+      <c r="P22">
+        <v>9.5</v>
+      </c>
+      <c r="Q22">
+        <v>2.15</v>
+      </c>
+      <c r="R22">
+        <v>1.36</v>
+      </c>
+      <c r="S22">
+        <v>2.87</v>
+      </c>
+      <c r="T22">
+        <v>2.6</v>
+      </c>
+      <c r="U22">
+        <v>1.43</v>
+      </c>
+      <c r="V22">
+        <v>6.5</v>
+      </c>
+      <c r="W22">
+        <v>1.1</v>
+      </c>
+      <c r="X22">
+        <v>1.05</v>
+      </c>
+      <c r="Y22">
+        <v>9.5</v>
+      </c>
+      <c r="Z22">
+        <v>1.27</v>
+      </c>
+      <c r="AA22">
         <v>3.4</v>
       </c>
-      <c r="O22">
-        <v>1.73</v>
-      </c>
-      <c r="P22">
-        <v>7</v>
-      </c>
-      <c r="Q22">
-        <v>2.5</v>
-      </c>
-      <c r="R22">
-        <v>1.6</v>
-      </c>
-      <c r="S22">
-        <v>2.23</v>
-      </c>
-      <c r="T22">
-        <v>3.5</v>
-      </c>
-      <c r="U22">
-        <v>1.22</v>
-      </c>
-      <c r="V22">
-        <v>9.1</v>
-      </c>
-      <c r="W22">
-        <v>1</v>
-      </c>
-      <c r="X22">
-        <v>1.14</v>
-      </c>
-      <c r="Y22">
-        <v>6</v>
-      </c>
-      <c r="Z22">
-        <v>1.55</v>
-      </c>
-      <c r="AA22">
-        <v>2.25</v>
-      </c>
       <c r="AB22">
-        <v>2.7</v>
+        <v>1.82</v>
       </c>
       <c r="AC22">
-        <v>1.4</v>
+        <v>1.88</v>
       </c>
       <c r="AD22">
-        <v>5.95</v>
+        <v>1.02</v>
       </c>
       <c r="AE22">
+        <v>1.02</v>
+      </c>
+      <c r="AF22">
+        <v>1.68</v>
+      </c>
+      <c r="AG22">
+        <v>2.05</v>
+      </c>
+      <c r="AH22">
+        <v>5.5</v>
+      </c>
+      <c r="AI22">
         <v>1.12</v>
       </c>
-      <c r="AF22">
-        <v>2.25</v>
-      </c>
-      <c r="AG22">
-        <v>1.57</v>
-      </c>
-      <c r="AH22">
-        <v>9.5</v>
-      </c>
-      <c r="AI22">
-        <v>1.01</v>
-      </c>
       <c r="AJ22" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AK22" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AL22" s="3">
         <v>45854.89583333334</v>
@@ -3381,10 +3387,10 @@
         <v>1.18</v>
       </c>
       <c r="AJ23" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AK23" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AL23" s="3">
         <v>45854.89583333334</v>
@@ -3398,7 +3404,7 @@
         <v>46</v>
       </c>
       <c r="C24" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D24" t="s">
         <v>54</v>
@@ -3425,82 +3431,82 @@
         <v>111</v>
       </c>
       <c r="L24">
-        <v>1.39</v>
+        <v>2.53</v>
       </c>
       <c r="M24">
-        <v>4.52</v>
+        <v>3.3</v>
       </c>
       <c r="N24">
-        <v>6.9</v>
+        <v>2.37</v>
       </c>
       <c r="O24">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="P24">
-        <v>8.25</v>
+        <v>10</v>
       </c>
       <c r="Q24">
-        <v>3.5</v>
+        <v>1.93</v>
       </c>
       <c r="R24">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="S24">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="T24">
-        <v>3.17</v>
+        <v>2.5</v>
       </c>
       <c r="U24">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="V24">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="W24">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X24">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y24">
-        <v>10.5</v>
+        <v>9.5</v>
       </c>
       <c r="Z24">
+        <v>1.25</v>
+      </c>
+      <c r="AA24">
+        <v>3.75</v>
+      </c>
+      <c r="AB24">
+        <v>1.77</v>
+      </c>
+      <c r="AC24">
+        <v>1.93</v>
+      </c>
+      <c r="AD24">
+        <v>3</v>
+      </c>
+      <c r="AE24">
         <v>1.38</v>
       </c>
-      <c r="AA24">
-        <v>3</v>
-      </c>
-      <c r="AB24">
-        <v>2.12</v>
-      </c>
-      <c r="AC24">
-        <v>1.67</v>
-      </c>
-      <c r="AD24">
-        <v>3.65</v>
-      </c>
-      <c r="AE24">
-        <v>1.25</v>
-      </c>
       <c r="AF24">
-        <v>2.4</v>
+        <v>1.63</v>
       </c>
       <c r="AG24">
-        <v>1.53</v>
+        <v>2.1</v>
       </c>
       <c r="AH24">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="AI24">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AJ24" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AK24" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AL24" s="3">
         <v>45854.89583333334</v>
@@ -3613,10 +3619,10 @@
         <v>1.1</v>
       </c>
       <c r="AJ25" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AK25" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AL25" s="3">
         <v>45854.95833333334</v>
@@ -3657,16 +3663,16 @@
         <v>111</v>
       </c>
       <c r="L26">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="M26">
-        <v>3.41</v>
+        <v>3.25</v>
       </c>
       <c r="N26">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O26">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="P26">
         <v>10.5</v>
@@ -3675,22 +3681,22 @@
         <v>2.3</v>
       </c>
       <c r="R26">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S26">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="T26">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="U26">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="V26">
         <v>6</v>
       </c>
       <c r="W26">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X26">
         <v>1.05</v>
@@ -3699,40 +3705,40 @@
         <v>9.5</v>
       </c>
       <c r="Z26">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AA26">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="AB26">
-        <v>1.72</v>
+        <v>1.54</v>
       </c>
       <c r="AC26">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AD26">
-        <v>2.95</v>
+        <v>2.62</v>
       </c>
       <c r="AE26">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="AF26">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AG26">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AH26">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="AI26">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AJ26" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AK26" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AL26" s="3">
         <v>45854.97916666666</v>
@@ -3845,10 +3851,10 @@
         <v>0</v>
       </c>
       <c r="AJ27" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AK27" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AL27" s="3">
         <v>45854.97916666666</v>
@@ -3889,82 +3895,82 @@
         <v>111</v>
       </c>
       <c r="L28">
-        <v>1.59</v>
+        <v>1.94</v>
       </c>
       <c r="M28">
-        <v>3.95</v>
+        <v>3.41</v>
       </c>
       <c r="N28">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="O28">
-        <v>1.51</v>
+        <v>1.71</v>
       </c>
       <c r="P28">
-        <v>17.5</v>
+        <v>10.5</v>
       </c>
       <c r="Q28">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="R28">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="S28">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
       <c r="T28">
-        <v>1.93</v>
+        <v>2.45</v>
       </c>
       <c r="U28">
-        <v>1.77</v>
+        <v>1.47</v>
       </c>
       <c r="V28">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="W28">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="X28">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y28">
-        <v>23</v>
+        <v>9.5</v>
       </c>
       <c r="Z28">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AA28">
-        <v>6.25</v>
+        <v>3.8</v>
       </c>
       <c r="AB28">
-        <v>1.34</v>
+        <v>1.72</v>
       </c>
       <c r="AC28">
-        <v>3.09</v>
+        <v>2</v>
       </c>
       <c r="AD28">
-        <v>1.9</v>
+        <v>2.95</v>
       </c>
       <c r="AE28">
-        <v>1.8</v>
+        <v>1.38</v>
       </c>
       <c r="AF28">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="AG28">
-        <v>2.55</v>
+        <v>2.1</v>
       </c>
       <c r="AH28">
-        <v>3.1</v>
+        <v>5.5</v>
       </c>
       <c r="AI28">
-        <v>1.35</v>
+        <v>1.14</v>
       </c>
       <c r="AJ28" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AK28" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AL28" s="3">
         <v>45854.97916666666</v>
@@ -4005,82 +4011,82 @@
         <v>111</v>
       </c>
       <c r="L29">
-        <v>1.99</v>
+        <v>1.59</v>
       </c>
       <c r="M29">
-        <v>3.25</v>
+        <v>3.95</v>
       </c>
       <c r="N29">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="O29">
-        <v>1.67</v>
+        <v>1.51</v>
       </c>
       <c r="P29">
-        <v>10.5</v>
+        <v>17.5</v>
       </c>
       <c r="Q29">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="R29">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="S29">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="T29">
-        <v>2.5</v>
+        <v>1.93</v>
       </c>
       <c r="U29">
-        <v>1.5</v>
+        <v>1.77</v>
       </c>
       <c r="V29">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="W29">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="X29">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>9.5</v>
+        <v>23</v>
       </c>
       <c r="Z29">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="AA29">
-        <v>4.2</v>
+        <v>6.25</v>
       </c>
       <c r="AB29">
-        <v>1.54</v>
+        <v>1.34</v>
       </c>
       <c r="AC29">
-        <v>2.3</v>
+        <v>3.09</v>
       </c>
       <c r="AD29">
-        <v>2.62</v>
+        <v>1.9</v>
       </c>
       <c r="AE29">
-        <v>1.48</v>
+        <v>1.8</v>
       </c>
       <c r="AF29">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AG29">
-        <v>2.25</v>
+        <v>2.55</v>
       </c>
       <c r="AH29">
-        <v>4.75</v>
+        <v>3.1</v>
       </c>
       <c r="AI29">
-        <v>1.18</v>
+        <v>1.35</v>
       </c>
       <c r="AJ29" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AK29" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AL29" s="3">
         <v>45854.97916666666</v>

--- a/jogos_2025-07-16.xlsx
+++ b/jogos_2025-07-16.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="150">
   <si>
     <t>Date</t>
   </si>
@@ -154,6 +154,9 @@
     <t>21:00</t>
   </si>
   <si>
+    <t>21:15</t>
+  </si>
+  <si>
     <t>21:30</t>
   </si>
   <si>
@@ -169,12 +172,12 @@
     <t>Norway Eliteserien</t>
   </si>
   <si>
+    <t>USA USL Championship</t>
+  </si>
+  <si>
     <t>USA MLS</t>
   </si>
   <si>
-    <t>USA USL Championship</t>
-  </si>
-  <si>
     <t>USA MLS Next Pro</t>
   </si>
   <si>
@@ -184,15 +187,15 @@
     <t>Grêmio</t>
   </si>
   <si>
+    <t>Bahia</t>
+  </si>
+  <si>
+    <t>Juventude</t>
+  </si>
+  <si>
     <t>Atlético Mineiro</t>
   </si>
   <si>
-    <t>Juventude</t>
-  </si>
-  <si>
-    <t>Bahia</t>
-  </si>
-  <si>
     <t>Fredrikstad</t>
   </si>
   <si>
@@ -205,78 +208,78 @@
     <t>Santos</t>
   </si>
   <si>
+    <t>Hartford Athletic</t>
+  </si>
+  <si>
     <t>Philadelphia Union</t>
   </si>
   <si>
+    <t>Charlotte</t>
+  </si>
+  <si>
+    <t>Atlanta United FC</t>
+  </si>
+  <si>
+    <t>New York City II</t>
+  </si>
+  <si>
     <t>FC Cincinnati</t>
   </si>
   <si>
-    <t>Hartford Athletic</t>
+    <t>New York RB</t>
+  </si>
+  <si>
+    <t>St. Louis City II</t>
   </si>
   <si>
     <t>Orlando City</t>
   </si>
   <si>
-    <t>Charlotte</t>
-  </si>
-  <si>
-    <t>New York RB</t>
-  </si>
-  <si>
-    <t>Atlanta United FC</t>
-  </si>
-  <si>
-    <t>New York City II</t>
-  </si>
-  <si>
-    <t>St. Louis City II</t>
+    <t>Nashville SC</t>
+  </si>
+  <si>
+    <t>Botafogo</t>
+  </si>
+  <si>
+    <t>Tulsa Roughnecks</t>
+  </si>
+  <si>
+    <t>Houston Dynamo</t>
   </si>
   <si>
     <t>Bragantino</t>
   </si>
   <si>
-    <t>Tulsa Roughnecks</t>
-  </si>
-  <si>
-    <t>Botafogo</t>
-  </si>
-  <si>
-    <t>Houston Dynamo</t>
-  </si>
-  <si>
-    <t>Nashville SC</t>
-  </si>
-  <si>
     <t>Minnesota United</t>
   </si>
   <si>
     <t>Seattle Sounders</t>
   </si>
   <si>
+    <t>SJ Earthquakes</t>
+  </si>
+  <si>
+    <t>LA Galaxy</t>
+  </si>
+  <si>
+    <t>San Diego</t>
+  </si>
+  <si>
     <t>Portland Timbers</t>
   </si>
   <si>
-    <t>San Diego</t>
-  </si>
-  <si>
-    <t>LA Galaxy</t>
-  </si>
-  <si>
-    <t>SJ Earthquakes</t>
-  </si>
-  <si>
     <t>Fortaleza</t>
   </si>
   <si>
+    <t>Internacional</t>
+  </si>
+  <si>
+    <t>Vasco da Gama</t>
+  </si>
+  <si>
     <t>Sport Recife</t>
   </si>
   <si>
-    <t>Vasco da Gama</t>
-  </si>
-  <si>
-    <t>Internacional</t>
-  </si>
-  <si>
     <t>FK Bodo - Glimt</t>
   </si>
   <si>
@@ -289,66 +292,66 @@
     <t>Flamengo</t>
   </si>
   <si>
+    <t>Tampa Bay Rowdies</t>
+  </si>
+  <si>
     <t>Montreal Impact</t>
   </si>
   <si>
+    <t>DC United</t>
+  </si>
+  <si>
+    <t>Chicago Fire</t>
+  </si>
+  <si>
+    <t>Toronto II</t>
+  </si>
+  <si>
     <t>Inter Miami</t>
   </si>
   <si>
-    <t>Tampa Bay Rowdies</t>
+    <t>New England Revolution</t>
+  </si>
+  <si>
+    <t>LA Galaxy II</t>
   </si>
   <si>
     <t>New York City</t>
   </si>
   <si>
-    <t>DC United</t>
-  </si>
-  <si>
-    <t>New England Revolution</t>
-  </si>
-  <si>
-    <t>Chicago Fire</t>
-  </si>
-  <si>
-    <t>Toronto II</t>
-  </si>
-  <si>
-    <t>LA Galaxy II</t>
+    <t>Columbus Crew</t>
+  </si>
+  <si>
+    <t>Vitória</t>
+  </si>
+  <si>
+    <t>Monterey Bay</t>
+  </si>
+  <si>
+    <t>Vancouver Whitecaps</t>
   </si>
   <si>
     <t>São Paulo</t>
   </si>
   <si>
-    <t>Monterey Bay</t>
-  </si>
-  <si>
-    <t>Vitória</t>
-  </si>
-  <si>
-    <t>Vancouver Whitecaps</t>
-  </si>
-  <si>
-    <t>Columbus Crew</t>
-  </si>
-  <si>
     <t>Los Angeles FC</t>
   </si>
   <si>
     <t>Colorado Rapids</t>
   </si>
   <si>
+    <t>FC Dallas</t>
+  </si>
+  <si>
+    <t>Austin</t>
+  </si>
+  <si>
+    <t>Toronto</t>
+  </si>
+  <si>
     <t>Real Salt Lake</t>
   </si>
   <si>
-    <t>Toronto</t>
-  </si>
-  <si>
-    <t>Austin</t>
-  </si>
-  <si>
-    <t>FC Dallas</t>
-  </si>
-  <si>
     <t>incomplete</t>
   </si>
   <si>
@@ -361,7 +364,106 @@
     <t>[]</t>
   </si>
   <si>
+    <t>['54']</t>
+  </si>
+  <si>
+    <t>['84']</t>
+  </si>
+  <si>
+    <t>['37', '50']</t>
+  </si>
+  <si>
+    <t>['44', '48']</t>
+  </si>
+  <si>
+    <t>['56', '90+4']</t>
+  </si>
+  <si>
+    <t>['53']</t>
+  </si>
+  <si>
+    <t>['16', '50', '70']</t>
+  </si>
+  <si>
+    <t>['56', '70', '72', '83', '88']</t>
+  </si>
+  <si>
+    <t>['57']</t>
+  </si>
+  <si>
+    <t>['36']</t>
+  </si>
+  <si>
+    <t>['2', '30', '82']</t>
+  </si>
+  <si>
+    <t>['47', '48']</t>
+  </si>
+  <si>
+    <t>['43', '48']</t>
+  </si>
+  <si>
+    <t>['16', '43', '47']</t>
+  </si>
+  <si>
+    <t>['21', '86']</t>
+  </si>
+  <si>
+    <t>['90+3']</t>
+  </si>
+  <si>
     <t>['87']</t>
+  </si>
+  <si>
+    <t>['72']</t>
+  </si>
+  <si>
+    <t>['71']</t>
+  </si>
+  <si>
+    <t>['83']</t>
+  </si>
+  <si>
+    <t>['45+2']</t>
+  </si>
+  <si>
+    <t>['60']</t>
+  </si>
+  <si>
+    <t>['2', '79']</t>
+  </si>
+  <si>
+    <t>['5', '30', '90+3']</t>
+  </si>
+  <si>
+    <t>['33']</t>
+  </si>
+  <si>
+    <t>['87', '90+1']</t>
+  </si>
+  <si>
+    <t>['9']</t>
+  </si>
+  <si>
+    <t>['4', '42', '56']</t>
+  </si>
+  <si>
+    <t>['9', '64']</t>
+  </si>
+  <si>
+    <t>['42']</t>
+  </si>
+  <si>
+    <t>['50', '53', '75']</t>
+  </si>
+  <si>
+    <t>['45+3', '85']</t>
+  </si>
+  <si>
+    <t>['40', '63']</t>
+  </si>
+  <si>
+    <t>['20']</t>
   </si>
 </sst>
 </file>
@@ -852,16 +954,16 @@
         <v>38</v>
       </c>
       <c r="C2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -876,7 +978,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L2">
         <v>2.18</v>
@@ -951,10 +1053,10 @@
         <v>0</v>
       </c>
       <c r="AJ2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AK2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AL2" s="3">
         <v>45854.45833333334</v>
@@ -968,16 +1070,16 @@
         <v>39</v>
       </c>
       <c r="C3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -992,43 +1094,43 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L3">
-        <v>1.49</v>
+        <v>2.49</v>
       </c>
       <c r="M3">
-        <v>5.2</v>
+        <v>3.1</v>
       </c>
       <c r="N3">
-        <v>6.55</v>
+        <v>2.9</v>
       </c>
       <c r="O3">
-        <v>1.33</v>
+        <v>1.83</v>
       </c>
       <c r="P3">
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="R3">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="S3">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="T3">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="U3">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="V3">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="W3">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X3">
         <v>0</v>
@@ -1043,10 +1145,10 @@
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="AC3">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -1055,10 +1157,10 @@
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AG3">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -1067,10 +1169,10 @@
         <v>0</v>
       </c>
       <c r="AJ3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AK3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AL3" s="3">
         <v>45854.5</v>
@@ -1084,16 +1186,16 @@
         <v>39</v>
       </c>
       <c r="C4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -1108,7 +1210,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L4">
         <v>2.23</v>
@@ -1183,10 +1285,10 @@
         <v>0</v>
       </c>
       <c r="AJ4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AK4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AL4" s="3">
         <v>45854.5</v>
@@ -1200,16 +1302,16 @@
         <v>39</v>
       </c>
       <c r="C5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1224,43 +1326,43 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L5">
-        <v>2.49</v>
+        <v>1.49</v>
       </c>
       <c r="M5">
-        <v>3.1</v>
+        <v>5.2</v>
       </c>
       <c r="N5">
-        <v>2.9</v>
+        <v>6.55</v>
       </c>
       <c r="O5">
-        <v>1.83</v>
+        <v>1.33</v>
       </c>
       <c r="P5">
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>2.3</v>
+        <v>3.6</v>
       </c>
       <c r="R5">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="S5">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="T5">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="U5">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="V5">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="W5">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X5">
         <v>0</v>
@@ -1275,10 +1377,10 @@
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>2.35</v>
+        <v>1.95</v>
       </c>
       <c r="AC5">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="AD5">
         <v>0</v>
@@ -1287,10 +1389,10 @@
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AG5">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AH5">
         <v>0</v>
@@ -1299,10 +1401,10 @@
         <v>0</v>
       </c>
       <c r="AJ5" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AK5" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AL5" s="3">
         <v>45854.5</v>
@@ -1316,16 +1418,16 @@
         <v>40</v>
       </c>
       <c r="C6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1340,7 +1442,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L6">
         <v>4.1</v>
@@ -1415,10 +1517,10 @@
         <v>1.09</v>
       </c>
       <c r="AJ6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AK6" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="AL6" s="3">
         <v>45854.54166666666</v>
@@ -1432,22 +1534,22 @@
         <v>41</v>
       </c>
       <c r="C7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -1456,16 +1558,16 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="L7">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="M7">
         <v>4.1</v>
       </c>
       <c r="N7">
-        <v>8.859999999999999</v>
+        <v>9.15</v>
       </c>
       <c r="O7">
         <v>1.29</v>
@@ -1480,13 +1582,13 @@
         <v>1.4</v>
       </c>
       <c r="S7">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="T7">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="U7">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="V7">
         <v>8</v>
@@ -1495,46 +1597,46 @@
         <v>1.08</v>
       </c>
       <c r="X7">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y7">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="Z7">
+        <v>1.35</v>
+      </c>
+      <c r="AA7">
+        <v>3.12</v>
+      </c>
+      <c r="AB7">
+        <v>1.95</v>
+      </c>
+      <c r="AC7">
+        <v>1.73</v>
+      </c>
+      <c r="AD7">
+        <v>3.5</v>
+      </c>
+      <c r="AE7">
         <v>1.3</v>
-      </c>
-      <c r="AA7">
-        <v>3</v>
-      </c>
-      <c r="AB7">
-        <v>2</v>
-      </c>
-      <c r="AC7">
-        <v>1.75</v>
-      </c>
-      <c r="AD7">
-        <v>3.62</v>
-      </c>
-      <c r="AE7">
-        <v>1.22</v>
       </c>
       <c r="AF7">
         <v>2.25</v>
       </c>
       <c r="AG7">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AH7">
-        <v>7.5</v>
+        <v>5.3</v>
       </c>
       <c r="AI7">
         <v>1.08</v>
       </c>
       <c r="AJ7" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="AK7" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="AL7" s="3">
         <v>45854.79166666666</v>
@@ -1548,22 +1650,22 @@
         <v>42</v>
       </c>
       <c r="C8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -1572,13 +1674,13 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="L8">
         <v>2.4</v>
       </c>
       <c r="M8">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="N8">
         <v>3.25</v>
@@ -1593,64 +1695,64 @@
         <v>2.2</v>
       </c>
       <c r="R8">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="S8">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="T8">
         <v>3.4</v>
       </c>
       <c r="U8">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="V8">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="W8">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X8">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Y8">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="Z8">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AA8">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="AB8">
-        <v>2.96</v>
+        <v>2.8</v>
       </c>
       <c r="AC8">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AD8">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="AE8">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF8">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AG8">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AH8">
-        <v>14</v>
+        <v>8.5</v>
       </c>
       <c r="AI8">
         <v>1.03</v>
       </c>
       <c r="AJ8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AK8" t="s">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="AL8" s="3">
         <v>45854.8125</v>
@@ -1664,19 +1766,19 @@
         <v>43</v>
       </c>
       <c r="C9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -1688,16 +1790,16 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="L9">
         <v>3.9</v>
       </c>
       <c r="M9">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="N9">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="O9">
         <v>2.63</v>
@@ -1709,34 +1811,34 @@
         <v>1.57</v>
       </c>
       <c r="R9">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="S9">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="T9">
         <v>3.46</v>
       </c>
       <c r="U9">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="V9">
-        <v>8.699999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="W9">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X9">
         <v>1.08</v>
       </c>
       <c r="Y9">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="Z9">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AA9">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="AB9">
         <v>2.3</v>
@@ -1745,28 +1847,28 @@
         <v>1.55</v>
       </c>
       <c r="AD9">
-        <v>4.45</v>
+        <v>4.33</v>
       </c>
       <c r="AE9">
         <v>1.2</v>
       </c>
       <c r="AF9">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="AG9">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AH9">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="AI9">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AJ9" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="AK9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AL9" s="3">
         <v>45854.83333333334</v>
@@ -1780,22 +1882,22 @@
         <v>44</v>
       </c>
       <c r="C10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G10">
         <v>0</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -1804,85 +1906,85 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="L10">
-        <v>1.38</v>
+        <v>2.36</v>
       </c>
       <c r="M10">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="N10">
-        <v>6</v>
+        <v>2.39</v>
       </c>
       <c r="O10">
-        <v>1.44</v>
+        <v>1.95</v>
       </c>
       <c r="P10">
         <v>12.5</v>
       </c>
       <c r="Q10">
-        <v>2.95</v>
+        <v>1.92</v>
       </c>
       <c r="R10">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="S10">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="T10">
-        <v>2.25</v>
+        <v>2.63</v>
       </c>
       <c r="U10">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="V10">
-        <v>5</v>
+        <v>6.55</v>
       </c>
       <c r="W10">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="X10">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y10">
         <v>10</v>
       </c>
       <c r="Z10">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AA10">
-        <v>4.33</v>
+        <v>3.6</v>
       </c>
       <c r="AB10">
-        <v>1.52</v>
+        <v>1.8</v>
       </c>
       <c r="AC10">
-        <v>2.35</v>
+        <v>1.95</v>
       </c>
       <c r="AD10">
-        <v>2.55</v>
+        <v>2.97</v>
       </c>
       <c r="AE10">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="AF10">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AG10">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AH10">
-        <v>4.33</v>
+        <v>5.49</v>
       </c>
       <c r="AI10">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="AJ10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AK10" t="s">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="AL10" s="3">
         <v>45854.85416666666</v>
@@ -1896,67 +1998,67 @@
         <v>44</v>
       </c>
       <c r="C11" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="L11">
-        <v>2.06</v>
+        <v>1.38</v>
       </c>
       <c r="M11">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="N11">
-        <v>2.82</v>
+        <v>6</v>
       </c>
       <c r="O11">
-        <v>1.82</v>
+        <v>1.44</v>
       </c>
       <c r="P11">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Q11">
-        <v>2.05</v>
+        <v>2.95</v>
       </c>
       <c r="R11">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S11">
         <v>3.4</v>
       </c>
       <c r="T11">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="U11">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="V11">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="W11">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X11">
         <v>1.04</v>
@@ -1965,40 +2067,40 @@
         <v>10</v>
       </c>
       <c r="Z11">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AA11">
-        <v>4.75</v>
+        <v>4.33</v>
       </c>
       <c r="AB11">
-        <v>1.37</v>
+        <v>1.52</v>
       </c>
       <c r="AC11">
-        <v>2.94</v>
+        <v>2.35</v>
       </c>
       <c r="AD11">
-        <v>2.04</v>
+        <v>2.55</v>
       </c>
       <c r="AE11">
-        <v>1.69</v>
+        <v>1.5</v>
       </c>
       <c r="AF11">
-        <v>1.47</v>
+        <v>1.7</v>
       </c>
       <c r="AG11">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="AH11">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AI11">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AJ11" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="AK11" t="s">
-        <v>114</v>
+        <v>136</v>
       </c>
       <c r="AL11" s="3">
         <v>45854.85416666666</v>
@@ -2012,109 +2114,109 @@
         <v>44</v>
       </c>
       <c r="C12" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E12" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F12" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12">
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="L12">
-        <v>2.33</v>
+        <v>1.61</v>
       </c>
       <c r="M12">
-        <v>3.3</v>
+        <v>3.81</v>
       </c>
       <c r="N12">
-        <v>2.39</v>
+        <v>4.2</v>
       </c>
       <c r="O12">
-        <v>1.95</v>
+        <v>1.53</v>
       </c>
       <c r="P12">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Q12">
-        <v>1.92</v>
+        <v>2.6</v>
       </c>
       <c r="R12">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="S12">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="T12">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="U12">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="V12">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="W12">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="X12">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y12">
         <v>10</v>
       </c>
       <c r="Z12">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AA12">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="AB12">
-        <v>1.79</v>
+        <v>1.57</v>
       </c>
       <c r="AC12">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="AD12">
-        <v>2.96</v>
+        <v>2.3</v>
       </c>
       <c r="AE12">
-        <v>1.38</v>
+        <v>1.54</v>
       </c>
       <c r="AF12">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AG12">
         <v>2.15</v>
       </c>
       <c r="AH12">
-        <v>5.46</v>
+        <v>4.33</v>
       </c>
       <c r="AI12">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AJ12" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="AK12" t="s">
-        <v>114</v>
+        <v>137</v>
       </c>
       <c r="AL12" s="3">
         <v>45854.85416666666</v>
@@ -2128,49 +2230,49 @@
         <v>44</v>
       </c>
       <c r="C13" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E13" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F13" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I13">
         <v>0</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="L13">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="M13">
-        <v>3.55</v>
+        <v>3.63</v>
       </c>
       <c r="N13">
-        <v>3.83</v>
+        <v>2.91</v>
       </c>
       <c r="O13">
-        <v>1.52</v>
+        <v>1.75</v>
       </c>
       <c r="P13">
         <v>13</v>
       </c>
       <c r="Q13">
-        <v>2.65</v>
+        <v>2.15</v>
       </c>
       <c r="R13">
         <v>1.27</v>
@@ -2179,13 +2281,13 @@
         <v>3.4</v>
       </c>
       <c r="T13">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="U13">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="V13">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="W13">
         <v>1.15</v>
@@ -2203,22 +2305,22 @@
         <v>4.75</v>
       </c>
       <c r="AB13">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="AC13">
-        <v>2.27</v>
+        <v>2.36</v>
       </c>
       <c r="AD13">
+        <v>2.1</v>
+      </c>
+      <c r="AE13">
+        <v>1.65</v>
+      </c>
+      <c r="AF13">
+        <v>1.49</v>
+      </c>
+      <c r="AG13">
         <v>2.4</v>
-      </c>
-      <c r="AE13">
-        <v>1.57</v>
-      </c>
-      <c r="AF13">
-        <v>1.57</v>
-      </c>
-      <c r="AG13">
-        <v>2.25</v>
       </c>
       <c r="AH13">
         <v>4.2</v>
@@ -2227,10 +2329,10 @@
         <v>1.22</v>
       </c>
       <c r="AJ13" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="AK13" t="s">
-        <v>114</v>
+        <v>138</v>
       </c>
       <c r="AL13" s="3">
         <v>45854.85416666666</v>
@@ -2244,19 +2346,19 @@
         <v>44</v>
       </c>
       <c r="C14" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D14" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E14" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F14" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -2268,85 +2370,85 @@
         <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="L14">
-        <v>1.61</v>
+        <v>1.71</v>
       </c>
       <c r="M14">
-        <v>3.81</v>
+        <v>3.5</v>
       </c>
       <c r="N14">
-        <v>4.2</v>
+        <v>4.37</v>
       </c>
       <c r="O14">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="P14">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Q14">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="R14">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="S14">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="T14">
-        <v>2.25</v>
+        <v>2.61</v>
       </c>
       <c r="U14">
-        <v>1.57</v>
+        <v>1.42</v>
       </c>
       <c r="V14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W14">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="X14">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y14">
         <v>10</v>
       </c>
       <c r="Z14">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AA14">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="AB14">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AC14">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AD14">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="AE14">
-        <v>1.54</v>
+        <v>1.33</v>
       </c>
       <c r="AF14">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AG14">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AH14">
-        <v>4.33</v>
+        <v>5</v>
       </c>
       <c r="AI14">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AJ14" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="AK14" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AL14" s="3">
         <v>45854.85416666666</v>
@@ -2360,109 +2462,109 @@
         <v>44</v>
       </c>
       <c r="C15" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D15" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E15" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F15" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H15">
         <v>0</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15">
         <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="L15">
-        <v>1.74</v>
+        <v>2.06</v>
       </c>
       <c r="M15">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="N15">
-        <v>3.87</v>
+        <v>2.82</v>
       </c>
       <c r="O15">
+        <v>1.82</v>
+      </c>
+      <c r="P15">
+        <v>13</v>
+      </c>
+      <c r="Q15">
+        <v>2.05</v>
+      </c>
+      <c r="R15">
+        <v>1.27</v>
+      </c>
+      <c r="S15">
+        <v>3.4</v>
+      </c>
+      <c r="T15">
+        <v>2.2</v>
+      </c>
+      <c r="U15">
         <v>1.6</v>
       </c>
-      <c r="P15">
-        <v>10.5</v>
-      </c>
-      <c r="Q15">
-        <v>2.55</v>
-      </c>
-      <c r="R15">
-        <v>1.33</v>
-      </c>
-      <c r="S15">
-        <v>3</v>
-      </c>
-      <c r="T15">
-        <v>2.5</v>
-      </c>
-      <c r="U15">
-        <v>1.46</v>
-      </c>
       <c r="V15">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="W15">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X15">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y15">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="Z15">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AA15">
-        <v>3.8</v>
+        <v>4.75</v>
       </c>
       <c r="AB15">
-        <v>1.68</v>
+        <v>1.37</v>
       </c>
       <c r="AC15">
-        <v>2.05</v>
+        <v>2.94</v>
       </c>
       <c r="AD15">
-        <v>2.95</v>
+        <v>2.04</v>
       </c>
       <c r="AE15">
-        <v>1.38</v>
+        <v>1.69</v>
       </c>
       <c r="AF15">
-        <v>1.7</v>
+        <v>1.47</v>
       </c>
       <c r="AG15">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="AH15">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="AI15">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AJ15" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="AK15" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AL15" s="3">
         <v>45854.85416666666</v>
@@ -2476,109 +2578,109 @@
         <v>44</v>
       </c>
       <c r="C16" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D16" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E16" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F16" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I16">
         <v>0</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K16" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="L16">
+        <v>1.74</v>
+      </c>
+      <c r="M16">
+        <v>3.5</v>
+      </c>
+      <c r="N16">
+        <v>3.87</v>
+      </c>
+      <c r="O16">
+        <v>1.6</v>
+      </c>
+      <c r="P16">
+        <v>10.5</v>
+      </c>
+      <c r="Q16">
+        <v>2.55</v>
+      </c>
+      <c r="R16">
+        <v>1.33</v>
+      </c>
+      <c r="S16">
+        <v>3</v>
+      </c>
+      <c r="T16">
+        <v>2.5</v>
+      </c>
+      <c r="U16">
+        <v>1.46</v>
+      </c>
+      <c r="V16">
+        <v>6</v>
+      </c>
+      <c r="W16">
+        <v>1.11</v>
+      </c>
+      <c r="X16">
+        <v>1.05</v>
+      </c>
+      <c r="Y16">
+        <v>9.5</v>
+      </c>
+      <c r="Z16">
+        <v>1.25</v>
+      </c>
+      <c r="AA16">
+        <v>3.8</v>
+      </c>
+      <c r="AB16">
+        <v>1.67</v>
+      </c>
+      <c r="AC16">
+        <v>2.07</v>
+      </c>
+      <c r="AD16">
+        <v>2.95</v>
+      </c>
+      <c r="AE16">
+        <v>1.38</v>
+      </c>
+      <c r="AF16">
+        <v>1.7</v>
+      </c>
+      <c r="AG16">
         <v>2</v>
       </c>
-      <c r="M16">
-        <v>3.63</v>
-      </c>
-      <c r="N16">
-        <v>2.91</v>
-      </c>
-      <c r="O16">
-        <v>1.75</v>
-      </c>
-      <c r="P16">
-        <v>13</v>
-      </c>
-      <c r="Q16">
-        <v>2.15</v>
-      </c>
-      <c r="R16">
-        <v>1.27</v>
-      </c>
-      <c r="S16">
-        <v>3.4</v>
-      </c>
-      <c r="T16">
-        <v>2.2</v>
-      </c>
-      <c r="U16">
-        <v>1.58</v>
-      </c>
-      <c r="V16">
-        <v>5</v>
-      </c>
-      <c r="W16">
-        <v>1.15</v>
-      </c>
-      <c r="X16">
-        <v>1.04</v>
-      </c>
-      <c r="Y16">
-        <v>10</v>
-      </c>
-      <c r="Z16">
-        <v>1.18</v>
-      </c>
-      <c r="AA16">
-        <v>4.75</v>
-      </c>
-      <c r="AB16">
-        <v>1.59</v>
-      </c>
-      <c r="AC16">
-        <v>2.36</v>
-      </c>
-      <c r="AD16">
-        <v>2.1</v>
-      </c>
-      <c r="AE16">
-        <v>1.65</v>
-      </c>
-      <c r="AF16">
-        <v>1.49</v>
-      </c>
-      <c r="AG16">
-        <v>2.4</v>
-      </c>
       <c r="AH16">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="AI16">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AJ16" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="AK16" t="s">
-        <v>114</v>
+        <v>139</v>
       </c>
       <c r="AL16" s="3">
         <v>45854.85416666666</v>
@@ -2589,115 +2691,115 @@
         <v>45854</v>
       </c>
       <c r="B17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C17" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D17" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E17" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F17" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17">
         <v>0</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="L17">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="M17">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="N17">
-        <v>3.9</v>
+        <v>4.49</v>
       </c>
       <c r="O17">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="P17">
         <v>0</v>
       </c>
       <c r="Q17">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="R17">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="S17">
-        <v>3.22</v>
+        <v>4</v>
       </c>
       <c r="T17">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="U17">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="V17">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="W17">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="X17">
         <v>1.01</v>
       </c>
       <c r="Y17">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="Z17">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AA17">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="AB17">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="AC17">
-        <v>2.25</v>
+        <v>2.63</v>
       </c>
       <c r="AD17">
+        <v>2.08</v>
+      </c>
+      <c r="AE17">
+        <v>1.65</v>
+      </c>
+      <c r="AF17">
+        <v>1.45</v>
+      </c>
+      <c r="AG17">
         <v>2.45</v>
       </c>
-      <c r="AE17">
-        <v>1.5</v>
-      </c>
-      <c r="AF17">
-        <v>1.55</v>
-      </c>
-      <c r="AG17">
-        <v>2.2</v>
-      </c>
       <c r="AH17">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="AI17">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AJ17" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="AK17" t="s">
-        <v>114</v>
+        <v>140</v>
       </c>
       <c r="AL17" s="3">
-        <v>45854.85416666666</v>
+        <v>45854.875</v>
       </c>
     </row>
     <row r="18" spans="1:38">
@@ -2705,115 +2807,115 @@
         <v>45854</v>
       </c>
       <c r="B18" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C18" t="s">
         <v>53</v>
       </c>
       <c r="D18" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E18" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F18" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18">
         <v>0</v>
       </c>
       <c r="K18" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="L18">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="M18">
-        <v>3.99</v>
+        <v>3.55</v>
       </c>
       <c r="N18">
-        <v>4.6</v>
+        <v>3.83</v>
       </c>
       <c r="O18">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q18">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="R18">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="S18">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="T18">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="U18">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="V18">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="W18">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z18">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AA18">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="AB18">
-        <v>1.37</v>
+        <v>1.56</v>
       </c>
       <c r="AC18">
-        <v>2.65</v>
+        <v>2.27</v>
       </c>
       <c r="AD18">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AE18">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AF18">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="AG18">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AH18">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="AI18">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AJ18" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="AK18" t="s">
-        <v>114</v>
+        <v>141</v>
       </c>
       <c r="AL18" s="3">
-        <v>45854.875</v>
+        <v>45854.88541666666</v>
       </c>
     </row>
     <row r="19" spans="1:38">
@@ -2821,112 +2923,112 @@
         <v>45854</v>
       </c>
       <c r="B19" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C19" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D19" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E19" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F19" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H19">
         <v>0</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J19">
         <v>0</v>
       </c>
       <c r="K19" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="L19">
-        <v>2.28</v>
+        <v>1.98</v>
       </c>
       <c r="M19">
-        <v>3</v>
+        <v>3.39</v>
       </c>
       <c r="N19">
-        <v>3.4</v>
+        <v>3.12</v>
       </c>
       <c r="O19">
         <v>1.73</v>
       </c>
       <c r="P19">
-        <v>7</v>
+        <v>11.5</v>
       </c>
       <c r="Q19">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="R19">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="S19">
-        <v>2.23</v>
+        <v>3.2</v>
       </c>
       <c r="T19">
-        <v>3.5</v>
+        <v>2.35</v>
       </c>
       <c r="U19">
-        <v>1.22</v>
+        <v>1.52</v>
       </c>
       <c r="V19">
-        <v>9.1</v>
+        <v>5.5</v>
       </c>
       <c r="W19">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="X19">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="Y19">
-        <v>6</v>
+        <v>11.5</v>
       </c>
       <c r="Z19">
-        <v>1.55</v>
+        <v>1.2</v>
       </c>
       <c r="AA19">
-        <v>2.25</v>
+        <v>4.1</v>
       </c>
       <c r="AB19">
+        <v>1.54</v>
+      </c>
+      <c r="AC19">
+        <v>2.3</v>
+      </c>
+      <c r="AD19">
         <v>2.7</v>
       </c>
-      <c r="AC19">
-        <v>1.4</v>
-      </c>
-      <c r="AD19">
-        <v>5.95</v>
-      </c>
       <c r="AE19">
-        <v>1.12</v>
+        <v>1.46</v>
       </c>
       <c r="AF19">
-        <v>2.25</v>
+        <v>1.57</v>
       </c>
       <c r="AG19">
-        <v>1.57</v>
+        <v>2.2</v>
       </c>
       <c r="AH19">
-        <v>9.5</v>
+        <v>4.5</v>
       </c>
       <c r="AI19">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="AJ19" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="AK19" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AL19" s="3">
         <v>45854.89583333334</v>
@@ -2937,19 +3039,19 @@
         <v>45854</v>
       </c>
       <c r="B20" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C20" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D20" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E20" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F20" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -2964,85 +3066,85 @@
         <v>0</v>
       </c>
       <c r="K20" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="L20">
-        <v>1.51</v>
+        <v>1.39</v>
       </c>
       <c r="M20">
-        <v>3.78</v>
+        <v>4.46</v>
       </c>
       <c r="N20">
-        <v>5.82</v>
+        <v>6.9</v>
       </c>
       <c r="O20">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P20">
-        <v>11.75</v>
+        <v>8.25</v>
       </c>
       <c r="Q20">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="R20">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="S20">
-        <v>2.9</v>
+        <v>2.62</v>
       </c>
       <c r="T20">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="U20">
         <v>1.37</v>
       </c>
       <c r="V20">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="W20">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X20">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y20">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="Z20">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AA20">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="AB20">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AC20">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AD20">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="AE20">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AF20">
-        <v>2.04</v>
+        <v>2.38</v>
       </c>
       <c r="AG20">
-        <v>1.79</v>
+        <v>1.53</v>
       </c>
       <c r="AH20">
-        <v>6.9</v>
+        <v>7.5</v>
       </c>
       <c r="AI20">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AJ20" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AK20" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AL20" s="3">
         <v>45854.89583333334</v>
@@ -3053,112 +3155,112 @@
         <v>45854</v>
       </c>
       <c r="B21" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C21" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D21" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E21" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F21" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21">
         <v>0</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="L21">
-        <v>1.39</v>
+        <v>1.51</v>
       </c>
       <c r="M21">
-        <v>4.52</v>
+        <v>3.7</v>
       </c>
       <c r="N21">
-        <v>6.9</v>
+        <v>6</v>
       </c>
       <c r="O21">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P21">
-        <v>8.25</v>
+        <v>11.75</v>
       </c>
       <c r="Q21">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="R21">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="S21">
         <v>2.8</v>
       </c>
       <c r="T21">
-        <v>3.17</v>
+        <v>2.8</v>
       </c>
       <c r="U21">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="V21">
         <v>8</v>
       </c>
       <c r="W21">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X21">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y21">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="Z21">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AA21">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="AB21">
-        <v>2.12</v>
+        <v>2.01</v>
       </c>
       <c r="AC21">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AD21">
-        <v>3.65</v>
+        <v>3.34</v>
       </c>
       <c r="AE21">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AF21">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="AG21">
-        <v>1.53</v>
+        <v>1.83</v>
       </c>
       <c r="AH21">
-        <v>7</v>
+        <v>6.75</v>
       </c>
       <c r="AI21">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AJ21" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="AK21" t="s">
-        <v>114</v>
+        <v>142</v>
       </c>
       <c r="AL21" s="3">
         <v>45854.89583333334</v>
@@ -3169,34 +3271,34 @@
         <v>45854</v>
       </c>
       <c r="B22" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C22" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D22" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E22" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F22" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G22">
         <v>0</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I22">
         <v>0</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K22" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="L22">
         <v>2.16</v>
@@ -3271,10 +3373,10 @@
         <v>1.12</v>
       </c>
       <c r="AJ22" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AK22" t="s">
-        <v>114</v>
+        <v>143</v>
       </c>
       <c r="AL22" s="3">
         <v>45854.89583333334</v>
@@ -3285,112 +3387,112 @@
         <v>45854</v>
       </c>
       <c r="B23" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C23" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D23" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E23" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F23" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="L23">
-        <v>1.98</v>
+        <v>2.33</v>
       </c>
       <c r="M23">
-        <v>3.39</v>
+        <v>3</v>
       </c>
       <c r="N23">
-        <v>3.12</v>
+        <v>3.4</v>
       </c>
       <c r="O23">
         <v>1.73</v>
       </c>
       <c r="P23">
-        <v>11.5</v>
+        <v>7</v>
       </c>
       <c r="Q23">
+        <v>2.5</v>
+      </c>
+      <c r="R23">
+        <v>1.56</v>
+      </c>
+      <c r="S23">
         <v>2.25</v>
       </c>
-      <c r="R23">
-        <v>1.3</v>
-      </c>
-      <c r="S23">
-        <v>3.2</v>
-      </c>
       <c r="T23">
-        <v>2.35</v>
+        <v>3.72</v>
       </c>
       <c r="U23">
-        <v>1.52</v>
+        <v>1.2</v>
       </c>
       <c r="V23">
-        <v>5.5</v>
+        <v>9.1</v>
       </c>
       <c r="W23">
+        <v>1</v>
+      </c>
+      <c r="X23">
         <v>1.13</v>
       </c>
-      <c r="X23">
-        <v>1.03</v>
-      </c>
       <c r="Y23">
-        <v>11.5</v>
+        <v>6</v>
       </c>
       <c r="Z23">
-        <v>1.2</v>
+        <v>1.57</v>
       </c>
       <c r="AA23">
-        <v>4.1</v>
+        <v>2.3</v>
       </c>
       <c r="AB23">
-        <v>1.54</v>
+        <v>2.75</v>
       </c>
       <c r="AC23">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="AD23">
-        <v>2.7</v>
+        <v>5.25</v>
       </c>
       <c r="AE23">
-        <v>1.46</v>
+        <v>1.13</v>
       </c>
       <c r="AF23">
+        <v>2.25</v>
+      </c>
+      <c r="AG23">
         <v>1.57</v>
       </c>
-      <c r="AG23">
-        <v>2.2</v>
-      </c>
       <c r="AH23">
-        <v>4.5</v>
+        <v>13</v>
       </c>
       <c r="AI23">
-        <v>1.18</v>
+        <v>1.02</v>
       </c>
       <c r="AJ23" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="AK23" t="s">
-        <v>114</v>
+        <v>144</v>
       </c>
       <c r="AL23" s="3">
         <v>45854.89583333334</v>
@@ -3401,34 +3503,34 @@
         <v>45854</v>
       </c>
       <c r="B24" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C24" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D24" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E24" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F24" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G24">
         <v>0</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24">
         <v>0</v>
       </c>
       <c r="J24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="L24">
         <v>2.53</v>
@@ -3503,10 +3605,10 @@
         <v>1.14</v>
       </c>
       <c r="AJ24" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AK24" t="s">
-        <v>114</v>
+        <v>145</v>
       </c>
       <c r="AL24" s="3">
         <v>45854.89583333334</v>
@@ -3517,34 +3619,34 @@
         <v>45854</v>
       </c>
       <c r="B25" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C25" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E25" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F25" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G25">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J25">
         <v>0</v>
       </c>
       <c r="K25" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="L25">
         <v>1.44</v>
@@ -3619,10 +3721,10 @@
         <v>1.1</v>
       </c>
       <c r="AJ25" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="AK25" t="s">
-        <v>114</v>
+        <v>146</v>
       </c>
       <c r="AL25" s="3">
         <v>45854.95833333334</v>
@@ -3633,112 +3735,112 @@
         <v>45854</v>
       </c>
       <c r="B26" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C26" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D26" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E26" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F26" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="L26">
-        <v>1.99</v>
+        <v>1.59</v>
       </c>
       <c r="M26">
-        <v>3.25</v>
+        <v>3.95</v>
       </c>
       <c r="N26">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="O26">
-        <v>1.67</v>
+        <v>1.51</v>
       </c>
       <c r="P26">
-        <v>10.5</v>
+        <v>17.5</v>
       </c>
       <c r="Q26">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="R26">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="S26">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="T26">
-        <v>2.5</v>
+        <v>1.93</v>
       </c>
       <c r="U26">
-        <v>1.5</v>
+        <v>1.77</v>
       </c>
       <c r="V26">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="W26">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="X26">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>9.5</v>
+        <v>23</v>
       </c>
       <c r="Z26">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="AA26">
-        <v>4.2</v>
+        <v>6.25</v>
       </c>
       <c r="AB26">
-        <v>1.54</v>
+        <v>1.34</v>
       </c>
       <c r="AC26">
-        <v>2.3</v>
+        <v>3.09</v>
       </c>
       <c r="AD26">
-        <v>2.62</v>
+        <v>1.9</v>
       </c>
       <c r="AE26">
-        <v>1.48</v>
+        <v>1.8</v>
       </c>
       <c r="AF26">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AG26">
-        <v>2.25</v>
+        <v>2.55</v>
       </c>
       <c r="AH26">
-        <v>4.75</v>
+        <v>3.1</v>
       </c>
       <c r="AI26">
-        <v>1.18</v>
+        <v>1.35</v>
       </c>
       <c r="AJ26" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="AK26" t="s">
-        <v>114</v>
+        <v>147</v>
       </c>
       <c r="AL26" s="3">
         <v>45854.97916666666</v>
@@ -3749,112 +3851,112 @@
         <v>45854</v>
       </c>
       <c r="B27" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C27" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D27" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E27" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F27" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I27">
         <v>0</v>
       </c>
       <c r="J27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="L27">
-        <v>1.29</v>
+        <v>1.94</v>
       </c>
       <c r="M27">
-        <v>4.8</v>
+        <v>3.41</v>
       </c>
       <c r="N27">
-        <v>7.3</v>
+        <v>3.2</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AB27">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="AC27">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AD27">
-        <v>2.05</v>
+        <v>2.95</v>
       </c>
       <c r="AE27">
-        <v>1.68</v>
+        <v>1.38</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG27">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH27">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AI27">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AJ27" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="AK27" t="s">
-        <v>114</v>
+        <v>148</v>
       </c>
       <c r="AL27" s="3">
         <v>45854.97916666666</v>
@@ -3865,112 +3967,112 @@
         <v>45854</v>
       </c>
       <c r="B28" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C28" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D28" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E28" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G28">
         <v>0</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28">
         <v>0</v>
       </c>
       <c r="J28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="L28">
-        <v>1.94</v>
+        <v>1.29</v>
       </c>
       <c r="M28">
-        <v>3.41</v>
+        <v>4.8</v>
       </c>
       <c r="N28">
-        <v>3.2</v>
+        <v>7.3</v>
       </c>
       <c r="O28">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="P28">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="Q28">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="R28">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S28">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T28">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="U28">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="V28">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W28">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X28">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y28">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="Z28">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AA28">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AB28">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="AC28">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AD28">
-        <v>2.95</v>
+        <v>2.05</v>
       </c>
       <c r="AE28">
-        <v>1.38</v>
+        <v>1.68</v>
       </c>
       <c r="AF28">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG28">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH28">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AI28">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AJ28" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AK28" t="s">
-        <v>114</v>
+        <v>149</v>
       </c>
       <c r="AL28" s="3">
         <v>45854.97916666666</v>
@@ -3981,25 +4083,25 @@
         <v>45854</v>
       </c>
       <c r="B29" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C29" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D29" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E29" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F29" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G29">
         <v>0</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29">
         <v>0</v>
@@ -4008,85 +4110,85 @@
         <v>0</v>
       </c>
       <c r="K29" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="L29">
-        <v>1.59</v>
+        <v>1.99</v>
       </c>
       <c r="M29">
-        <v>3.95</v>
+        <v>3.25</v>
       </c>
       <c r="N29">
+        <v>3.25</v>
+      </c>
+      <c r="O29">
+        <v>1.67</v>
+      </c>
+      <c r="P29">
+        <v>10.5</v>
+      </c>
+      <c r="Q29">
+        <v>2.3</v>
+      </c>
+      <c r="R29">
+        <v>1.3</v>
+      </c>
+      <c r="S29">
+        <v>3.4</v>
+      </c>
+      <c r="T29">
+        <v>2.5</v>
+      </c>
+      <c r="U29">
+        <v>1.5</v>
+      </c>
+      <c r="V29">
+        <v>6</v>
+      </c>
+      <c r="W29">
+        <v>1.13</v>
+      </c>
+      <c r="X29">
+        <v>1.05</v>
+      </c>
+      <c r="Y29">
+        <v>9.5</v>
+      </c>
+      <c r="Z29">
+        <v>1.22</v>
+      </c>
+      <c r="AA29">
         <v>4.2</v>
       </c>
-      <c r="O29">
-        <v>1.51</v>
-      </c>
-      <c r="P29">
-        <v>17.5</v>
-      </c>
-      <c r="Q29">
-        <v>2.55</v>
-      </c>
-      <c r="R29">
-        <v>1.2</v>
-      </c>
-      <c r="S29">
-        <v>4.1</v>
-      </c>
-      <c r="T29">
-        <v>1.93</v>
-      </c>
-      <c r="U29">
-        <v>1.77</v>
-      </c>
-      <c r="V29">
-        <v>4</v>
-      </c>
-      <c r="W29">
-        <v>1.21</v>
-      </c>
-      <c r="X29">
-        <v>1.01</v>
-      </c>
-      <c r="Y29">
-        <v>23</v>
-      </c>
-      <c r="Z29">
-        <v>1.11</v>
-      </c>
-      <c r="AA29">
-        <v>6.25</v>
-      </c>
       <c r="AB29">
-        <v>1.34</v>
+        <v>1.54</v>
       </c>
       <c r="AC29">
-        <v>3.09</v>
+        <v>2.3</v>
       </c>
       <c r="AD29">
-        <v>1.9</v>
+        <v>2.62</v>
       </c>
       <c r="AE29">
-        <v>1.8</v>
+        <v>1.48</v>
       </c>
       <c r="AF29">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AG29">
-        <v>2.55</v>
+        <v>2.25</v>
       </c>
       <c r="AH29">
-        <v>3.1</v>
+        <v>4.75</v>
       </c>
       <c r="AI29">
-        <v>1.35</v>
+        <v>1.18</v>
       </c>
       <c r="AJ29" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AK29" t="s">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="AL29" s="3">
         <v>45854.97916666666</v>

--- a/jogos_2025-07-16.xlsx
+++ b/jogos_2025-07-16.xlsx
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1693,7 +1693,7 @@
         <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1701,25 +1701,25 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.38</v>
+        <v>1.61</v>
       </c>
       <c r="M10" t="n">
-        <v>4.3</v>
+        <v>3.81</v>
       </c>
       <c r="N10" t="n">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="O10" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="P10" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="Q10" t="n">
-        <v>5</v>
+        <v>4.33</v>
       </c>
       <c r="R10" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S10" t="n">
         <v>3.4</v>
@@ -1737,47 +1737,47 @@
         <v>1.2</v>
       </c>
       <c r="X10" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AD10" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>['37', '50']</t>
+          <t>['44', '48']</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>['45+2']</t>
+          <t>['60']</t>
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2.95</v>
+        <v>2.6</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45854.85416666666</v>
@@ -1804,109 +1804,109 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G11" t="n">
+        <v>5</v>
+      </c>
+      <c r="H11" t="n">
+        <v>3</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
         <v>2</v>
       </c>
-      <c r="H11" t="n">
-        <v>2</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="M11" t="n">
-        <v>3.63</v>
+        <v>3.8</v>
       </c>
       <c r="N11" t="n">
-        <v>2.91</v>
+        <v>4.04</v>
       </c>
       <c r="O11" t="n">
-        <v>2.55</v>
+        <v>2.31</v>
       </c>
       <c r="P11" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.4</v>
+        <v>4.55</v>
       </c>
       <c r="R11" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="S11" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="T11" t="n">
-        <v>2.2</v>
+        <v>2.66</v>
       </c>
       <c r="U11" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="V11" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W11" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="X11" t="n">
-        <v>4.75</v>
+        <v>4.2</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.59</v>
+        <v>1.73</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.36</v>
+        <v>2.09</v>
       </c>
       <c r="AA11" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD11" t="n">
         <v>2.1</v>
       </c>
-      <c r="AB11" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>['56', '90+4']</t>
+          <t>['56', '70', '72', '83', '88']</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>['2', '79']</t>
+          <t>['5', '30', '90+3']</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.68</v>
+        <v>1.98</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45854.85416666666</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,23 +1933,23 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
         <v>1</v>
       </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
@@ -1959,83 +1959,83 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.36</v>
+        <v>2.6</v>
       </c>
       <c r="M12" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q12" t="n">
         <v>3.25</v>
       </c>
-      <c r="N12" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="O12" t="n">
+      <c r="R12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X12" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AD12" t="n">
         <v>2.8</v>
       </c>
-      <c r="P12" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X12" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AE12" t="inlineStr">
         <is>
+          <t>['16', '50', '70']</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>['83']</t>
-        </is>
-      </c>
       <c r="AG12" t="n">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45854.85416666666</v>
@@ -2062,103 +2062,103 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G13" t="n">
         <v>2</v>
       </c>
       <c r="H13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
         <v>1</v>
       </c>
-      <c r="I13" t="n">
-        <v>1</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
       <c r="K13" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.66</v>
+        <v>2.2</v>
       </c>
       <c r="M13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S13" t="n">
         <v>4.2</v>
       </c>
-      <c r="N13" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>5.22</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3.5</v>
-      </c>
       <c r="T13" t="n">
-        <v>2.25</v>
+        <v>1.97</v>
       </c>
       <c r="U13" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X13" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>['56', '90+4']</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>['2', '79']</t>
+        </is>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH13" t="n">
         <v>1.57</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X13" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>['44', '48']</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>['60']</t>
-        </is>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>2.73</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,25 +2191,25 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -2217,83 +2217,83 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.72</v>
+        <v>2.36</v>
       </c>
       <c r="M14" t="n">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="N14" t="n">
-        <v>4.04</v>
+        <v>2.39</v>
       </c>
       <c r="O14" t="n">
-        <v>2.31</v>
+        <v>2.8</v>
       </c>
       <c r="P14" t="n">
-        <v>2.24</v>
+        <v>2.14</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.55</v>
+        <v>2.7</v>
       </c>
       <c r="R14" t="n">
         <v>1.33</v>
       </c>
       <c r="S14" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="T14" t="n">
-        <v>2.66</v>
+        <v>2.63</v>
       </c>
       <c r="U14" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="V14" t="n">
         <v>1.01</v>
       </c>
       <c r="W14" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="X14" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.09</v>
+        <v>1.95</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.9</v>
+        <v>2.97</v>
       </c>
       <c r="AB14" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>['83']</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH14" t="n">
         <v>1.4</v>
       </c>
-      <c r="AC14" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>['56', '70', '72', '83', '88']</t>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>['5', '30', '90+3']</t>
-        </is>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.98</v>
-      </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45854.85416666666</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,22 +2320,22 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2346,83 +2346,83 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.6</v>
+        <v>1.71</v>
       </c>
       <c r="M15" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="N15" t="n">
-        <v>2.83</v>
+        <v>4.37</v>
       </c>
       <c r="O15" t="n">
-        <v>2.54</v>
+        <v>2.15</v>
       </c>
       <c r="P15" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="R15" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="S15" t="n">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="T15" t="n">
-        <v>2</v>
+        <v>2.61</v>
       </c>
       <c r="U15" t="n">
-        <v>1.7</v>
+        <v>1.42</v>
       </c>
       <c r="V15" t="n">
         <v>1.02</v>
       </c>
       <c r="W15" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="X15" t="n">
-        <v>5.8</v>
+        <v>3.4</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.4</v>
+        <v>1.75</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.7</v>
+        <v>1.85</v>
       </c>
       <c r="AA15" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>['53']</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH15" t="n">
         <v>2</v>
       </c>
-      <c r="AB15" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>['16', '50', '70']</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.42</v>
-      </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45854.85416666666</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,25 +2449,25 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G16" t="n">
+        <v>2</v>
+      </c>
+      <c r="H16" t="n">
         <v>1</v>
       </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -2475,83 +2475,83 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.71</v>
+        <v>1.38</v>
       </c>
       <c r="M16" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="N16" t="n">
-        <v>4.37</v>
+        <v>6</v>
       </c>
       <c r="O16" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="P16" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>5</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T16" t="n">
         <v>2.25</v>
       </c>
-      <c r="Q16" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.61</v>
-      </c>
       <c r="U16" t="n">
-        <v>1.42</v>
+        <v>1.57</v>
       </c>
       <c r="V16" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W16" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X16" t="n">
-        <v>3.4</v>
+        <v>4.33</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.75</v>
+        <v>1.52</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.85</v>
+        <v>2.35</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.9</v>
+        <v>2.55</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AC16" t="n">
         <v>1.7</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>['53']</t>
+          <t>['37', '50']</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45+2']</t>
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="AH16" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AJ16" t="n">
-        <v>2.4</v>
+        <v>2.95</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45854.85416666666</v>
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="M18" t="n">
-        <v>3.55</v>
+        <v>3.95</v>
       </c>
       <c r="N18" t="n">
-        <v>3.83</v>
+        <v>4.8</v>
       </c>
       <c r="O18" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="P18" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="R18" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="S18" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="T18" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="U18" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="V18" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W18" t="n">
         <v>1.18</v>
       </c>
       <c r="X18" t="n">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AC18" t="n">
         <v>1.57</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,16 +2800,16 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.15</v>
+        <v>2.24</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45854.88541666666</v>
@@ -2836,25 +2836,25 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -2862,58 +2862,58 @@
         </is>
       </c>
       <c r="L19" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="M19" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="O19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X19" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Z19" t="n">
         <v>2.05</v>
       </c>
-      <c r="M19" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="N19" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O19" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="X19" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1.96</v>
-      </c>
       <c r="AA19" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AD19" t="n">
         <v>2.2</v>
@@ -2925,14 +2925,14 @@
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>['4', '42', '56']</t>
+          <t>['42']</t>
         </is>
       </c>
       <c r="AG19" t="n">
         <v>1.3</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,25 +2965,25 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.4</v>
+        <v>1.39</v>
       </c>
       <c r="M20" t="n">
-        <v>3.25</v>
+        <v>4.46</v>
       </c>
       <c r="N20" t="n">
-        <v>2.85</v>
+        <v>6.9</v>
       </c>
       <c r="O20" t="n">
-        <v>3.2</v>
+        <v>2.03</v>
       </c>
       <c r="P20" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="Q20" t="n">
+        <v>6.66</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X20" t="n">
         <v>3.1</v>
       </c>
-      <c r="R20" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W20" t="n">
+      <c r="Y20" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AB20" t="n">
         <v>1.25</v>
       </c>
-      <c r="X20" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.42</v>
-      </c>
       <c r="AC20" t="n">
-        <v>1.6</v>
+        <v>2.38</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.2</v>
+        <v>1.53</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3054,20 +3054,20 @@
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>['42']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.6</v>
+        <v>2.8</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45854.89583333334</v>
@@ -3094,25 +3094,25 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -3120,83 +3120,83 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.39</v>
+        <v>2.33</v>
       </c>
       <c r="M21" t="n">
-        <v>4.46</v>
+        <v>3</v>
       </c>
       <c r="N21" t="n">
-        <v>6.9</v>
+        <v>3.4</v>
       </c>
       <c r="O21" t="n">
-        <v>2.03</v>
+        <v>2.84</v>
       </c>
       <c r="P21" t="n">
-        <v>2.22</v>
+        <v>1.9</v>
       </c>
       <c r="Q21" t="n">
-        <v>6.66</v>
+        <v>4.5</v>
       </c>
       <c r="R21" t="n">
-        <v>1.42</v>
+        <v>1.56</v>
       </c>
       <c r="S21" t="n">
-        <v>2.62</v>
+        <v>2.25</v>
       </c>
       <c r="T21" t="n">
-        <v>2.8</v>
+        <v>3.72</v>
       </c>
       <c r="U21" t="n">
-        <v>1.37</v>
+        <v>1.2</v>
       </c>
       <c r="V21" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="W21" t="n">
-        <v>1.28</v>
+        <v>1.57</v>
       </c>
       <c r="X21" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="Y21" t="n">
-        <v>2</v>
+        <v>2.75</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.7</v>
+        <v>5.25</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['43', '48']</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['9', '64']</t>
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.8</v>
+        <v>1.57</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="AJ21" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45854.89583333334</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,25 +3223,25 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G22" t="n">
+        <v>3</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
         <v>2</v>
       </c>
-      <c r="H22" t="n">
-        <v>1</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -3249,83 +3249,83 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.51</v>
+        <v>1.98</v>
       </c>
       <c r="M22" t="n">
-        <v>3.7</v>
+        <v>3.39</v>
       </c>
       <c r="N22" t="n">
-        <v>6</v>
+        <v>3.12</v>
       </c>
       <c r="O22" t="n">
-        <v>2.05</v>
+        <v>2.55</v>
       </c>
       <c r="P22" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="Q22" t="n">
-        <v>6.34</v>
+        <v>3.5</v>
       </c>
       <c r="R22" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="S22" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="T22" t="n">
-        <v>2.8</v>
+        <v>2.35</v>
       </c>
       <c r="U22" t="n">
-        <v>1.37</v>
+        <v>1.52</v>
       </c>
       <c r="V22" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="W22" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="X22" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.01</v>
+        <v>1.54</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.34</v>
+        <v>2.7</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.29</v>
+        <v>1.46</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.05</v>
+        <v>1.57</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>['47', '48']</t>
+          <t>['2', '30', '82']</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>['9']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.4</v>
+        <v>1.72</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.41</v>
+        <v>1.73</v>
       </c>
       <c r="AJ22" t="n">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45854.89583333334</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,109 +3352,109 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>3</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
         <v>2</v>
       </c>
-      <c r="H23" t="n">
-        <v>2</v>
-      </c>
-      <c r="I23" t="n">
-        <v>1</v>
-      </c>
-      <c r="J23" t="n">
-        <v>1</v>
-      </c>
       <c r="K23" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.33</v>
+        <v>2.16</v>
       </c>
       <c r="M23" t="n">
-        <v>3</v>
+        <v>3.21</v>
       </c>
       <c r="N23" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="O23" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X23" t="n">
         <v>3.4</v>
       </c>
-      <c r="O23" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="P23" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T23" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="X23" t="n">
-        <v>2.3</v>
-      </c>
       <c r="Y23" t="n">
-        <v>2.75</v>
+        <v>1.82</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.4</v>
+        <v>1.88</v>
       </c>
       <c r="AA23" t="n">
-        <v>5.25</v>
+        <v>1.02</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.13</v>
+        <v>1.02</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.25</v>
+        <v>1.68</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.57</v>
+        <v>2.05</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>['43', '48']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>['9', '64']</t>
+          <t>['4', '42', '56']</t>
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="AJ23" t="n">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45854.89583333334</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,25 +3481,25 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -3507,83 +3507,83 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.05</v>
+        <v>1.51</v>
       </c>
       <c r="M24" t="n">
         <v>3.7</v>
       </c>
       <c r="N24" t="n">
-        <v>3.45</v>
+        <v>6</v>
       </c>
       <c r="O24" t="n">
-        <v>2.54</v>
+        <v>2.05</v>
       </c>
       <c r="P24" t="n">
-        <v>2.46</v>
+        <v>2.33</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.7</v>
+        <v>6.34</v>
       </c>
       <c r="R24" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="S24" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="T24" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="U24" t="n">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="V24" t="n">
         <v>1.05</v>
       </c>
       <c r="W24" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="X24" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.7</v>
+        <v>2.01</v>
       </c>
       <c r="Z24" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AC24" t="n">
         <v>2.05</v>
       </c>
-      <c r="AA24" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AD24" t="n">
-        <v>2.15</v>
+        <v>1.83</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>['2', '30', '82']</t>
+          <t>['47', '48']</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['9']</t>
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.83</v>
+        <v>2.4</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45854.89583333334</v>
@@ -3739,25 +3739,25 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H26" t="n">
+        <v>2</v>
+      </c>
+      <c r="I26" t="n">
         <v>1</v>
       </c>
-      <c r="I26" t="n">
-        <v>0</v>
-      </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -3765,77 +3765,77 @@
         </is>
       </c>
       <c r="L26" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M26" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="N26" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O26" t="n">
+        <v>2</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>5</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S26" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X26" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA26" t="n">
         <v>2.08</v>
       </c>
-      <c r="M26" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N26" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="O26" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="P26" t="n">
+      <c r="AB26" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>['21', '86']</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>['45+3', '85']</t>
+        </is>
+      </c>
+      <c r="AG26" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH26" t="n">
         <v>2.3</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S26" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X26" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>['83']</t>
-        </is>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.62</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3997,22 +3997,22 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H28" t="n">
         <v>2</v>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
         <v>1</v>
@@ -4023,83 +4023,83 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.44</v>
+        <v>1.94</v>
       </c>
       <c r="M28" t="n">
-        <v>4.45</v>
+        <v>3.41</v>
       </c>
       <c r="N28" t="n">
-        <v>4.8</v>
+        <v>3.2</v>
       </c>
       <c r="O28" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X28" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Z28" t="n">
         <v>2</v>
       </c>
-      <c r="P28" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>5</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S28" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X28" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>2.9</v>
-      </c>
       <c r="AA28" t="n">
-        <v>2.08</v>
+        <v>2.95</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.73</v>
+        <v>1.38</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.52</v>
+        <v>2.1</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>['21', '86']</t>
+          <t>['90+3']</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>['45+3', '85']</t>
+          <t>['40', '63']</t>
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AH28" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AJ28" t="n">
         <v>2.3</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>0</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45854.97916666666</v>
@@ -4126,25 +4126,25 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
         <v>1</v>
       </c>
-      <c r="H29" t="n">
-        <v>2</v>
-      </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -4152,83 +4152,83 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.94</v>
+        <v>2.08</v>
       </c>
       <c r="M29" t="n">
-        <v>3.41</v>
+        <v>3.5</v>
       </c>
       <c r="N29" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="O29" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X29" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Z29" t="n">
         <v>2.5</v>
       </c>
-      <c r="P29" t="n">
+      <c r="AA29" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q29" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S29" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X29" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>2.95</v>
-      </c>
       <c r="AB29" t="n">
-        <v>1.38</v>
+        <v>1.67</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>['90+3']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>['40', '63']</t>
+          <t>['83']</t>
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AJ29" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45854.97916666666</v>
